--- a/attendance/reports/残業報告書_202406_スタッフA.xlsx
+++ b/attendance/reports/残業報告書_202406_スタッフA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JPTインターン\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\attendance\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10312D6F-E091-4228-833B-62E62D9E5C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E62D160-8433-41F4-AC75-A72DD02EBE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="2592" windowWidth="15192" windowHeight="9372" xr2:uid="{C68CD064-B3C7-480F-9DDF-FEC4ECEBFE12}"/>
+    <workbookView xWindow="3120" yWindow="1044" windowWidth="15480" windowHeight="11196" xr2:uid="{C68CD064-B3C7-480F-9DDF-FEC4ECEBFE12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -611,48 +611,6 @@
     <xf numFmtId="177" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -671,6 +629,12 @@
     <xf numFmtId="177" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -679,6 +643,42 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1015,162 +1015,162 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:38" ht="25.8" x14ac:dyDescent="0.45">
-      <c r="A2" s="22" t="str">
+      <c r="A2" s="41" t="str">
         <f>TEXT(Q2,"ggge年 m月")&amp;" 残業報告書"</f>
-        <v>令和6年 6月 残業報告書</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+        <v>令和8年 6月 残業報告書</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
       <c r="P2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="34">
-        <v>45444</v>
-      </c>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="20">
+        <v>46174</v>
+      </c>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
     </row>
     <row r="3" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="P3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
     </row>
     <row r="4" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F4" s="23" t="str">
+      <c r="F4" s="42" t="str">
         <f>Q3&amp;" "&amp;Q4&amp;"  印"</f>
         <v>営業部 スタッフC  印</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
       <c r="P4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="Q4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
     </row>
     <row r="5" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="P5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
     </row>
     <row r="6" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3"/>
       <c r="P6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="24">
         <f>IF($Q$5&lt;&gt;"",VLOOKUP($Q$5,AJ11:AL26,2),"")</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
     </row>
     <row r="7" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="40" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
       <c r="P7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="24">
         <f>IF($Q$5&lt;&gt;"",VLOOKUP($Q$5,AJ11:AL26,3),"")</f>
         <v>0.69791666666666663</v>
       </c>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="30" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30" t="s">
+      <c r="G8" s="37"/>
+      <c r="H8" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30" t="s">
+      <c r="I8" s="37"/>
+      <c r="J8" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30" t="s">
+      <c r="K8" s="37"/>
+      <c r="L8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="30"/>
-      <c r="W8" s="28" t="s">
+      <c r="M8" s="37"/>
+      <c r="W8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28" t="s">
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="40"/>
       <c r="AE8" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1195,11 +1195,11 @@
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
       <c r="S9" s="10" t="s">
         <v>20</v>
       </c>
@@ -1252,53 +1252,53 @@
     <row r="10" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A10" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U10,$Q$2+$U10,"")</f>
-        <v>45444</v>
+        <v>46174</v>
       </c>
       <c r="B10" s="6" t="str">
         <f>IF(A10&lt;&gt;"",IF(R10=0,"",R10),"")</f>
         <v/>
       </c>
-      <c r="C10" s="6" t="str">
+      <c r="C10" s="6">
         <f>IF(AND($A10&lt;&gt;"",$V10=FALSE),$Q$6,IF(R11=0,"",IF(Q11&gt;$Q$2+U10,R11+1,R11)))</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D10" s="26">
         <f>SUM(W10:Z11)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="25" t="str">
+      <c r="E10" s="31" t="str">
         <f>IF(S10&lt;&gt;"",S10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="36">
         <f>IF(ROUNDUP(AA10*24,0)&gt;60,60,ROUNDUP(AA10*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G10" s="27" t="str">
+      <c r="G10" s="36" t="str">
         <f>IF(ROUNDUP(AA10*24,0)&gt;60,ROUNDUP(AA10*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="36">
         <f>IF(ROUNDUP(AB10*24,0)&gt;60,60,ROUNDUP(AB10*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="27" t="str">
+      <c r="I10" s="36" t="str">
         <f>IF(ROUNDUP(AB10*24,0)&gt;60,ROUNDUP(AB10*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="36">
         <f>IF(ROUNDUP(AC10*24,0)&gt;60,60,ROUNDUP(AC10*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="27" t="str">
+      <c r="K10" s="36" t="str">
         <f>IF(ROUNDUP(AC10*24,0)&gt;60,ROUNDUP(AC10*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="36">
         <f>IF(ROUNDUP(AD10*24,0)&gt;60,60,ROUNDUP(AD10*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M10" s="27" t="str">
+      <c r="M10" s="36" t="str">
         <f>IF(ROUNDUP(AD10*24,0)&gt;60,ROUNDUP(AD10*24,0)-60,"")</f>
         <v/>
       </c>
@@ -1307,16 +1307,16 @@
       </c>
       <c r="Q10" s="17">
         <f>Q$2+U10</f>
-        <v>45444</v>
+        <v>46174</v>
       </c>
       <c r="R10" s="8"/>
-      <c r="S10" s="29"/>
+      <c r="S10" s="33"/>
       <c r="U10" s="12">
         <v>0</v>
       </c>
       <c r="V10" s="13" t="b">
         <f>IF(A10&lt;&gt;"",IF(OR(WEEKDAY(A10)=1,WEEKDAY(A10)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" s="13">
         <f t="shared" ref="W10" si="0">IF(V10=FALSE,
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="13">
-        <f t="shared" ref="X10:X41" si="1">IF(V10=FALSE,
+        <f t="shared" ref="X10" si="1">IF(V10=FALSE,
   IF(B10&lt;&gt;"",
     IF(C10-B10&gt;0,
                   IF(B10&lt;(5/24),(5/24)-B10,0),0
@@ -1342,39 +1342,39 @@
         <f>IF(X10=TRUE,IF(D10&lt;&gt;"",IF(D10&lt;(5/24),(5/24)-D10,0),0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="20">
+      <c r="AA10" s="38">
         <f>SUM(W10:W11)</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="20">
+      <c r="AB10" s="38">
         <f>SUM(X10:X11)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="20">
+      <c r="AC10" s="38">
         <f>SUM(Y10:Y11)</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="20">
+      <c r="AD10" s="38">
         <f>SUM(Z10:Z11)</f>
         <v>0</v>
       </c>
       <c r="AE10" s="19">
         <f>IF(OR(R10="",R11=""),IF(V10=FALSE,$Q$7-$Q$6-(1/24),0),IF(V10=FALSE,IF($C11&gt;$B11,$C11,$B11) - IF($B10&lt;$C10,$B10,$C10),$C10-$B10))</f>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF10" s="38" t="b">
         <f>IF(AND($V10=FALSE,AE10&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="20" t="b">
+      <c r="AG10" s="38" t="b">
         <f>IF(AND($V10=FALSE,AE10&gt;10/24),IF($AF10=TRUE,AE10&gt;(18/24),AE10&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="20" t="b">
+      <c r="AH10" s="38" t="b">
         <f>IF(AND($V10=TRUE,AE10&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="20" t="b">
+      <c r="AI10" s="38" t="b">
         <f>IF(AND($V10=TRUE,AE10&gt;10/24),IF($AH10=TRUE,AE10&gt;(18/24),AE10&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -1391,35 +1391,35 @@
     <row r="11" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A11" s="9" t="str">
         <f>IF(A10="","",TEXT(A10,"(aaa)"))</f>
-        <v>(土)</v>
-      </c>
-      <c r="B11" s="6" t="str">
+        <v>(月)</v>
+      </c>
+      <c r="B11" s="6">
         <f>IF(AND($A10&lt;&gt;"",$V10=FALSE),$Q$7,IF($V10=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>IF(AND(A10&lt;&gt;"",$V10=FALSE),IF(R11=0,"",IF(Q11&gt;$Q$2+U11,R11+1,R11)),IF($V10=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
+        <v/>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
       <c r="P11" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q11" s="17">
         <f>Q$2+U11</f>
-        <v>45444</v>
+        <v>46174</v>
       </c>
       <c r="R11" s="8"/>
-      <c r="S11" s="29"/>
+      <c r="S11" s="33"/>
       <c r="U11" s="14">
         <v>0</v>
       </c>
@@ -1440,15 +1440,15 @@
         <f>IF(V10=TRUE,IF(C10&lt;&gt;"",IF(C10&gt;(22/24),C10-(22/24),0),0),0) - IF(AI10,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
+      <c r="AA11" s="39"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="39"/>
+      <c r="AD11" s="39"/>
       <c r="AE11" s="18"/>
-      <c r="AF11" s="21"/>
-      <c r="AG11" s="21"/>
-      <c r="AH11" s="21"/>
-      <c r="AI11" s="21"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
       <c r="AJ11" s="16" t="s">
         <v>28</v>
       </c>
@@ -1462,53 +1462,53 @@
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A12" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U12,$Q$2+$U12,"")</f>
-        <v>45445</v>
+        <v>46175</v>
       </c>
       <c r="B12" s="6" t="str">
         <f>IF(A12&lt;&gt;"",IF(R12=0,"",R12),"")</f>
         <v/>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" s="6">
         <f>IF(AND($A12&lt;&gt;"",$V12=FALSE),$Q$6,IF(R13=0,"",IF(Q13&gt;$Q$2+U12,R13+1,R13)))</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D12" s="26">
         <f>SUM(W12:Z13)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="25" t="str">
+      <c r="E12" s="31" t="str">
         <f>IF(S12&lt;&gt;"",S12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="36">
         <f>IF(ROUNDUP(AA12*24,0)&gt;60,60,ROUNDUP(AA12*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="27" t="str">
+      <c r="G12" s="36" t="str">
         <f>IF(ROUNDUP(AA12*24,0)&gt;60,ROUNDUP(AA12*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="36">
         <f>IF(ROUNDUP(AB12*24,0)&gt;60,60,ROUNDUP(AB12*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I12" s="27" t="str">
+      <c r="I12" s="36" t="str">
         <f>IF(ROUNDUP(AB12*24,0)&gt;60,ROUNDUP(AB12*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="36">
         <f>IF(ROUNDUP(AC12*24,0)&gt;60,60,ROUNDUP(AC12*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="27" t="str">
+      <c r="K12" s="36" t="str">
         <f>IF(ROUNDUP(AC12*24,0)&gt;60,ROUNDUP(AC12*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="36">
         <f>IF(ROUNDUP(AD12*24,0)&gt;60,60,ROUNDUP(AD12*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M12" s="27" t="str">
+      <c r="M12" s="36" t="str">
         <f>IF(ROUNDUP(AD12*24,0)&gt;60,ROUNDUP(AD12*24,0)-60,"")</f>
         <v/>
       </c>
@@ -1517,16 +1517,16 @@
       </c>
       <c r="Q12" s="17">
         <f t="shared" ref="Q12:Q71" si="4">Q$2+U12</f>
-        <v>45445</v>
+        <v>46175</v>
       </c>
       <c r="R12" s="8"/>
-      <c r="S12" s="29"/>
+      <c r="S12" s="33"/>
       <c r="U12" s="12">
         <v>1</v>
       </c>
       <c r="V12" s="13" t="b">
         <f t="shared" ref="V12" si="5">IF(A12&lt;&gt;"",IF(OR(WEEKDAY(A12)=1,WEEKDAY(A12)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" s="13">
         <f t="shared" ref="W12" si="6">IF(V12=FALSE,
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="13">
-        <f t="shared" ref="X12:X43" si="7">IF(V12=FALSE,
+        <f t="shared" ref="X12" si="7">IF(V12=FALSE,
   IF(B12&lt;&gt;"",
     IF(C12-B12&gt;0,
                   IF(B12&lt;(5/24),(5/24)-B12,0),0
@@ -1552,39 +1552,39 @@
         <f>IF(X12=TRUE,IF(D12&lt;&gt;"",IF(D12&lt;(5/24),(5/24)-D12,0),0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="20">
+      <c r="AA12" s="38">
         <f>SUM(W12:W13,W10:W11)</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="20">
+      <c r="AB12" s="38">
         <f>SUM(X12:X13,X10:X11)</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="20">
+      <c r="AC12" s="38">
         <f>SUM(Y12:Y13,Y10:Y11)</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="20">
+      <c r="AD12" s="38">
         <f>SUM(Z12:Z13,Z10:Z11)</f>
         <v>0</v>
       </c>
       <c r="AE12" s="19">
         <f>IF(OR(R12="",R13=""),IF(V12=FALSE,$Q$7-$Q$6-(1/24),0),IF(V12=FALSE,IF($C13&gt;$B13,$C13,$B13) - IF($B12&lt;$C12,$B12,$C12),$C12-$B12))</f>
-        <v>0</v>
-      </c>
-      <c r="AF12" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF12" s="38" t="b">
         <f t="shared" ref="AF12" si="8">IF(AND($V12=FALSE,AE12&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG12" s="20" t="b">
+      <c r="AG12" s="38" t="b">
         <f t="shared" ref="AG12" si="9">IF(AND($V12=FALSE,AE12&gt;10/24),IF($AF12=TRUE,AE12&gt;(18/24),AE12&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH12" s="20" t="b">
+      <c r="AH12" s="38" t="b">
         <f t="shared" ref="AH12" si="10">IF(AND($V12=TRUE,AE12&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI12" s="20" t="b">
+      <c r="AI12" s="38" t="b">
         <f t="shared" ref="AI12" si="11">IF(AND($V12=TRUE,AE12&gt;10/24),IF($AH12=TRUE,AE12&gt;(18/24),AE12&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -1601,35 +1601,35 @@
     <row r="13" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A13" s="9" t="str">
         <f t="shared" ref="A13" si="12">IF(A12="","",TEXT(A12,"(aaa)"))</f>
-        <v>(日)</v>
-      </c>
-      <c r="B13" s="6" t="str">
+        <v>(火)</v>
+      </c>
+      <c r="B13" s="6">
         <f>IF(AND($A12&lt;&gt;"",$V12=FALSE),$Q$7,IF($V12=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C13" s="6" t="str">
         <f>IF(AND(A12&lt;&gt;"",$V12=FALSE),IF(R13=0,"",IF(Q13&gt;$Q$2+U13,R13+1,R13)),IF($V12=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
+        <v/>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
       <c r="P13" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q13" s="17">
         <f t="shared" si="4"/>
-        <v>45445</v>
+        <v>46175</v>
       </c>
       <c r="R13" s="8"/>
-      <c r="S13" s="29"/>
+      <c r="S13" s="33"/>
       <c r="U13" s="14">
         <v>1</v>
       </c>
@@ -1650,15 +1650,15 @@
         <f>IF(V12=TRUE,IF(C12&lt;&gt;"",IF(C12&gt;(22/24),C12-(22/24),0),0),0) - IF(AI12,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
       <c r="AE13" s="18"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
+      <c r="AF13" s="39"/>
+      <c r="AG13" s="39"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="39"/>
       <c r="AJ13" s="16" t="s">
         <v>30</v>
       </c>
@@ -1672,7 +1672,7 @@
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A14" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U14,$Q$2+$U14,"")</f>
-        <v>45446</v>
+        <v>46176</v>
       </c>
       <c r="B14" s="6" t="str">
         <f>IF(A14&lt;&gt;"",IF(R14=0,"",R14),"")</f>
@@ -1682,43 +1682,43 @@
         <f>IF(AND($A14&lt;&gt;"",$V14=FALSE),$Q$6,IF(R15=0,"",IF(Q15&gt;$Q$2+U14,R15+1,R15)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="26">
         <f>SUM(W14:Z15)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="25" t="str">
+      <c r="E14" s="31" t="str">
         <f>IF(S14&lt;&gt;"",S14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="36">
         <f>IF(ROUNDUP(AA14*24,0)&gt;60,60,ROUNDUP(AA14*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="27" t="str">
+      <c r="G14" s="36" t="str">
         <f>IF(ROUNDUP(AA14*24,0)&gt;60,ROUNDUP(AA14*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="36">
         <f>IF(ROUNDUP(AB14*24,0)&gt;60,60,ROUNDUP(AB14*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="27" t="str">
+      <c r="I14" s="36" t="str">
         <f>IF(ROUNDUP(AB14*24,0)&gt;60,ROUNDUP(AB14*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="36">
         <f>IF(ROUNDUP(AC14*24,0)&gt;60,60,ROUNDUP(AC14*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="27" t="str">
+      <c r="K14" s="36" t="str">
         <f>IF(ROUNDUP(AC14*24,0)&gt;60,ROUNDUP(AC14*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="36">
         <f>IF(ROUNDUP(AD14*24,0)&gt;60,60,ROUNDUP(AD14*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M14" s="27" t="str">
+      <c r="M14" s="36" t="str">
         <f>IF(ROUNDUP(AD14*24,0)&gt;60,ROUNDUP(AD14*24,0)-60,"")</f>
         <v/>
       </c>
@@ -1727,10 +1727,10 @@
       </c>
       <c r="Q14" s="17">
         <f t="shared" si="4"/>
-        <v>45446</v>
+        <v>46176</v>
       </c>
       <c r="R14" s="8"/>
-      <c r="S14" s="29"/>
+      <c r="S14" s="33"/>
       <c r="U14" s="12">
         <v>2</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="13">
-        <f t="shared" ref="X14:X45" si="15">IF(V14=FALSE,
+        <f t="shared" ref="X14" si="15">IF(V14=FALSE,
   IF(B14&lt;&gt;"",
     IF(C14-B14&gt;0,
                   IF(B14&lt;(5/24),(5/24)-B14,0),0
@@ -1762,19 +1762,19 @@
         <f>IF(X14=TRUE,IF(D14&lt;&gt;"",IF(D14&lt;(5/24),(5/24)-D14,0),0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="20">
+      <c r="AA14" s="38">
         <f>SUM(W14:W15,W10:W13)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="20">
+      <c r="AB14" s="38">
         <f>SUM(X14:X15,X10:X13)</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="20">
+      <c r="AC14" s="38">
         <f>SUM(Y14:Y15,Y10:Y13)</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="20">
+      <c r="AD14" s="38">
         <f>SUM(Z14:Z15,Z10:Z13)</f>
         <v>0</v>
       </c>
@@ -1782,19 +1782,19 @@
         <f>IF(OR(R14="",R15=""),IF(V14=FALSE,$Q$7-$Q$6-(1/24),0),IF(V14=FALSE,IF($C15&gt;$B15,$C15,$B15) - IF($B14&lt;$C14,$B14,$C14),$C14-$B14))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF14" s="20" t="b">
+      <c r="AF14" s="38" t="b">
         <f t="shared" ref="AF14" si="16">IF(AND($V14=FALSE,AE14&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="20" t="b">
+      <c r="AG14" s="38" t="b">
         <f t="shared" ref="AG14" si="17">IF(AND($V14=FALSE,AE14&gt;10/24),IF($AF14=TRUE,AE14&gt;(18/24),AE14&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH14" s="20" t="b">
+      <c r="AH14" s="38" t="b">
         <f t="shared" ref="AH14" si="18">IF(AND($V14=TRUE,AE14&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="20" t="b">
+      <c r="AI14" s="38" t="b">
         <f t="shared" ref="AI14" si="19">IF(AND($V14=TRUE,AE14&gt;10/24),IF($AH14=TRUE,AE14&gt;(18/24),AE14&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -1811,7 +1811,7 @@
     <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="str">
         <f t="shared" ref="A15" si="20">IF(A14="","",TEXT(A14,"(aaa)"))</f>
-        <v>(月)</v>
+        <v>(水)</v>
       </c>
       <c r="B15" s="6">
         <f>IF(AND($A14&lt;&gt;"",$V14=FALSE),$Q$7,IF($V14=TRUE,"---",""))</f>
@@ -1821,25 +1821,25 @@
         <f>IF(AND(A14&lt;&gt;"",$V14=FALSE),IF(R15=0,"",IF(Q15&gt;$Q$2+U15,R15+1,R15)),IF($V14=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
       <c r="P15" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q15" s="17">
         <f t="shared" si="4"/>
-        <v>45446</v>
+        <v>46176</v>
       </c>
       <c r="R15" s="8"/>
-      <c r="S15" s="29"/>
+      <c r="S15" s="33"/>
       <c r="U15" s="14">
         <v>2</v>
       </c>
@@ -1860,15 +1860,15 @@
         <f>IF(V14=TRUE,IF(C14&lt;&gt;"",IF(C14&gt;(22/24),C14-(22/24),0),0),0) - IF(AI14,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
       <c r="AE15" s="18"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
-      <c r="AI15" s="21"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
       <c r="AJ15" s="16" t="s">
         <v>32</v>
       </c>
@@ -1882,7 +1882,7 @@
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U16,$Q$2+$U16,"")</f>
-        <v>45447</v>
+        <v>46177</v>
       </c>
       <c r="B16" s="6" t="str">
         <f>IF(A16&lt;&gt;"",IF(R16=0,"",R16),"")</f>
@@ -1892,43 +1892,43 @@
         <f>IF(AND($A16&lt;&gt;"",$V16=FALSE),$Q$6,IF(R17=0,"",IF(Q17&gt;$Q$2+U16,R17+1,R17)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="26">
         <f>SUM(W16:Z17)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="25" t="str">
+      <c r="E16" s="31" t="str">
         <f>IF(S16&lt;&gt;"",S16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="36">
         <f>IF(ROUNDUP(AA16*24,0)&gt;60,60,ROUNDUP(AA16*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G16" s="27" t="str">
+      <c r="G16" s="36" t="str">
         <f>IF(ROUNDUP(AA16*24,0)&gt;60,ROUNDUP(AA16*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="36">
         <f>IF(ROUNDUP(AB16*24,0)&gt;60,60,ROUNDUP(AB16*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I16" s="27" t="str">
+      <c r="I16" s="36" t="str">
         <f>IF(ROUNDUP(AB16*24,0)&gt;60,ROUNDUP(AB16*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="36">
         <f>IF(ROUNDUP(AC16*24,0)&gt;60,60,ROUNDUP(AC16*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K16" s="27" t="str">
+      <c r="K16" s="36" t="str">
         <f>IF(ROUNDUP(AC16*24,0)&gt;60,ROUNDUP(AC16*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="36">
         <f>IF(ROUNDUP(AD16*24,0)&gt;60,60,ROUNDUP(AD16*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M16" s="27" t="str">
+      <c r="M16" s="36" t="str">
         <f>IF(ROUNDUP(AD16*24,0)&gt;60,ROUNDUP(AD16*24,0)-60,"")</f>
         <v/>
       </c>
@@ -1937,10 +1937,10 @@
       </c>
       <c r="Q16" s="17">
         <f t="shared" si="4"/>
-        <v>45447</v>
+        <v>46177</v>
       </c>
       <c r="R16" s="8"/>
-      <c r="S16" s="29"/>
+      <c r="S16" s="33"/>
       <c r="U16" s="12">
         <v>3</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="X16" s="13">
-        <f t="shared" ref="X16:X47" si="23">IF(V16=FALSE,
+        <f t="shared" ref="X16" si="23">IF(V16=FALSE,
   IF(B16&lt;&gt;"",
     IF(C16-B16&gt;0,
                   IF(B16&lt;(5/24),(5/24)-B16,0),0
@@ -1972,19 +1972,19 @@
         <f>IF(X16=TRUE,IF(D16&lt;&gt;"",IF(D16&lt;(5/24),(5/24)-D16,0),0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="20">
+      <c r="AA16" s="38">
         <f>SUM(W16:W17,W10:W15)</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="20">
+      <c r="AB16" s="38">
         <f>SUM(X16:X17,X10:X15)</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="20">
+      <c r="AC16" s="38">
         <f>SUM(Y16:Y17,Y10:Y15)</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="38">
         <f>SUM(Z16:Z17,Z10:Z15)</f>
         <v>0</v>
       </c>
@@ -1992,19 +1992,19 @@
         <f>IF(OR(R16="",R17=""),IF(V16=FALSE,$Q$7-$Q$6-(1/24),0),IF(V16=FALSE,IF($C17&gt;$B17,$C17,$B17) - IF($B16&lt;$C16,$B16,$C16),$C16-$B16))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF16" s="20" t="b">
+      <c r="AF16" s="38" t="b">
         <f t="shared" ref="AF16" si="24">IF(AND($V16=FALSE,AE16&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG16" s="20" t="b">
+      <c r="AG16" s="38" t="b">
         <f t="shared" ref="AG16" si="25">IF(AND($V16=FALSE,AE16&gt;10/24),IF($AF16=TRUE,AE16&gt;(18/24),AE16&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH16" s="20" t="b">
+      <c r="AH16" s="38" t="b">
         <f t="shared" ref="AH16" si="26">IF(AND($V16=TRUE,AE16&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI16" s="20" t="b">
+      <c r="AI16" s="38" t="b">
         <f t="shared" ref="AI16" si="27">IF(AND($V16=TRUE,AE16&gt;10/24),IF($AH16=TRUE,AE16&gt;(18/24),AE16&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -2021,7 +2021,7 @@
     <row r="17" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="str">
         <f t="shared" ref="A17" si="28">IF(A16="","",TEXT(A16,"(aaa)"))</f>
-        <v>(火)</v>
+        <v>(木)</v>
       </c>
       <c r="B17" s="6">
         <f>IF(AND($A16&lt;&gt;"",$V16=FALSE),$Q$7,IF($V16=TRUE,"---",""))</f>
@@ -2031,25 +2031,25 @@
         <f>IF(AND(A16&lt;&gt;"",$V16=FALSE),IF(R17=0,"",IF(Q17&gt;$Q$2+U17,R17+1,R17)),IF($V16=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
       <c r="P17" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q17" s="17">
         <f t="shared" si="4"/>
-        <v>45447</v>
+        <v>46177</v>
       </c>
       <c r="R17" s="8"/>
-      <c r="S17" s="29"/>
+      <c r="S17" s="33"/>
       <c r="U17" s="14">
         <v>3</v>
       </c>
@@ -2070,15 +2070,15 @@
         <f>IF(V16=TRUE,IF(C16&lt;&gt;"",IF(C16&gt;(22/24),C16-(22/24),0),0),0) - IF(AI16,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="21"/>
+      <c r="AA17" s="39"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
       <c r="AE17" s="18"/>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="21"/>
-      <c r="AH17" s="21"/>
-      <c r="AI17" s="21"/>
+      <c r="AF17" s="39"/>
+      <c r="AG17" s="39"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="39"/>
       <c r="AJ17" s="11" t="s">
         <v>4</v>
       </c>
@@ -2092,7 +2092,7 @@
     <row r="18" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U18,$Q$2+$U18,"")</f>
-        <v>45448</v>
+        <v>46178</v>
       </c>
       <c r="B18" s="6" t="str">
         <f>IF(A18&lt;&gt;"",IF(R18=0,"",R18),"")</f>
@@ -2102,43 +2102,43 @@
         <f>IF(AND($A18&lt;&gt;"",$V18=FALSE),$Q$6,IF(R19=0,"",IF(Q19&gt;$Q$2+U18,R19+1,R19)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="26">
         <f>SUM(W18:Z19)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="25" t="str">
+      <c r="E18" s="31" t="str">
         <f>IF(S18&lt;&gt;"",S18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="36">
         <f>IF(ROUNDUP(AA18*24,0)&gt;60,60,ROUNDUP(AA18*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G18" s="27" t="str">
+      <c r="G18" s="36" t="str">
         <f>IF(ROUNDUP(AA18*24,0)&gt;60,ROUNDUP(AA18*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="36">
         <f>IF(ROUNDUP(AB18*24,0)&gt;60,60,ROUNDUP(AB18*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I18" s="27" t="str">
+      <c r="I18" s="36" t="str">
         <f>IF(ROUNDUP(AB18*24,0)&gt;60,ROUNDUP(AB18*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="36">
         <f>IF(ROUNDUP(AC18*24,0)&gt;60,60,ROUNDUP(AC18*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="27" t="str">
+      <c r="K18" s="36" t="str">
         <f>IF(ROUNDUP(AC18*24,0)&gt;60,ROUNDUP(AC18*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="36">
         <f>IF(ROUNDUP(AD18*24,0)&gt;60,60,ROUNDUP(AD18*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M18" s="27" t="str">
+      <c r="M18" s="36" t="str">
         <f>IF(ROUNDUP(AD18*24,0)&gt;60,ROUNDUP(AD18*24,0)-60,"")</f>
         <v/>
       </c>
@@ -2147,10 +2147,10 @@
       </c>
       <c r="Q18" s="17">
         <f t="shared" si="4"/>
-        <v>45448</v>
+        <v>46178</v>
       </c>
       <c r="R18" s="8"/>
-      <c r="S18" s="29"/>
+      <c r="S18" s="33"/>
       <c r="U18" s="12">
         <v>4</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="13">
-        <f t="shared" ref="X18:X49" si="31">IF(V18=FALSE,
+        <f t="shared" ref="X18" si="31">IF(V18=FALSE,
   IF(B18&lt;&gt;"",
     IF(C18-B18&gt;0,
                   IF(B18&lt;(5/24),(5/24)-B18,0),0
@@ -2182,19 +2182,19 @@
         <f>IF(X18=TRUE,IF(D18&lt;&gt;"",IF(D18&lt;(5/24),(5/24)-D18,0),0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="20">
+      <c r="AA18" s="38">
         <f>SUM(W18:W19,W10:W17)</f>
         <v>0</v>
       </c>
-      <c r="AB18" s="20">
+      <c r="AB18" s="38">
         <f>SUM(X18:X19,X10:X17)</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="20">
+      <c r="AC18" s="38">
         <f>SUM(Y18:Y19,Y10:Y17)</f>
         <v>0</v>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="38">
         <f>SUM(Z18:Z19,Z10:Z17)</f>
         <v>0</v>
       </c>
@@ -2202,19 +2202,19 @@
         <f>IF(OR(R18="",R19=""),IF(V18=FALSE,$Q$7-$Q$6-(1/24),0),IF(V18=FALSE,IF($C19&gt;$B19,$C19,$B19) - IF($B18&lt;$C18,$B18,$C18),$C18-$B18))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF18" s="20" t="b">
+      <c r="AF18" s="38" t="b">
         <f t="shared" ref="AF18" si="32">IF(AND($V18=FALSE,AE18&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG18" s="20" t="b">
+      <c r="AG18" s="38" t="b">
         <f t="shared" ref="AG18" si="33">IF(AND($V18=FALSE,AE18&gt;10/24),IF($AF18=TRUE,AE18&gt;(18/24),AE18&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH18" s="20" t="b">
+      <c r="AH18" s="38" t="b">
         <f t="shared" ref="AH18" si="34">IF(AND($V18=TRUE,AE18&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI18" s="20" t="b">
+      <c r="AI18" s="38" t="b">
         <f t="shared" ref="AI18" si="35">IF(AND($V18=TRUE,AE18&gt;10/24),IF($AH18=TRUE,AE18&gt;(18/24),AE18&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -2231,7 +2231,7 @@
     <row r="19" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A19" s="9" t="str">
         <f t="shared" ref="A19" si="36">IF(A18="","",TEXT(A18,"(aaa)"))</f>
-        <v>(水)</v>
+        <v>(金)</v>
       </c>
       <c r="B19" s="6">
         <f>IF(AND($A18&lt;&gt;"",$V18=FALSE),$Q$7,IF($V18=TRUE,"---",""))</f>
@@ -2241,25 +2241,25 @@
         <f>IF(AND(A18&lt;&gt;"",$V18=FALSE),IF(R19=0,"",IF(Q19&gt;$Q$2+U19,R19+1,R19)),IF($V18=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
       <c r="P19" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q19" s="17">
         <f t="shared" si="4"/>
-        <v>45448</v>
+        <v>46178</v>
       </c>
       <c r="R19" s="8"/>
-      <c r="S19" s="29"/>
+      <c r="S19" s="33"/>
       <c r="U19" s="14">
         <v>4</v>
       </c>
@@ -2280,15 +2280,15 @@
         <f>IF(V18=TRUE,IF(C18&lt;&gt;"",IF(C18&gt;(22/24),C18-(22/24),0),0),0) - IF(AI18,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
+      <c r="AA19" s="39"/>
+      <c r="AB19" s="39"/>
+      <c r="AC19" s="39"/>
+      <c r="AD19" s="39"/>
       <c r="AE19" s="18"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
-      <c r="AI19" s="21"/>
+      <c r="AF19" s="39"/>
+      <c r="AG19" s="39"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="39"/>
       <c r="AJ19" s="11" t="s">
         <v>35</v>
       </c>
@@ -2302,53 +2302,53 @@
     <row r="20" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U20,$Q$2+$U20,"")</f>
-        <v>45449</v>
+        <v>46179</v>
       </c>
       <c r="B20" s="6" t="str">
         <f>IF(A20&lt;&gt;"",IF(R20=0,"",R20),"")</f>
         <v/>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="6" t="str">
         <f>IF(AND($A20&lt;&gt;"",$V20=FALSE),$Q$6,IF(R21=0,"",IF(Q21&gt;$Q$2+U20,R21+1,R21)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D20" s="32">
+        <v/>
+      </c>
+      <c r="D20" s="26">
         <f>SUM(W20:Z21)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="25" t="str">
+      <c r="E20" s="31" t="str">
         <f>IF(S20&lt;&gt;"",S20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="36">
         <f>IF(ROUNDUP(AA20*24,0)&gt;60,60,ROUNDUP(AA20*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="27" t="str">
+      <c r="G20" s="36" t="str">
         <f>IF(ROUNDUP(AA20*24,0)&gt;60,ROUNDUP(AA20*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="36">
         <f>IF(ROUNDUP(AB20*24,0)&gt;60,60,ROUNDUP(AB20*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="27" t="str">
+      <c r="I20" s="36" t="str">
         <f>IF(ROUNDUP(AB20*24,0)&gt;60,ROUNDUP(AB20*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="36">
         <f>IF(ROUNDUP(AC20*24,0)&gt;60,60,ROUNDUP(AC20*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K20" s="27" t="str">
+      <c r="K20" s="36" t="str">
         <f>IF(ROUNDUP(AC20*24,0)&gt;60,ROUNDUP(AC20*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L20" s="27">
+      <c r="L20" s="36">
         <f>IF(ROUNDUP(AD20*24,0)&gt;60,60,ROUNDUP(AD20*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M20" s="27" t="str">
+      <c r="M20" s="36" t="str">
         <f>IF(ROUNDUP(AD20*24,0)&gt;60,ROUNDUP(AD20*24,0)-60,"")</f>
         <v/>
       </c>
@@ -2357,16 +2357,16 @@
       </c>
       <c r="Q20" s="17">
         <f t="shared" si="4"/>
-        <v>45449</v>
+        <v>46179</v>
       </c>
       <c r="R20" s="8"/>
-      <c r="S20" s="29"/>
+      <c r="S20" s="33"/>
       <c r="U20" s="12">
         <v>5</v>
       </c>
       <c r="V20" s="13" t="b">
         <f t="shared" ref="V20" si="37">IF(A20&lt;&gt;"",IF(OR(WEEKDAY(A20)=1,WEEKDAY(A20)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="13">
         <f t="shared" ref="W20" si="38">IF(V20=FALSE,
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="13">
-        <f t="shared" ref="X20:X51" si="39">IF(V20=FALSE,
+        <f t="shared" ref="X20" si="39">IF(V20=FALSE,
   IF(B20&lt;&gt;"",
     IF(C20-B20&gt;0,
                   IF(B20&lt;(5/24),(5/24)-B20,0),0
@@ -2392,39 +2392,39 @@
         <f t="shared" ref="Z20" si="41">IF(V20=TRUE,IF(B20&lt;(5/24),(5/24)-B20,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="20">
+      <c r="AA20" s="38">
         <f>SUM(W20:W21,W10:W19)</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="20">
+      <c r="AB20" s="38">
         <f>SUM(X20:X21,X10:X19)</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="20">
+      <c r="AC20" s="38">
         <f>SUM(Y20:Y21,Y10:Y19)</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="38">
         <f>SUM(Z20:Z21,Z10:Z19)</f>
         <v>0</v>
       </c>
       <c r="AE20" s="19">
         <f>IF(OR(R20="",R21=""),IF(V20=FALSE,$Q$7-$Q$6-(1/24),0),IF(V20=FALSE,IF($C21&gt;$B21,$C21,$B21) - IF($B20&lt;$C20,$B20,$C20),$C20-$B20))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF20" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="38" t="b">
         <f t="shared" ref="AF20" si="42">IF(AND($V20=FALSE,AE20&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG20" s="20" t="b">
+      <c r="AG20" s="38" t="b">
         <f t="shared" ref="AG20" si="43">IF(AND($V20=FALSE,AE20&gt;10/24),IF($AF20=TRUE,AE20&gt;(18/24),AE20&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH20" s="20" t="b">
+      <c r="AH20" s="38" t="b">
         <f t="shared" ref="AH20" si="44">IF(AND($V20=TRUE,AE20&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI20" s="20" t="b">
+      <c r="AI20" s="38" t="b">
         <f t="shared" ref="AI20" si="45">IF(AND($V20=TRUE,AE20&gt;10/24),IF($AH20=TRUE,AE20&gt;(18/24),AE20&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -2441,35 +2441,35 @@
     <row r="21" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A21" s="9" t="str">
         <f t="shared" ref="A21" si="46">IF(A20="","",TEXT(A20,"(aaa)"))</f>
-        <v>(木)</v>
-      </c>
-      <c r="B21" s="6">
+        <v>(土)</v>
+      </c>
+      <c r="B21" s="6" t="str">
         <f>IF(AND($A20&lt;&gt;"",$V20=FALSE),$Q$7,IF($V20=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C21" s="6" t="str">
         <f>IF(AND(A20&lt;&gt;"",$V20=FALSE),IF(R21=0,"",IF(Q21&gt;$Q$2+U21,R21+1,R21)),IF($V20=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D21" s="27"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
       <c r="P21" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q21" s="17">
         <f t="shared" si="4"/>
-        <v>45449</v>
+        <v>46179</v>
       </c>
       <c r="R21" s="8"/>
-      <c r="S21" s="29"/>
+      <c r="S21" s="33"/>
       <c r="U21" s="14">
         <v>5</v>
       </c>
@@ -2490,15 +2490,15 @@
         <f t="shared" ref="Z21" si="48">IF(V20=TRUE,IF(C20&lt;&gt;"",IF(C20&gt;(22/24),C20-(22/24),0),0),0) - IF(AI20,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="21"/>
+      <c r="AA21" s="39"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="39"/>
       <c r="AE21" s="18"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="21"/>
+      <c r="AF21" s="39"/>
+      <c r="AG21" s="39"/>
+      <c r="AH21" s="39"/>
+      <c r="AI21" s="39"/>
       <c r="AJ21" s="11" t="s">
         <v>37</v>
       </c>
@@ -2512,53 +2512,53 @@
     <row r="22" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U22,$Q$2+$U22,"")</f>
-        <v>45450</v>
+        <v>46180</v>
       </c>
       <c r="B22" s="6" t="str">
         <f>IF(A22&lt;&gt;"",IF(R22=0,"",R22),"")</f>
         <v/>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="6" t="str">
         <f>IF(AND($A22&lt;&gt;"",$V22=FALSE),$Q$6,IF(R23=0,"",IF(Q23&gt;$Q$2+U22,R23+1,R23)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D22" s="32">
+        <v/>
+      </c>
+      <c r="D22" s="26">
         <f>SUM(W22:Z23)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="25" t="str">
+      <c r="E22" s="31" t="str">
         <f>IF(S22&lt;&gt;"",S22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="36">
         <f>IF(ROUNDUP(AA22*24,0)&gt;60,60,ROUNDUP(AA22*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G22" s="27" t="str">
+      <c r="G22" s="36" t="str">
         <f>IF(ROUNDUP(AA22*24,0)&gt;60,ROUNDUP(AA22*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="36">
         <f>IF(ROUNDUP(AB22*24,0)&gt;60,60,ROUNDUP(AB22*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I22" s="27" t="str">
+      <c r="I22" s="36" t="str">
         <f>IF(ROUNDUP(AB22*24,0)&gt;60,ROUNDUP(AB22*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="36">
         <f>IF(ROUNDUP(AC22*24,0)&gt;60,60,ROUNDUP(AC22*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K22" s="27" t="str">
+      <c r="K22" s="36" t="str">
         <f>IF(ROUNDUP(AC22*24,0)&gt;60,ROUNDUP(AC22*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L22" s="27">
+      <c r="L22" s="36">
         <f>IF(ROUNDUP(AD22*24,0)&gt;60,60,ROUNDUP(AD22*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M22" s="27" t="str">
+      <c r="M22" s="36" t="str">
         <f>IF(ROUNDUP(AD22*24,0)&gt;60,ROUNDUP(AD22*24,0)-60,"")</f>
         <v/>
       </c>
@@ -2567,16 +2567,16 @@
       </c>
       <c r="Q22" s="17">
         <f t="shared" si="4"/>
-        <v>45450</v>
+        <v>46180</v>
       </c>
       <c r="R22" s="8"/>
-      <c r="S22" s="29"/>
+      <c r="S22" s="33"/>
       <c r="U22" s="12">
         <v>6</v>
       </c>
       <c r="V22" s="13" t="b">
         <f t="shared" ref="V22" si="49">IF(A22&lt;&gt;"",IF(OR(WEEKDAY(A22)=1,WEEKDAY(A22)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="13">
         <f t="shared" ref="W22" si="50">IF(V22=FALSE,
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="13">
-        <f t="shared" ref="X22:X53" si="51">IF(V22=FALSE,
+        <f t="shared" ref="X22" si="51">IF(V22=FALSE,
   IF(B22&lt;&gt;"",
     IF(C22-B22&gt;0,
                   IF(B22&lt;(5/24),(5/24)-B22,0),0
@@ -2602,39 +2602,39 @@
         <f t="shared" ref="Z22" si="53">IF(V22=TRUE,IF(B22&lt;(5/24),(5/24)-B22,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="20">
+      <c r="AA22" s="38">
         <f>SUM(W22:W23,W10:W21)</f>
         <v>0</v>
       </c>
-      <c r="AB22" s="20">
+      <c r="AB22" s="38">
         <f>SUM(X22:X23,X10:X21)</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="20">
+      <c r="AC22" s="38">
         <f>SUM(Y22:Y23,Y10:Y21)</f>
         <v>0</v>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="38">
         <f>SUM(Z22:Z23,Z10:Z21)</f>
         <v>0</v>
       </c>
       <c r="AE22" s="19">
         <f>IF(OR(R22="",R23=""),IF(V22=FALSE,$Q$7-$Q$6-(1/24),0),IF(V22=FALSE,IF($C23&gt;$B23,$C23,$B23) - IF($B22&lt;$C22,$B22,$C22),$C22-$B22))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF22" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="38" t="b">
         <f t="shared" ref="AF22" si="54">IF(AND($V22=FALSE,AE22&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="20" t="b">
+      <c r="AG22" s="38" t="b">
         <f t="shared" ref="AG22" si="55">IF(AND($V22=FALSE,AE22&gt;10/24),IF($AF22=TRUE,AE22&gt;(18/24),AE22&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH22" s="20" t="b">
+      <c r="AH22" s="38" t="b">
         <f t="shared" ref="AH22" si="56">IF(AND($V22=TRUE,AE22&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI22" s="20" t="b">
+      <c r="AI22" s="38" t="b">
         <f t="shared" ref="AI22" si="57">IF(AND($V22=TRUE,AE22&gt;10/24),IF($AH22=TRUE,AE22&gt;(18/24),AE22&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -2651,35 +2651,35 @@
     <row r="23" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A23" s="9" t="str">
         <f t="shared" ref="A23" si="58">IF(A22="","",TEXT(A22,"(aaa)"))</f>
-        <v>(金)</v>
-      </c>
-      <c r="B23" s="6">
+        <v>(日)</v>
+      </c>
+      <c r="B23" s="6" t="str">
         <f>IF(AND($A22&lt;&gt;"",$V22=FALSE),$Q$7,IF($V22=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C23" s="6" t="str">
         <f>IF(AND(A22&lt;&gt;"",$V22=FALSE),IF(R23=0,"",IF(Q23&gt;$Q$2+U23,R23+1,R23)),IF($V22=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D23" s="27"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
       <c r="P23" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q23" s="17">
         <f t="shared" si="4"/>
-        <v>45450</v>
+        <v>46180</v>
       </c>
       <c r="R23" s="8"/>
-      <c r="S23" s="29"/>
+      <c r="S23" s="33"/>
       <c r="U23" s="14">
         <v>6</v>
       </c>
@@ -2700,15 +2700,15 @@
         <f t="shared" ref="Z23" si="60">IF(V22=TRUE,IF(C22&lt;&gt;"",IF(C22&gt;(22/24),C22-(22/24),0),0),0) - IF(AI22,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA23" s="21"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="21"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
       <c r="AE23" s="18"/>
-      <c r="AF23" s="21"/>
-      <c r="AG23" s="21"/>
-      <c r="AH23" s="21"/>
-      <c r="AI23" s="21"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="39"/>
       <c r="AJ23" s="11" t="s">
         <v>39</v>
       </c>
@@ -2722,53 +2722,53 @@
     <row r="24" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U24,$Q$2+$U24,"")</f>
-        <v>45451</v>
+        <v>46181</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>IF(A24&lt;&gt;"",IF(R24=0,"",R24),"")</f>
         <v/>
       </c>
-      <c r="C24" s="6" t="str">
+      <c r="C24" s="6">
         <f>IF(AND($A24&lt;&gt;"",$V24=FALSE),$Q$6,IF(R25=0,"",IF(Q25&gt;$Q$2+U24,R25+1,R25)))</f>
-        <v/>
-      </c>
-      <c r="D24" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D24" s="26">
         <f>SUM(W24:Z25)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="25" t="str">
+      <c r="E24" s="31" t="str">
         <f>IF(S24&lt;&gt;"",S24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="36">
         <f>IF(ROUNDUP(AA24*24,0)&gt;60,60,ROUNDUP(AA24*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G24" s="27" t="str">
+      <c r="G24" s="36" t="str">
         <f>IF(ROUNDUP(AA24*24,0)&gt;60,ROUNDUP(AA24*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="36">
         <f>IF(ROUNDUP(AB24*24,0)&gt;60,60,ROUNDUP(AB24*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I24" s="27" t="str">
+      <c r="I24" s="36" t="str">
         <f>IF(ROUNDUP(AB24*24,0)&gt;60,ROUNDUP(AB24*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J24" s="27">
+      <c r="J24" s="36">
         <f>IF(ROUNDUP(AC24*24,0)&gt;60,60,ROUNDUP(AC24*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K24" s="27" t="str">
+      <c r="K24" s="36" t="str">
         <f>IF(ROUNDUP(AC24*24,0)&gt;60,ROUNDUP(AC24*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L24" s="27">
+      <c r="L24" s="36">
         <f>IF(ROUNDUP(AD24*24,0)&gt;60,60,ROUNDUP(AD24*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M24" s="27" t="str">
+      <c r="M24" s="36" t="str">
         <f>IF(ROUNDUP(AD24*24,0)&gt;60,ROUNDUP(AD24*24,0)-60,"")</f>
         <v/>
       </c>
@@ -2777,16 +2777,16 @@
       </c>
       <c r="Q24" s="17">
         <f t="shared" si="4"/>
-        <v>45451</v>
+        <v>46181</v>
       </c>
       <c r="R24" s="8"/>
-      <c r="S24" s="29"/>
+      <c r="S24" s="33"/>
       <c r="U24" s="12">
         <v>7</v>
       </c>
       <c r="V24" s="13" t="b">
         <f t="shared" ref="V24" si="61">IF(A24&lt;&gt;"",IF(OR(WEEKDAY(A24)=1,WEEKDAY(A24)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" s="13">
         <f t="shared" ref="W24" si="62">IF(V24=FALSE,
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="13">
-        <f t="shared" ref="X24:X71" si="63">IF(V24=FALSE,
+        <f t="shared" ref="X24" si="63">IF(V24=FALSE,
   IF(B24&lt;&gt;"",
     IF(C24-B24&gt;0,
                   IF(B24&lt;(5/24),(5/24)-B24,0),0
@@ -2812,39 +2812,39 @@
         <f t="shared" ref="Z24" si="65">IF(V24=TRUE,IF(B24&lt;(5/24),(5/24)-B24,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA24" s="20">
+      <c r="AA24" s="38">
         <f>SUM(W24:W25,W10:W23)</f>
         <v>0</v>
       </c>
-      <c r="AB24" s="20">
+      <c r="AB24" s="38">
         <f>SUM(X24:X25,X10:X23)</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="20">
+      <c r="AC24" s="38">
         <f>SUM(Y24:Y25,Y10:Y23)</f>
         <v>0</v>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="38">
         <f>SUM(Z24:Z25,Z10:Z23)</f>
         <v>0</v>
       </c>
       <c r="AE24" s="19">
         <f>IF(OR(R24="",R25=""),IF(V24=FALSE,$Q$7-$Q$6-(1/24),0),IF(V24=FALSE,IF($C25&gt;$B25,$C25,$B25) - IF($B24&lt;$C24,$B24,$C24),$C24-$B24))</f>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF24" s="38" t="b">
         <f t="shared" ref="AF24" si="66">IF(AND($V24=FALSE,AE24&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG24" s="20" t="b">
+      <c r="AG24" s="38" t="b">
         <f t="shared" ref="AG24" si="67">IF(AND($V24=FALSE,AE24&gt;10/24),IF($AF24=TRUE,AE24&gt;(18/24),AE24&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH24" s="20" t="b">
+      <c r="AH24" s="38" t="b">
         <f t="shared" ref="AH24" si="68">IF(AND($V24=TRUE,AE24&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI24" s="20" t="b">
+      <c r="AI24" s="38" t="b">
         <f t="shared" ref="AI24" si="69">IF(AND($V24=TRUE,AE24&gt;10/24),IF($AH24=TRUE,AE24&gt;(18/24),AE24&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -2861,35 +2861,35 @@
     <row r="25" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A25" s="9" t="str">
         <f t="shared" ref="A25" si="70">IF(A24="","",TEXT(A24,"(aaa)"))</f>
-        <v>(土)</v>
-      </c>
-      <c r="B25" s="6" t="str">
+        <v>(月)</v>
+      </c>
+      <c r="B25" s="6">
         <f>IF(AND($A24&lt;&gt;"",$V24=FALSE),$Q$7,IF($V24=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C25" s="6" t="str">
         <f>IF(AND(A24&lt;&gt;"",$V24=FALSE),IF(R25=0,"",IF(Q25&gt;$Q$2+U25,R25+1,R25)),IF($V24=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
+        <v/>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
       <c r="P25" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q25" s="17">
         <f t="shared" si="4"/>
-        <v>45451</v>
+        <v>46181</v>
       </c>
       <c r="R25" s="8"/>
-      <c r="S25" s="29"/>
+      <c r="S25" s="33"/>
       <c r="U25" s="14">
         <v>7</v>
       </c>
@@ -2910,15 +2910,15 @@
         <f t="shared" ref="Z25" si="72">IF(V24=TRUE,IF(C24&lt;&gt;"",IF(C24&gt;(22/24),C24-(22/24),0),0),0) - IF(AI24,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
+      <c r="AA25" s="39"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="39"/>
+      <c r="AD25" s="39"/>
       <c r="AE25" s="18"/>
-      <c r="AF25" s="21"/>
-      <c r="AG25" s="21"/>
-      <c r="AH25" s="21"/>
-      <c r="AI25" s="21"/>
+      <c r="AF25" s="39"/>
+      <c r="AG25" s="39"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="39"/>
       <c r="AJ25" s="11" t="s">
         <v>41</v>
       </c>
@@ -2932,53 +2932,53 @@
     <row r="26" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U26,$Q$2+$U26,"")</f>
-        <v>45452</v>
+        <v>46182</v>
       </c>
       <c r="B26" s="6" t="str">
         <f>IF(A26&lt;&gt;"",IF(R26=0,"",R26),"")</f>
         <v/>
       </c>
-      <c r="C26" s="6" t="str">
+      <c r="C26" s="6">
         <f>IF(AND($A26&lt;&gt;"",$V26=FALSE),$Q$6,IF(R27=0,"",IF(Q27&gt;$Q$2+U26,R27+1,R27)))</f>
-        <v/>
-      </c>
-      <c r="D26" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D26" s="26">
         <f>SUM(W26:Z27)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="25" t="str">
+      <c r="E26" s="31" t="str">
         <f>IF(S26&lt;&gt;"",S26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="36">
         <f>IF(ROUNDUP(AA26*24,0)&gt;60,60,ROUNDUP(AA26*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="27" t="str">
+      <c r="G26" s="36" t="str">
         <f>IF(ROUNDUP(AA26*24,0)&gt;60,ROUNDUP(AA26*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="36">
         <f>IF(ROUNDUP(AB26*24,0)&gt;60,60,ROUNDUP(AB26*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I26" s="27" t="str">
+      <c r="I26" s="36" t="str">
         <f>IF(ROUNDUP(AB26*24,0)&gt;60,ROUNDUP(AB26*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="36">
         <f>IF(ROUNDUP(AC26*24,0)&gt;60,60,ROUNDUP(AC26*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K26" s="27" t="str">
+      <c r="K26" s="36" t="str">
         <f>IF(ROUNDUP(AC26*24,0)&gt;60,ROUNDUP(AC26*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L26" s="27">
+      <c r="L26" s="36">
         <f>IF(ROUNDUP(AD26*24,0)&gt;60,60,ROUNDUP(AD26*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M26" s="27" t="str">
+      <c r="M26" s="36" t="str">
         <f>IF(ROUNDUP(AD26*24,0)&gt;60,ROUNDUP(AD26*24,0)-60,"")</f>
         <v/>
       </c>
@@ -2987,16 +2987,16 @@
       </c>
       <c r="Q26" s="17">
         <f t="shared" si="4"/>
-        <v>45452</v>
+        <v>46182</v>
       </c>
       <c r="R26" s="8"/>
-      <c r="S26" s="29"/>
+      <c r="S26" s="33"/>
       <c r="U26" s="12">
         <v>8</v>
       </c>
       <c r="V26" s="13" t="b">
         <f t="shared" ref="V26" si="73">IF(A26&lt;&gt;"",IF(OR(WEEKDAY(A26)=1,WEEKDAY(A26)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="13">
         <f t="shared" ref="W26" si="74">IF(V26=FALSE,
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="13">
-        <f t="shared" ref="X26:X71" si="75">IF(V26=FALSE,
+        <f t="shared" ref="X26" si="75">IF(V26=FALSE,
   IF(B26&lt;&gt;"",
     IF(C26-B26&gt;0,
                   IF(B26&lt;(5/24),(5/24)-B26,0),0
@@ -3022,39 +3022,39 @@
         <f t="shared" ref="Z26" si="77">IF(V26=TRUE,IF(B26&lt;(5/24),(5/24)-B26,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA26" s="20">
+      <c r="AA26" s="38">
         <f>SUM(W26:W27,W10:W25)</f>
         <v>0</v>
       </c>
-      <c r="AB26" s="20">
+      <c r="AB26" s="38">
         <f>SUM(X26:X27,X10:X25)</f>
         <v>0</v>
       </c>
-      <c r="AC26" s="20">
+      <c r="AC26" s="38">
         <f>SUM(Y26:Y27,Y10:Y25)</f>
         <v>0</v>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="38">
         <f>SUM(Z26:Z27,Z10:Z25)</f>
         <v>0</v>
       </c>
       <c r="AE26" s="19">
         <f>IF(OR(R26="",R27=""),IF(V26=FALSE,$Q$7-$Q$6-(1/24),0),IF(V26=FALSE,IF($C27&gt;$B27,$C27,$B27) - IF($B26&lt;$C26,$B26,$C26),$C26-$B26))</f>
-        <v>0</v>
-      </c>
-      <c r="AF26" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF26" s="38" t="b">
         <f t="shared" ref="AF26" si="78">IF(AND($V26=FALSE,AE26&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG26" s="20" t="b">
+      <c r="AG26" s="38" t="b">
         <f t="shared" ref="AG26" si="79">IF(AND($V26=FALSE,AE26&gt;10/24),IF($AF26=TRUE,AE26&gt;(18/24),AE26&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH26" s="20" t="b">
+      <c r="AH26" s="38" t="b">
         <f t="shared" ref="AH26" si="80">IF(AND($V26=TRUE,AE26&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI26" s="20" t="b">
+      <c r="AI26" s="38" t="b">
         <f t="shared" ref="AI26" si="81">IF(AND($V26=TRUE,AE26&gt;10/24),IF($AH26=TRUE,AE26&gt;(18/24),AE26&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -3071,35 +3071,35 @@
     <row r="27" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A27" s="9" t="str">
         <f t="shared" ref="A27" si="82">IF(A26="","",TEXT(A26,"(aaa)"))</f>
-        <v>(日)</v>
-      </c>
-      <c r="B27" s="6" t="str">
+        <v>(火)</v>
+      </c>
+      <c r="B27" s="6">
         <f>IF(AND($A26&lt;&gt;"",$V26=FALSE),$Q$7,IF($V26=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C27" s="6" t="str">
         <f>IF(AND(A26&lt;&gt;"",$V26=FALSE),IF(R27=0,"",IF(Q27&gt;$Q$2+U27,R27+1,R27)),IF($V26=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
+        <v/>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
       <c r="P27" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q27" s="17">
         <f t="shared" si="4"/>
-        <v>45452</v>
+        <v>46182</v>
       </c>
       <c r="R27" s="8"/>
-      <c r="S27" s="29"/>
+      <c r="S27" s="33"/>
       <c r="U27" s="14">
         <v>8</v>
       </c>
@@ -3120,20 +3120,20 @@
         <f t="shared" ref="Z27" si="84">IF(V26=TRUE,IF(C26&lt;&gt;"",IF(C26&gt;(22/24),C26-(22/24),0),0),0) - IF(AI26,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA27" s="21"/>
-      <c r="AB27" s="21"/>
-      <c r="AC27" s="21"/>
-      <c r="AD27" s="21"/>
+      <c r="AA27" s="39"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="39"/>
+      <c r="AD27" s="39"/>
       <c r="AE27" s="18"/>
-      <c r="AF27" s="21"/>
-      <c r="AG27" s="21"/>
-      <c r="AH27" s="21"/>
-      <c r="AI27" s="21"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="39"/>
+      <c r="AH27" s="39"/>
+      <c r="AI27" s="39"/>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U28,$Q$2+$U28,"")</f>
-        <v>45453</v>
+        <v>46183</v>
       </c>
       <c r="B28" s="6" t="str">
         <f>IF(A28&lt;&gt;"",IF(R28=0,"",R28),"")</f>
@@ -3143,43 +3143,43 @@
         <f>IF(AND($A28&lt;&gt;"",$V28=FALSE),$Q$6,IF(R29=0,"",IF(Q29&gt;$Q$2+U28,R29+1,R29)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="26">
         <f>SUM(W28:Z29)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="25" t="str">
+      <c r="E28" s="31" t="str">
         <f>IF(S28&lt;&gt;"",S28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="36">
         <f>IF(ROUNDUP(AA28*24,0)&gt;60,60,ROUNDUP(AA28*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="27" t="str">
+      <c r="G28" s="36" t="str">
         <f>IF(ROUNDUP(AA28*24,0)&gt;60,ROUNDUP(AA28*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="36">
         <f>IF(ROUNDUP(AB28*24,0)&gt;60,60,ROUNDUP(AB28*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="27" t="str">
+      <c r="I28" s="36" t="str">
         <f>IF(ROUNDUP(AB28*24,0)&gt;60,ROUNDUP(AB28*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="36">
         <f>IF(ROUNDUP(AC28*24,0)&gt;60,60,ROUNDUP(AC28*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="27" t="str">
+      <c r="K28" s="36" t="str">
         <f>IF(ROUNDUP(AC28*24,0)&gt;60,ROUNDUP(AC28*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="36">
         <f>IF(ROUNDUP(AD28*24,0)&gt;60,60,ROUNDUP(AD28*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M28" s="27" t="str">
+      <c r="M28" s="36" t="str">
         <f>IF(ROUNDUP(AD28*24,0)&gt;60,ROUNDUP(AD28*24,0)-60,"")</f>
         <v/>
       </c>
@@ -3188,10 +3188,10 @@
       </c>
       <c r="Q28" s="17">
         <f t="shared" si="4"/>
-        <v>45453</v>
+        <v>46183</v>
       </c>
       <c r="R28" s="8"/>
-      <c r="S28" s="29"/>
+      <c r="S28" s="33"/>
       <c r="U28" s="12">
         <v>9</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="13">
-        <f t="shared" ref="X28:X71" si="87">IF(V28=FALSE,
+        <f t="shared" ref="X28" si="87">IF(V28=FALSE,
   IF(B28&lt;&gt;"",
     IF(C28-B28&gt;0,
                   IF(B28&lt;(5/24),(5/24)-B28,0),0
@@ -3223,19 +3223,19 @@
         <f t="shared" ref="Z28" si="89">IF(V28=TRUE,IF(B28&lt;(5/24),(5/24)-B28,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA28" s="20">
+      <c r="AA28" s="38">
         <f>SUM(W28:W29,W10:W27)</f>
         <v>0</v>
       </c>
-      <c r="AB28" s="20">
+      <c r="AB28" s="38">
         <f>SUM(X28:X29,X10:X27)</f>
         <v>0</v>
       </c>
-      <c r="AC28" s="20">
+      <c r="AC28" s="38">
         <f>SUM(Y28:Y29,Y10:Y27)</f>
         <v>0</v>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="38">
         <f>SUM(Z28:Z29,Z10:Z27)</f>
         <v>0</v>
       </c>
@@ -3243,19 +3243,19 @@
         <f>IF(OR(R28="",R29=""),IF(V28=FALSE,$Q$7-$Q$6-(1/24),0),IF(V28=FALSE,IF($C29&gt;$B29,$C29,$B29) - IF($B28&lt;$C28,$B28,$C28),$C28-$B28))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF28" s="20" t="b">
+      <c r="AF28" s="38" t="b">
         <f t="shared" ref="AF28" si="90">IF(AND($V28=FALSE,AE28&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="20" t="b">
+      <c r="AG28" s="38" t="b">
         <f t="shared" ref="AG28" si="91">IF(AND($V28=FALSE,AE28&gt;10/24),IF($AF28=TRUE,AE28&gt;(18/24),AE28&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH28" s="20" t="b">
+      <c r="AH28" s="38" t="b">
         <f t="shared" ref="AH28" si="92">IF(AND($V28=TRUE,AE28&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI28" s="20" t="b">
+      <c r="AI28" s="38" t="b">
         <f t="shared" ref="AI28" si="93">IF(AND($V28=TRUE,AE28&gt;10/24),IF($AH28=TRUE,AE28&gt;(18/24),AE28&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -3263,7 +3263,7 @@
     <row r="29" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="str">
         <f t="shared" ref="A29" si="94">IF(A28="","",TEXT(A28,"(aaa)"))</f>
-        <v>(月)</v>
+        <v>(水)</v>
       </c>
       <c r="B29" s="6">
         <f>IF(AND($A28&lt;&gt;"",$V28=FALSE),$Q$7,IF($V28=TRUE,"---",""))</f>
@@ -3273,25 +3273,25 @@
         <f>IF(AND(A28&lt;&gt;"",$V28=FALSE),IF(R29=0,"",IF(Q29&gt;$Q$2+U29,R29+1,R29)),IF($V28=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
       <c r="P29" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q29" s="17">
         <f t="shared" si="4"/>
-        <v>45453</v>
+        <v>46183</v>
       </c>
       <c r="R29" s="8"/>
-      <c r="S29" s="29"/>
+      <c r="S29" s="33"/>
       <c r="U29" s="14">
         <v>9</v>
       </c>
@@ -3312,20 +3312,20 @@
         <f t="shared" ref="Z29" si="96">IF(V28=TRUE,IF(C28&lt;&gt;"",IF(C28&gt;(22/24),C28-(22/24),0),0),0) - IF(AI28,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA29" s="21"/>
-      <c r="AB29" s="21"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="21"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="39"/>
       <c r="AE29" s="18"/>
-      <c r="AF29" s="21"/>
-      <c r="AG29" s="21"/>
-      <c r="AH29" s="21"/>
-      <c r="AI29" s="21"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="39"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="39"/>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U30,$Q$2+$U30,"")</f>
-        <v>45454</v>
+        <v>46184</v>
       </c>
       <c r="B30" s="6" t="str">
         <f>IF(A30&lt;&gt;"",IF(R30=0,"",R30),"")</f>
@@ -3335,43 +3335,43 @@
         <f>IF(AND($A30&lt;&gt;"",$V30=FALSE),$Q$6,IF(R31=0,"",IF(Q31&gt;$Q$2+U30,R31+1,R31)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="26">
         <f>SUM(W30:Z31)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="25" t="str">
+      <c r="E30" s="31" t="str">
         <f>IF(S30&lt;&gt;"",S30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="36">
         <f>IF(ROUNDUP(AA30*24,0)&gt;60,60,ROUNDUP(AA30*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="27" t="str">
+      <c r="G30" s="36" t="str">
         <f>IF(ROUNDUP(AA30*24,0)&gt;60,ROUNDUP(AA30*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="36">
         <f>IF(ROUNDUP(AB30*24,0)&gt;60,60,ROUNDUP(AB30*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I30" s="27" t="str">
+      <c r="I30" s="36" t="str">
         <f>IF(ROUNDUP(AB30*24,0)&gt;60,ROUNDUP(AB30*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="36">
         <f>IF(ROUNDUP(AC30*24,0)&gt;60,60,ROUNDUP(AC30*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K30" s="27" t="str">
+      <c r="K30" s="36" t="str">
         <f>IF(ROUNDUP(AC30*24,0)&gt;60,ROUNDUP(AC30*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="36">
         <f>IF(ROUNDUP(AD30*24,0)&gt;60,60,ROUNDUP(AD30*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M30" s="27" t="str">
+      <c r="M30" s="36" t="str">
         <f>IF(ROUNDUP(AD30*24,0)&gt;60,ROUNDUP(AD30*24,0)-60,"")</f>
         <v/>
       </c>
@@ -3380,10 +3380,10 @@
       </c>
       <c r="Q30" s="17">
         <f t="shared" si="4"/>
-        <v>45454</v>
+        <v>46184</v>
       </c>
       <c r="R30" s="8"/>
-      <c r="S30" s="29"/>
+      <c r="S30" s="33"/>
       <c r="U30" s="12">
         <v>10</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="13">
-        <f t="shared" ref="X30:X71" si="99">IF(V30=FALSE,
+        <f t="shared" ref="X30" si="99">IF(V30=FALSE,
   IF(B30&lt;&gt;"",
     IF(C30-B30&gt;0,
                   IF(B30&lt;(5/24),(5/24)-B30,0),0
@@ -3415,19 +3415,19 @@
         <f t="shared" ref="Z30" si="101">IF(V30=TRUE,IF(B30&lt;(5/24),(5/24)-B30,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA30" s="20">
+      <c r="AA30" s="38">
         <f>SUM(W30:W31,W10:W29)</f>
         <v>0</v>
       </c>
-      <c r="AB30" s="20">
+      <c r="AB30" s="38">
         <f>SUM(X30:X31,X10:X29)</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="20">
+      <c r="AC30" s="38">
         <f>SUM(Y30:Y31,Y10:Y29)</f>
         <v>0</v>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="38">
         <f>SUM(Z30:Z31,Z10:Z29)</f>
         <v>0</v>
       </c>
@@ -3435,19 +3435,19 @@
         <f>IF(OR(R30="",R31=""),IF(V30=FALSE,$Q$7-$Q$6-(1/24),0),IF(V30=FALSE,IF($C31&gt;$B31,$C31,$B31) - IF($B30&lt;$C30,$B30,$C30),$C30-$B30))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF30" s="20" t="b">
+      <c r="AF30" s="38" t="b">
         <f t="shared" ref="AF30" si="102">IF(AND($V30=FALSE,AE30&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG30" s="20" t="b">
+      <c r="AG30" s="38" t="b">
         <f t="shared" ref="AG30" si="103">IF(AND($V30=FALSE,AE30&gt;10/24),IF($AF30=TRUE,AE30&gt;(18/24),AE30&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH30" s="20" t="b">
+      <c r="AH30" s="38" t="b">
         <f t="shared" ref="AH30" si="104">IF(AND($V30=TRUE,AE30&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI30" s="20" t="b">
+      <c r="AI30" s="38" t="b">
         <f t="shared" ref="AI30" si="105">IF(AND($V30=TRUE,AE30&gt;10/24),IF($AH30=TRUE,AE30&gt;(18/24),AE30&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -3455,7 +3455,7 @@
     <row r="31" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A31" s="9" t="str">
         <f t="shared" ref="A31" si="106">IF(A30="","",TEXT(A30,"(aaa)"))</f>
-        <v>(火)</v>
+        <v>(木)</v>
       </c>
       <c r="B31" s="6">
         <f>IF(AND($A30&lt;&gt;"",$V30=FALSE),$Q$7,IF($V30=TRUE,"---",""))</f>
@@ -3465,25 +3465,25 @@
         <f>IF(AND(A30&lt;&gt;"",$V30=FALSE),IF(R31=0,"",IF(Q31&gt;$Q$2+U31,R31+1,R31)),IF($V30=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
       <c r="P31" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q31" s="17">
         <f t="shared" si="4"/>
-        <v>45454</v>
+        <v>46184</v>
       </c>
       <c r="R31" s="8"/>
-      <c r="S31" s="29"/>
+      <c r="S31" s="33"/>
       <c r="U31" s="14">
         <v>10</v>
       </c>
@@ -3504,20 +3504,20 @@
         <f t="shared" ref="Z31" si="108">IF(V30=TRUE,IF(C30&lt;&gt;"",IF(C30&gt;(22/24),C30-(22/24),0),0),0) - IF(AI30,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA31" s="21"/>
-      <c r="AB31" s="21"/>
-      <c r="AC31" s="21"/>
-      <c r="AD31" s="21"/>
+      <c r="AA31" s="39"/>
+      <c r="AB31" s="39"/>
+      <c r="AC31" s="39"/>
+      <c r="AD31" s="39"/>
       <c r="AE31" s="18"/>
-      <c r="AF31" s="21"/>
-      <c r="AG31" s="21"/>
-      <c r="AH31" s="21"/>
-      <c r="AI31" s="21"/>
+      <c r="AF31" s="39"/>
+      <c r="AG31" s="39"/>
+      <c r="AH31" s="39"/>
+      <c r="AI31" s="39"/>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U32,$Q$2+$U32,"")</f>
-        <v>45455</v>
+        <v>46185</v>
       </c>
       <c r="B32" s="6" t="str">
         <f>IF(A32&lt;&gt;"",IF(R32=0,"",R32),"")</f>
@@ -3527,43 +3527,43 @@
         <f>IF(AND($A32&lt;&gt;"",$V32=FALSE),$Q$6,IF(R33=0,"",IF(Q33&gt;$Q$2+U32,R33+1,R33)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="26">
         <f>SUM(W32:Z33)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="25" t="str">
+      <c r="E32" s="31" t="str">
         <f>IF(S32&lt;&gt;"",S32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="36">
         <f>IF(ROUNDUP(AA32*24,0)&gt;60,60,ROUNDUP(AA32*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G32" s="27" t="str">
+      <c r="G32" s="36" t="str">
         <f>IF(ROUNDUP(AA32*24,0)&gt;60,ROUNDUP(AA32*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="36">
         <f>IF(ROUNDUP(AB32*24,0)&gt;60,60,ROUNDUP(AB32*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I32" s="27" t="str">
+      <c r="I32" s="36" t="str">
         <f>IF(ROUNDUP(AB32*24,0)&gt;60,ROUNDUP(AB32*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J32" s="27">
+      <c r="J32" s="36">
         <f>IF(ROUNDUP(AC32*24,0)&gt;60,60,ROUNDUP(AC32*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K32" s="27" t="str">
+      <c r="K32" s="36" t="str">
         <f>IF(ROUNDUP(AC32*24,0)&gt;60,ROUNDUP(AC32*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="36">
         <f>IF(ROUNDUP(AD32*24,0)&gt;60,60,ROUNDUP(AD32*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M32" s="27" t="str">
+      <c r="M32" s="36" t="str">
         <f>IF(ROUNDUP(AD32*24,0)&gt;60,ROUNDUP(AD32*24,0)-60,"")</f>
         <v/>
       </c>
@@ -3572,10 +3572,10 @@
       </c>
       <c r="Q32" s="17">
         <f t="shared" si="4"/>
-        <v>45455</v>
+        <v>46185</v>
       </c>
       <c r="R32" s="8"/>
-      <c r="S32" s="29"/>
+      <c r="S32" s="33"/>
       <c r="U32" s="12">
         <v>11</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="13">
-        <f t="shared" ref="X32:X71" si="111">IF(V32=FALSE,
+        <f t="shared" ref="X32" si="111">IF(V32=FALSE,
   IF(B32&lt;&gt;"",
     IF(C32-B32&gt;0,
                   IF(B32&lt;(5/24),(5/24)-B32,0),0
@@ -3607,19 +3607,19 @@
         <f t="shared" ref="Z32" si="113">IF(V32=TRUE,IF(B32&lt;(5/24),(5/24)-B32,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA32" s="20">
+      <c r="AA32" s="38">
         <f>SUM(W32:W33,W10:W31)</f>
         <v>0</v>
       </c>
-      <c r="AB32" s="20">
+      <c r="AB32" s="38">
         <f>SUM(X32:X33,X10:X31)</f>
         <v>0</v>
       </c>
-      <c r="AC32" s="20">
+      <c r="AC32" s="38">
         <f>SUM(Y32:Y33,Y10:Y31)</f>
         <v>0</v>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="38">
         <f>SUM(Z32:Z33,Z10:Z31)</f>
         <v>0</v>
       </c>
@@ -3627,19 +3627,19 @@
         <f>IF(OR(R32="",R33=""),IF(V32=FALSE,$Q$7-$Q$6-(1/24),0),IF(V32=FALSE,IF($C33&gt;$B33,$C33,$B33) - IF($B32&lt;$C32,$B32,$C32),$C32-$B32))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF32" s="20" t="b">
+      <c r="AF32" s="38" t="b">
         <f t="shared" ref="AF32" si="114">IF(AND($V32=FALSE,AE32&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG32" s="20" t="b">
+      <c r="AG32" s="38" t="b">
         <f t="shared" ref="AG32" si="115">IF(AND($V32=FALSE,AE32&gt;10/24),IF($AF32=TRUE,AE32&gt;(18/24),AE32&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH32" s="20" t="b">
+      <c r="AH32" s="38" t="b">
         <f t="shared" ref="AH32" si="116">IF(AND($V32=TRUE,AE32&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI32" s="20" t="b">
+      <c r="AI32" s="38" t="b">
         <f t="shared" ref="AI32" si="117">IF(AND($V32=TRUE,AE32&gt;10/24),IF($AH32=TRUE,AE32&gt;(18/24),AE32&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -3647,7 +3647,7 @@
     <row r="33" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A33" s="9" t="str">
         <f t="shared" ref="A33" si="118">IF(A32="","",TEXT(A32,"(aaa)"))</f>
-        <v>(水)</v>
+        <v>(金)</v>
       </c>
       <c r="B33" s="6">
         <f>IF(AND($A32&lt;&gt;"",$V32=FALSE),$Q$7,IF($V32=TRUE,"---",""))</f>
@@ -3657,25 +3657,25 @@
         <f>IF(AND(A32&lt;&gt;"",$V32=FALSE),IF(R33=0,"",IF(Q33&gt;$Q$2+U33,R33+1,R33)),IF($V32=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D33" s="33"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
       <c r="P33" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q33" s="17">
         <f t="shared" si="4"/>
-        <v>45455</v>
+        <v>46185</v>
       </c>
       <c r="R33" s="8"/>
-      <c r="S33" s="29"/>
+      <c r="S33" s="33"/>
       <c r="U33" s="14">
         <v>11</v>
       </c>
@@ -3696,66 +3696,66 @@
         <f t="shared" ref="Z33" si="120">IF(V32=TRUE,IF(C32&lt;&gt;"",IF(C32&gt;(22/24),C32-(22/24),0),0),0) - IF(AI32,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="39"/>
+      <c r="AD33" s="39"/>
       <c r="AE33" s="18"/>
-      <c r="AF33" s="21"/>
-      <c r="AG33" s="21"/>
-      <c r="AH33" s="21"/>
-      <c r="AI33" s="21"/>
+      <c r="AF33" s="39"/>
+      <c r="AG33" s="39"/>
+      <c r="AH33" s="39"/>
+      <c r="AI33" s="39"/>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U34,$Q$2+$U34,"")</f>
-        <v>45456</v>
+        <v>46186</v>
       </c>
       <c r="B34" s="6" t="str">
         <f>IF(A34&lt;&gt;"",IF(R34=0,"",R34),"")</f>
         <v/>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="6" t="str">
         <f>IF(AND($A34&lt;&gt;"",$V34=FALSE),$Q$6,IF(R35=0,"",IF(Q35&gt;$Q$2+U34,R35+1,R35)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D34" s="32">
+        <v/>
+      </c>
+      <c r="D34" s="26">
         <f>SUM(W34:Z35)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="25" t="str">
+      <c r="E34" s="31" t="str">
         <f>IF(S34&lt;&gt;"",S34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="36">
         <f>IF(ROUNDUP(AA34*24,0)&gt;60,60,ROUNDUP(AA34*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G34" s="27" t="str">
+      <c r="G34" s="36" t="str">
         <f>IF(ROUNDUP(AA34*24,0)&gt;60,ROUNDUP(AA34*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="36">
         <f>IF(ROUNDUP(AB34*24,0)&gt;60,60,ROUNDUP(AB34*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I34" s="27" t="str">
+      <c r="I34" s="36" t="str">
         <f>IF(ROUNDUP(AB34*24,0)&gt;60,ROUNDUP(AB34*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J34" s="27">
+      <c r="J34" s="36">
         <f>IF(ROUNDUP(AC34*24,0)&gt;60,60,ROUNDUP(AC34*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K34" s="27" t="str">
+      <c r="K34" s="36" t="str">
         <f>IF(ROUNDUP(AC34*24,0)&gt;60,ROUNDUP(AC34*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="36">
         <f>IF(ROUNDUP(AD34*24,0)&gt;60,60,ROUNDUP(AD34*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M34" s="27" t="str">
+      <c r="M34" s="36" t="str">
         <f>IF(ROUNDUP(AD34*24,0)&gt;60,ROUNDUP(AD34*24,0)-60,"")</f>
         <v/>
       </c>
@@ -3764,16 +3764,16 @@
       </c>
       <c r="Q34" s="17">
         <f t="shared" si="4"/>
-        <v>45456</v>
+        <v>46186</v>
       </c>
       <c r="R34" s="8"/>
-      <c r="S34" s="29"/>
+      <c r="S34" s="33"/>
       <c r="U34" s="12">
         <v>12</v>
       </c>
       <c r="V34" s="13" t="b">
         <f t="shared" ref="V34" si="121">IF(A34&lt;&gt;"",IF(OR(WEEKDAY(A34)=1,WEEKDAY(A34)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="13">
         <f t="shared" ref="W34" si="122">IF(V34=FALSE,
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="X34" s="13">
-        <f t="shared" ref="X34:X71" si="123">IF(V34=FALSE,
+        <f t="shared" ref="X34" si="123">IF(V34=FALSE,
   IF(B34&lt;&gt;"",
     IF(C34-B34&gt;0,
                   IF(B34&lt;(5/24),(5/24)-B34,0),0
@@ -3799,39 +3799,39 @@
         <f t="shared" ref="Z34" si="125">IF(V34=TRUE,IF(B34&lt;(5/24),(5/24)-B34,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA34" s="20">
+      <c r="AA34" s="38">
         <f>SUM(W34:W35,W10:W33)</f>
         <v>0</v>
       </c>
-      <c r="AB34" s="20">
+      <c r="AB34" s="38">
         <f>SUM(X34:X35,X10:X33)</f>
         <v>0</v>
       </c>
-      <c r="AC34" s="20">
+      <c r="AC34" s="38">
         <f>SUM(Y34:Y35,Y10:Y33)</f>
         <v>0</v>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="38">
         <f>SUM(Z34:Z35,Z10:Z33)</f>
         <v>0</v>
       </c>
       <c r="AE34" s="19">
         <f>IF(OR(R34="",R35=""),IF(V34=FALSE,$Q$7-$Q$6-(1/24),0),IF(V34=FALSE,IF($C35&gt;$B35,$C35,$B35) - IF($B34&lt;$C34,$B34,$C34),$C34-$B34))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF34" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="38" t="b">
         <f t="shared" ref="AF34" si="126">IF(AND($V34=FALSE,AE34&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG34" s="20" t="b">
+      <c r="AG34" s="38" t="b">
         <f t="shared" ref="AG34" si="127">IF(AND($V34=FALSE,AE34&gt;10/24),IF($AF34=TRUE,AE34&gt;(18/24),AE34&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH34" s="20" t="b">
+      <c r="AH34" s="38" t="b">
         <f t="shared" ref="AH34" si="128">IF(AND($V34=TRUE,AE34&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI34" s="20" t="b">
+      <c r="AI34" s="38" t="b">
         <f t="shared" ref="AI34" si="129">IF(AND($V34=TRUE,AE34&gt;10/24),IF($AH34=TRUE,AE34&gt;(18/24),AE34&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -3839,35 +3839,35 @@
     <row r="35" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A35" s="9" t="str">
         <f t="shared" ref="A35" si="130">IF(A34="","",TEXT(A34,"(aaa)"))</f>
-        <v>(木)</v>
-      </c>
-      <c r="B35" s="6">
+        <v>(土)</v>
+      </c>
+      <c r="B35" s="6" t="str">
         <f>IF(AND($A34&lt;&gt;"",$V34=FALSE),$Q$7,IF($V34=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C35" s="6" t="str">
         <f>IF(AND(A34&lt;&gt;"",$V34=FALSE),IF(R35=0,"",IF(Q35&gt;$Q$2+U35,R35+1,R35)),IF($V34=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D35" s="27"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36"/>
       <c r="P35" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q35" s="17">
         <f t="shared" si="4"/>
-        <v>45456</v>
+        <v>46186</v>
       </c>
       <c r="R35" s="8"/>
-      <c r="S35" s="29"/>
+      <c r="S35" s="33"/>
       <c r="U35" s="14">
         <v>12</v>
       </c>
@@ -3888,66 +3888,66 @@
         <f t="shared" ref="Z35" si="132">IF(V34=TRUE,IF(C34&lt;&gt;"",IF(C34&gt;(22/24),C34-(22/24),0),0),0) - IF(AI34,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA35" s="21"/>
-      <c r="AB35" s="21"/>
-      <c r="AC35" s="21"/>
-      <c r="AD35" s="21"/>
+      <c r="AA35" s="39"/>
+      <c r="AB35" s="39"/>
+      <c r="AC35" s="39"/>
+      <c r="AD35" s="39"/>
       <c r="AE35" s="18"/>
-      <c r="AF35" s="21"/>
-      <c r="AG35" s="21"/>
-      <c r="AH35" s="21"/>
-      <c r="AI35" s="21"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="39"/>
+      <c r="AH35" s="39"/>
+      <c r="AI35" s="39"/>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A36" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U36,$Q$2+$U36,"")</f>
-        <v>45457</v>
+        <v>46187</v>
       </c>
       <c r="B36" s="6" t="str">
         <f>IF(A36&lt;&gt;"",IF(R36=0,"",R36),"")</f>
         <v/>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="6" t="str">
         <f>IF(AND($A36&lt;&gt;"",$V36=FALSE),$Q$6,IF(R37=0,"",IF(Q37&gt;$Q$2+U36,R37+1,R37)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D36" s="32">
+        <v/>
+      </c>
+      <c r="D36" s="26">
         <f>SUM(W36:Z37)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="25" t="str">
+      <c r="E36" s="31" t="str">
         <f>IF(S36&lt;&gt;"",S36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="27">
+      <c r="F36" s="36">
         <f>IF(ROUNDUP(AA36*24,0)&gt;60,60,ROUNDUP(AA36*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G36" s="27" t="str">
+      <c r="G36" s="36" t="str">
         <f>IF(ROUNDUP(AA36*24,0)&gt;60,ROUNDUP(AA36*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H36" s="27">
+      <c r="H36" s="36">
         <f>IF(ROUNDUP(AB36*24,0)&gt;60,60,ROUNDUP(AB36*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I36" s="27" t="str">
+      <c r="I36" s="36" t="str">
         <f>IF(ROUNDUP(AB36*24,0)&gt;60,ROUNDUP(AB36*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J36" s="27">
+      <c r="J36" s="36">
         <f>IF(ROUNDUP(AC36*24,0)&gt;60,60,ROUNDUP(AC36*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K36" s="27" t="str">
+      <c r="K36" s="36" t="str">
         <f>IF(ROUNDUP(AC36*24,0)&gt;60,ROUNDUP(AC36*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L36" s="27">
+      <c r="L36" s="36">
         <f>IF(ROUNDUP(AD36*24,0)&gt;60,60,ROUNDUP(AD36*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M36" s="27" t="str">
+      <c r="M36" s="36" t="str">
         <f>IF(ROUNDUP(AD36*24,0)&gt;60,ROUNDUP(AD36*24,0)-60,"")</f>
         <v/>
       </c>
@@ -3956,16 +3956,16 @@
       </c>
       <c r="Q36" s="17">
         <f t="shared" si="4"/>
-        <v>45457</v>
+        <v>46187</v>
       </c>
       <c r="R36" s="8"/>
-      <c r="S36" s="29"/>
+      <c r="S36" s="33"/>
       <c r="U36" s="12">
         <v>13</v>
       </c>
       <c r="V36" s="13" t="b">
         <f t="shared" ref="V36" si="133">IF(A36&lt;&gt;"",IF(OR(WEEKDAY(A36)=1,WEEKDAY(A36)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="13">
         <f t="shared" ref="W36" si="134">IF(V36=FALSE,
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="X36" s="13">
-        <f t="shared" ref="X36:X71" si="135">IF(V36=FALSE,
+        <f t="shared" ref="X36" si="135">IF(V36=FALSE,
   IF(B36&lt;&gt;"",
     IF(C36-B36&gt;0,
                   IF(B36&lt;(5/24),(5/24)-B36,0),0
@@ -3991,39 +3991,39 @@
         <f t="shared" ref="Z36" si="137">IF(V36=TRUE,IF(B36&lt;(5/24),(5/24)-B36,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA36" s="20">
+      <c r="AA36" s="38">
         <f>SUM(W36:W37,W10:W35)</f>
         <v>0</v>
       </c>
-      <c r="AB36" s="20">
+      <c r="AB36" s="38">
         <f>SUM(X36:X37,X10:X35)</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="20">
+      <c r="AC36" s="38">
         <f>SUM(Y36:Y37,Y10:Y35)</f>
         <v>0</v>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="38">
         <f>SUM(Z36:Z37,Z10:Z35)</f>
         <v>0</v>
       </c>
       <c r="AE36" s="19">
         <f>IF(OR(R36="",R37=""),IF(V36=FALSE,$Q$7-$Q$6-(1/24),0),IF(V36=FALSE,IF($C37&gt;$B37,$C37,$B37) - IF($B36&lt;$C36,$B36,$C36),$C36-$B36))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF36" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="38" t="b">
         <f t="shared" ref="AF36" si="138">IF(AND($V36=FALSE,AE36&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG36" s="20" t="b">
+      <c r="AG36" s="38" t="b">
         <f t="shared" ref="AG36" si="139">IF(AND($V36=FALSE,AE36&gt;10/24),IF($AF36=TRUE,AE36&gt;(18/24),AE36&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH36" s="20" t="b">
+      <c r="AH36" s="38" t="b">
         <f t="shared" ref="AH36" si="140">IF(AND($V36=TRUE,AE36&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI36" s="20" t="b">
+      <c r="AI36" s="38" t="b">
         <f t="shared" ref="AI36" si="141">IF(AND($V36=TRUE,AE36&gt;10/24),IF($AH36=TRUE,AE36&gt;(18/24),AE36&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -4031,35 +4031,35 @@
     <row r="37" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A37" s="9" t="str">
         <f t="shared" ref="A37" si="142">IF(A36="","",TEXT(A36,"(aaa)"))</f>
-        <v>(金)</v>
-      </c>
-      <c r="B37" s="6">
+        <v>(日)</v>
+      </c>
+      <c r="B37" s="6" t="str">
         <f>IF(AND($A36&lt;&gt;"",$V36=FALSE),$Q$7,IF($V36=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C37" s="6" t="str">
         <f>IF(AND(A36&lt;&gt;"",$V36=FALSE),IF(R37=0,"",IF(Q37&gt;$Q$2+U37,R37+1,R37)),IF($V36=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D37" s="27"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
       <c r="P37" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q37" s="17">
         <f t="shared" si="4"/>
-        <v>45457</v>
+        <v>46187</v>
       </c>
       <c r="R37" s="8"/>
-      <c r="S37" s="29"/>
+      <c r="S37" s="33"/>
       <c r="U37" s="14">
         <v>13</v>
       </c>
@@ -4080,66 +4080,66 @@
         <f t="shared" ref="Z37" si="144">IF(V36=TRUE,IF(C36&lt;&gt;"",IF(C36&gt;(22/24),C36-(22/24),0),0),0) - IF(AI36,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA37" s="21"/>
-      <c r="AB37" s="21"/>
-      <c r="AC37" s="21"/>
-      <c r="AD37" s="21"/>
+      <c r="AA37" s="39"/>
+      <c r="AB37" s="39"/>
+      <c r="AC37" s="39"/>
+      <c r="AD37" s="39"/>
       <c r="AE37" s="18"/>
-      <c r="AF37" s="21"/>
-      <c r="AG37" s="21"/>
-      <c r="AH37" s="21"/>
-      <c r="AI37" s="21"/>
+      <c r="AF37" s="39"/>
+      <c r="AG37" s="39"/>
+      <c r="AH37" s="39"/>
+      <c r="AI37" s="39"/>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A38" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U38,$Q$2+$U38,"")</f>
-        <v>45458</v>
+        <v>46188</v>
       </c>
       <c r="B38" s="6" t="str">
         <f>IF(A38&lt;&gt;"",IF(R38=0,"",R38),"")</f>
         <v/>
       </c>
-      <c r="C38" s="6" t="str">
+      <c r="C38" s="6">
         <f>IF(AND($A38&lt;&gt;"",$V38=FALSE),$Q$6,IF(R39=0,"",IF(Q39&gt;$Q$2+U38,R39+1,R39)))</f>
-        <v/>
-      </c>
-      <c r="D38" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D38" s="26">
         <f>SUM(W38:Z39)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="25" t="str">
+      <c r="E38" s="31" t="str">
         <f>IF(S38&lt;&gt;"",S38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="36">
         <f>IF(ROUNDUP(AA38*24,0)&gt;60,60,ROUNDUP(AA38*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G38" s="27" t="str">
+      <c r="G38" s="36" t="str">
         <f>IF(ROUNDUP(AA38*24,0)&gt;60,ROUNDUP(AA38*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="36">
         <f>IF(ROUNDUP(AB38*24,0)&gt;60,60,ROUNDUP(AB38*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I38" s="27" t="str">
+      <c r="I38" s="36" t="str">
         <f>IF(ROUNDUP(AB38*24,0)&gt;60,ROUNDUP(AB38*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J38" s="27">
+      <c r="J38" s="36">
         <f>IF(ROUNDUP(AC38*24,0)&gt;60,60,ROUNDUP(AC38*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K38" s="27" t="str">
+      <c r="K38" s="36" t="str">
         <f>IF(ROUNDUP(AC38*24,0)&gt;60,ROUNDUP(AC38*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L38" s="27">
+      <c r="L38" s="36">
         <f>IF(ROUNDUP(AD38*24,0)&gt;60,60,ROUNDUP(AD38*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M38" s="27" t="str">
+      <c r="M38" s="36" t="str">
         <f>IF(ROUNDUP(AD38*24,0)&gt;60,ROUNDUP(AD38*24,0)-60,"")</f>
         <v/>
       </c>
@@ -4148,16 +4148,16 @@
       </c>
       <c r="Q38" s="17">
         <f t="shared" si="4"/>
-        <v>45458</v>
+        <v>46188</v>
       </c>
       <c r="R38" s="8"/>
-      <c r="S38" s="29"/>
+      <c r="S38" s="33"/>
       <c r="U38" s="12">
         <v>14</v>
       </c>
       <c r="V38" s="13" t="b">
         <f t="shared" ref="V38" si="145">IF(A38&lt;&gt;"",IF(OR(WEEKDAY(A38)=1,WEEKDAY(A38)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="146">IF(V38=FALSE,
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="13">
-        <f t="shared" ref="X38:X71" si="147">IF(V38=FALSE,
+        <f t="shared" ref="X38" si="147">IF(V38=FALSE,
   IF(B38&lt;&gt;"",
     IF(C38-B38&gt;0,
                   IF(B38&lt;(5/24),(5/24)-B38,0),0
@@ -4183,39 +4183,39 @@
         <f t="shared" ref="Z38" si="149">IF(V38=TRUE,IF(B38&lt;(5/24),(5/24)-B38,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA38" s="20">
+      <c r="AA38" s="38">
         <f>SUM(W38:W39,W10:W37)</f>
         <v>0</v>
       </c>
-      <c r="AB38" s="20">
+      <c r="AB38" s="38">
         <f>SUM(X38:X39,X10:X37)</f>
         <v>0</v>
       </c>
-      <c r="AC38" s="20">
+      <c r="AC38" s="38">
         <f>SUM(Y38:Y39,Y10:Y37)</f>
         <v>0</v>
       </c>
-      <c r="AD38" s="20">
+      <c r="AD38" s="38">
         <f>SUM(Z38:Z39,Z10:Z37)</f>
         <v>0</v>
       </c>
       <c r="AE38" s="19">
         <f>IF(OR(R38="",R39=""),IF(V38=FALSE,$Q$7-$Q$6-(1/24),0),IF(V38=FALSE,IF($C39&gt;$B39,$C39,$B39) - IF($B38&lt;$C38,$B38,$C38),$C38-$B38))</f>
-        <v>0</v>
-      </c>
-      <c r="AF38" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF38" s="38" t="b">
         <f t="shared" ref="AF38" si="150">IF(AND($V38=FALSE,AE38&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG38" s="20" t="b">
+      <c r="AG38" s="38" t="b">
         <f t="shared" ref="AG38" si="151">IF(AND($V38=FALSE,AE38&gt;10/24),IF($AF38=TRUE,AE38&gt;(18/24),AE38&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH38" s="20" t="b">
+      <c r="AH38" s="38" t="b">
         <f t="shared" ref="AH38" si="152">IF(AND($V38=TRUE,AE38&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI38" s="20" t="b">
+      <c r="AI38" s="38" t="b">
         <f t="shared" ref="AI38" si="153">IF(AND($V38=TRUE,AE38&gt;10/24),IF($AH38=TRUE,AE38&gt;(18/24),AE38&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -4223,35 +4223,35 @@
     <row r="39" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A39" s="9" t="str">
         <f t="shared" ref="A39" si="154">IF(A38="","",TEXT(A38,"(aaa)"))</f>
-        <v>(土)</v>
-      </c>
-      <c r="B39" s="6" t="str">
+        <v>(月)</v>
+      </c>
+      <c r="B39" s="6">
         <f>IF(AND($A38&lt;&gt;"",$V38=FALSE),$Q$7,IF($V38=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C39" s="6" t="str">
         <f>IF(AND(A38&lt;&gt;"",$V38=FALSE),IF(R39=0,"",IF(Q39&gt;$Q$2+U39,R39+1,R39)),IF($V38=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
+        <v/>
+      </c>
+      <c r="D39" s="27"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
       <c r="P39" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q39" s="17">
         <f t="shared" si="4"/>
-        <v>45458</v>
+        <v>46188</v>
       </c>
       <c r="R39" s="8"/>
-      <c r="S39" s="29"/>
+      <c r="S39" s="33"/>
       <c r="U39" s="14">
         <v>14</v>
       </c>
@@ -4272,66 +4272,66 @@
         <f t="shared" ref="Z39" si="156">IF(V38=TRUE,IF(C38&lt;&gt;"",IF(C38&gt;(22/24),C38-(22/24),0),0),0) - IF(AI38,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA39" s="21"/>
-      <c r="AB39" s="21"/>
-      <c r="AC39" s="21"/>
-      <c r="AD39" s="21"/>
+      <c r="AA39" s="39"/>
+      <c r="AB39" s="39"/>
+      <c r="AC39" s="39"/>
+      <c r="AD39" s="39"/>
       <c r="AE39" s="18"/>
-      <c r="AF39" s="21"/>
-      <c r="AG39" s="21"/>
-      <c r="AH39" s="21"/>
-      <c r="AI39" s="21"/>
+      <c r="AF39" s="39"/>
+      <c r="AG39" s="39"/>
+      <c r="AH39" s="39"/>
+      <c r="AI39" s="39"/>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A40" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U40,$Q$2+$U40,"")</f>
-        <v>45459</v>
+        <v>46189</v>
       </c>
       <c r="B40" s="6" t="str">
         <f>IF(A40&lt;&gt;"",IF(R40=0,"",R40),"")</f>
         <v/>
       </c>
-      <c r="C40" s="6" t="str">
+      <c r="C40" s="6">
         <f>IF(AND($A40&lt;&gt;"",$V40=FALSE),$Q$6,IF(R41=0,"",IF(Q41&gt;$Q$2+U40,R41+1,R41)))</f>
-        <v/>
-      </c>
-      <c r="D40" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D40" s="26">
         <f>SUM(W40:Z41)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="25" t="str">
+      <c r="E40" s="31" t="str">
         <f>IF(S40&lt;&gt;"",S40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="36">
         <f>IF(ROUNDUP(AA40*24,0)&gt;60,60,ROUNDUP(AA40*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G40" s="27" t="str">
+      <c r="G40" s="36" t="str">
         <f>IF(ROUNDUP(AA40*24,0)&gt;60,ROUNDUP(AA40*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="36">
         <f>IF(ROUNDUP(AB40*24,0)&gt;60,60,ROUNDUP(AB40*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I40" s="27" t="str">
+      <c r="I40" s="36" t="str">
         <f>IF(ROUNDUP(AB40*24,0)&gt;60,ROUNDUP(AB40*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="36">
         <f>IF(ROUNDUP(AC40*24,0)&gt;60,60,ROUNDUP(AC40*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K40" s="27" t="str">
+      <c r="K40" s="36" t="str">
         <f>IF(ROUNDUP(AC40*24,0)&gt;60,ROUNDUP(AC40*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L40" s="27">
+      <c r="L40" s="36">
         <f>IF(ROUNDUP(AD40*24,0)&gt;60,60,ROUNDUP(AD40*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M40" s="27" t="str">
+      <c r="M40" s="36" t="str">
         <f>IF(ROUNDUP(AD40*24,0)&gt;60,ROUNDUP(AD40*24,0)-60,"")</f>
         <v/>
       </c>
@@ -4340,16 +4340,16 @@
       </c>
       <c r="Q40" s="17">
         <f t="shared" si="4"/>
-        <v>45459</v>
+        <v>46189</v>
       </c>
       <c r="R40" s="8"/>
-      <c r="S40" s="29"/>
+      <c r="S40" s="33"/>
       <c r="U40" s="12">
         <v>15</v>
       </c>
       <c r="V40" s="13" t="b">
         <f t="shared" ref="V40" si="157">IF(A40&lt;&gt;"",IF(OR(WEEKDAY(A40)=1,WEEKDAY(A40)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" s="13">
         <f t="shared" ref="W40" si="158">IF(V40=FALSE,
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="13">
-        <f t="shared" ref="X40:X71" si="159">IF(V40=FALSE,
+        <f t="shared" ref="X40" si="159">IF(V40=FALSE,
   IF(B40&lt;&gt;"",
     IF(C40-B40&gt;0,
                   IF(B40&lt;(5/24),(5/24)-B40,0),0
@@ -4375,39 +4375,39 @@
         <f t="shared" ref="Z40" si="161">IF(V40=TRUE,IF(B40&lt;(5/24),(5/24)-B40,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA40" s="20">
+      <c r="AA40" s="38">
         <f>SUM(W40:W41,W10:W39)</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="20">
+      <c r="AB40" s="38">
         <f>SUM(X40:X41,X10:X39)</f>
         <v>0</v>
       </c>
-      <c r="AC40" s="20">
+      <c r="AC40" s="38">
         <f>SUM(Y40:Y41,Y10:Y39)</f>
         <v>0</v>
       </c>
-      <c r="AD40" s="20">
+      <c r="AD40" s="38">
         <f>SUM(Z40:Z41,Z10:Z39)</f>
         <v>0</v>
       </c>
       <c r="AE40" s="19">
         <f>IF(OR(R40="",R41=""),IF(V40=FALSE,$Q$7-$Q$6-(1/24),0),IF(V40=FALSE,IF($C41&gt;$B41,$C41,$B41) - IF($B40&lt;$C40,$B40,$C40),$C40-$B40))</f>
-        <v>0</v>
-      </c>
-      <c r="AF40" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF40" s="38" t="b">
         <f t="shared" ref="AF40" si="162">IF(AND($V40=FALSE,AE40&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG40" s="20" t="b">
+      <c r="AG40" s="38" t="b">
         <f t="shared" ref="AG40" si="163">IF(AND($V40=FALSE,AE40&gt;10/24),IF($AF40=TRUE,AE40&gt;(18/24),AE40&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH40" s="20" t="b">
+      <c r="AH40" s="38" t="b">
         <f t="shared" ref="AH40" si="164">IF(AND($V40=TRUE,AE40&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI40" s="20" t="b">
+      <c r="AI40" s="38" t="b">
         <f t="shared" ref="AI40" si="165">IF(AND($V40=TRUE,AE40&gt;10/24),IF($AH40=TRUE,AE40&gt;(18/24),AE40&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -4415,35 +4415,35 @@
     <row r="41" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A41" s="9" t="str">
         <f t="shared" ref="A41" si="166">IF(A40="","",TEXT(A40,"(aaa)"))</f>
-        <v>(日)</v>
-      </c>
-      <c r="B41" s="6" t="str">
+        <v>(火)</v>
+      </c>
+      <c r="B41" s="6">
         <f>IF(AND($A40&lt;&gt;"",$V40=FALSE),$Q$7,IF($V40=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C41" s="6" t="str">
         <f>IF(AND(A40&lt;&gt;"",$V40=FALSE),IF(R41=0,"",IF(Q41&gt;$Q$2+U41,R41+1,R41)),IF($V40=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D41" s="33"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
+        <v/>
+      </c>
+      <c r="D41" s="27"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
       <c r="P41" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q41" s="17">
         <f t="shared" si="4"/>
-        <v>45459</v>
+        <v>46189</v>
       </c>
       <c r="R41" s="8"/>
-      <c r="S41" s="29"/>
+      <c r="S41" s="33"/>
       <c r="U41" s="14">
         <v>15</v>
       </c>
@@ -4464,20 +4464,20 @@
         <f t="shared" ref="Z41" si="168">IF(V40=TRUE,IF(C40&lt;&gt;"",IF(C40&gt;(22/24),C40-(22/24),0),0),0) - IF(AI40,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA41" s="21"/>
-      <c r="AB41" s="21"/>
-      <c r="AC41" s="21"/>
-      <c r="AD41" s="21"/>
+      <c r="AA41" s="39"/>
+      <c r="AB41" s="39"/>
+      <c r="AC41" s="39"/>
+      <c r="AD41" s="39"/>
       <c r="AE41" s="18"/>
-      <c r="AF41" s="21"/>
-      <c r="AG41" s="21"/>
-      <c r="AH41" s="21"/>
-      <c r="AI41" s="21"/>
+      <c r="AF41" s="39"/>
+      <c r="AG41" s="39"/>
+      <c r="AH41" s="39"/>
+      <c r="AI41" s="39"/>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A42" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U42,$Q$2+$U42,"")</f>
-        <v>45460</v>
+        <v>46190</v>
       </c>
       <c r="B42" s="6" t="str">
         <f>IF(A42&lt;&gt;"",IF(R42=0,"",R42),"")</f>
@@ -4487,43 +4487,43 @@
         <f>IF(AND($A42&lt;&gt;"",$V42=FALSE),$Q$6,IF(R43=0,"",IF(Q43&gt;$Q$2+U42,R43+1,R43)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="26">
         <f>SUM(W42:Z43)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="25" t="str">
+      <c r="E42" s="31" t="str">
         <f>IF(S42&lt;&gt;"",S42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="36">
         <f>IF(ROUNDUP(AA42*24,0)&gt;60,60,ROUNDUP(AA42*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G42" s="27" t="str">
+      <c r="G42" s="36" t="str">
         <f>IF(ROUNDUP(AA42*24,0)&gt;60,ROUNDUP(AA42*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="36">
         <f>IF(ROUNDUP(AB42*24,0)&gt;60,60,ROUNDUP(AB42*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I42" s="27" t="str">
+      <c r="I42" s="36" t="str">
         <f>IF(ROUNDUP(AB42*24,0)&gt;60,ROUNDUP(AB42*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J42" s="27">
+      <c r="J42" s="36">
         <f>IF(ROUNDUP(AC42*24,0)&gt;60,60,ROUNDUP(AC42*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K42" s="27" t="str">
+      <c r="K42" s="36" t="str">
         <f>IF(ROUNDUP(AC42*24,0)&gt;60,ROUNDUP(AC42*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L42" s="27">
+      <c r="L42" s="36">
         <f>IF(ROUNDUP(AD42*24,0)&gt;60,60,ROUNDUP(AD42*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M42" s="27" t="str">
+      <c r="M42" s="36" t="str">
         <f>IF(ROUNDUP(AD42*24,0)&gt;60,ROUNDUP(AD42*24,0)-60,"")</f>
         <v/>
       </c>
@@ -4532,10 +4532,10 @@
       </c>
       <c r="Q42" s="17">
         <f t="shared" si="4"/>
-        <v>45460</v>
+        <v>46190</v>
       </c>
       <c r="R42" s="8"/>
-      <c r="S42" s="29"/>
+      <c r="S42" s="33"/>
       <c r="U42" s="12">
         <v>16</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="13">
-        <f t="shared" ref="X42:X71" si="171">IF(V42=FALSE,
+        <f t="shared" ref="X42" si="171">IF(V42=FALSE,
   IF(B42&lt;&gt;"",
     IF(C42-B42&gt;0,
                   IF(B42&lt;(5/24),(5/24)-B42,0),0
@@ -4567,19 +4567,19 @@
         <f t="shared" ref="Z42" si="173">IF(V42=TRUE,IF(B42&lt;(5/24),(5/24)-B42,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA42" s="20">
+      <c r="AA42" s="38">
         <f>SUM(W42:W43,W10:W41)</f>
         <v>0</v>
       </c>
-      <c r="AB42" s="20">
+      <c r="AB42" s="38">
         <f>SUM(X42:X43,X10:X41)</f>
         <v>0</v>
       </c>
-      <c r="AC42" s="20">
+      <c r="AC42" s="38">
         <f>SUM(Y42:Y43,Y10:Y41)</f>
         <v>0</v>
       </c>
-      <c r="AD42" s="20">
+      <c r="AD42" s="38">
         <f>SUM(Z42:Z43,Z10:Z41)</f>
         <v>0</v>
       </c>
@@ -4587,19 +4587,19 @@
         <f>IF(OR(R42="",R43=""),IF(V42=FALSE,$Q$7-$Q$6-(1/24),0),IF(V42=FALSE,IF($C43&gt;$B43,$C43,$B43) - IF($B42&lt;$C42,$B42,$C42),$C42-$B42))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF42" s="20" t="b">
+      <c r="AF42" s="38" t="b">
         <f t="shared" ref="AF42" si="174">IF(AND($V42=FALSE,AE42&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG42" s="20" t="b">
+      <c r="AG42" s="38" t="b">
         <f t="shared" ref="AG42" si="175">IF(AND($V42=FALSE,AE42&gt;10/24),IF($AF42=TRUE,AE42&gt;(18/24),AE42&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH42" s="20" t="b">
+      <c r="AH42" s="38" t="b">
         <f t="shared" ref="AH42" si="176">IF(AND($V42=TRUE,AE42&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI42" s="20" t="b">
+      <c r="AI42" s="38" t="b">
         <f t="shared" ref="AI42" si="177">IF(AND($V42=TRUE,AE42&gt;10/24),IF($AH42=TRUE,AE42&gt;(18/24),AE42&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -4607,7 +4607,7 @@
     <row r="43" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A43" s="9" t="str">
         <f t="shared" ref="A43" si="178">IF(A42="","",TEXT(A42,"(aaa)"))</f>
-        <v>(月)</v>
+        <v>(水)</v>
       </c>
       <c r="B43" s="6">
         <f>IF(AND($A42&lt;&gt;"",$V42=FALSE),$Q$7,IF($V42=TRUE,"---",""))</f>
@@ -4617,25 +4617,25 @@
         <f>IF(AND(A42&lt;&gt;"",$V42=FALSE),IF(R43=0,"",IF(Q43&gt;$Q$2+U43,R43+1,R43)),IF($V42=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="36"/>
       <c r="P43" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q43" s="17">
         <f t="shared" si="4"/>
-        <v>45460</v>
+        <v>46190</v>
       </c>
       <c r="R43" s="8"/>
-      <c r="S43" s="29"/>
+      <c r="S43" s="33"/>
       <c r="U43" s="14">
         <v>16</v>
       </c>
@@ -4656,20 +4656,20 @@
         <f t="shared" ref="Z43" si="180">IF(V42=TRUE,IF(C42&lt;&gt;"",IF(C42&gt;(22/24),C42-(22/24),0),0),0) - IF(AI42,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA43" s="21"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="21"/>
-      <c r="AD43" s="21"/>
+      <c r="AA43" s="39"/>
+      <c r="AB43" s="39"/>
+      <c r="AC43" s="39"/>
+      <c r="AD43" s="39"/>
       <c r="AE43" s="18"/>
-      <c r="AF43" s="21"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="21"/>
+      <c r="AF43" s="39"/>
+      <c r="AG43" s="39"/>
+      <c r="AH43" s="39"/>
+      <c r="AI43" s="39"/>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A44" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U44,$Q$2+$U44,"")</f>
-        <v>45461</v>
+        <v>46191</v>
       </c>
       <c r="B44" s="6" t="str">
         <f>IF(A44&lt;&gt;"",IF(R44=0,"",R44),"")</f>
@@ -4679,43 +4679,43 @@
         <f>IF(AND($A44&lt;&gt;"",$V44=FALSE),$Q$6,IF(R45=0,"",IF(Q45&gt;$Q$2+U44,R45+1,R45)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="26">
         <f>SUM(W44:Z45)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="25" t="str">
+      <c r="E44" s="31" t="str">
         <f>IF(S44&lt;&gt;"",S44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="36">
         <f>IF(ROUNDUP(AA44*24,0)&gt;60,60,ROUNDUP(AA44*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G44" s="27" t="str">
+      <c r="G44" s="36" t="str">
         <f>IF(ROUNDUP(AA44*24,0)&gt;60,ROUNDUP(AA44*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="36">
         <f>IF(ROUNDUP(AB44*24,0)&gt;60,60,ROUNDUP(AB44*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I44" s="27" t="str">
+      <c r="I44" s="36" t="str">
         <f>IF(ROUNDUP(AB44*24,0)&gt;60,ROUNDUP(AB44*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J44" s="27">
+      <c r="J44" s="36">
         <f>IF(ROUNDUP(AC44*24,0)&gt;60,60,ROUNDUP(AC44*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K44" s="27" t="str">
+      <c r="K44" s="36" t="str">
         <f>IF(ROUNDUP(AC44*24,0)&gt;60,ROUNDUP(AC44*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L44" s="27">
+      <c r="L44" s="36">
         <f>IF(ROUNDUP(AD44*24,0)&gt;60,60,ROUNDUP(AD44*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M44" s="27" t="str">
+      <c r="M44" s="36" t="str">
         <f>IF(ROUNDUP(AD44*24,0)&gt;60,ROUNDUP(AD44*24,0)-60,"")</f>
         <v/>
       </c>
@@ -4724,10 +4724,10 @@
       </c>
       <c r="Q44" s="17">
         <f t="shared" si="4"/>
-        <v>45461</v>
+        <v>46191</v>
       </c>
       <c r="R44" s="8"/>
-      <c r="S44" s="29"/>
+      <c r="S44" s="33"/>
       <c r="U44" s="12">
         <v>17</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="13">
-        <f t="shared" ref="X44:X71" si="183">IF(V44=FALSE,
+        <f t="shared" ref="X44" si="183">IF(V44=FALSE,
   IF(B44&lt;&gt;"",
     IF(C44-B44&gt;0,
                   IF(B44&lt;(5/24),(5/24)-B44,0),0
@@ -4759,19 +4759,19 @@
         <f t="shared" ref="Z44" si="185">IF(V44=TRUE,IF(B44&lt;(5/24),(5/24)-B44,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA44" s="20">
+      <c r="AA44" s="38">
         <f>SUM(W44:W45,W10:W43)</f>
         <v>0</v>
       </c>
-      <c r="AB44" s="20">
+      <c r="AB44" s="38">
         <f>SUM(X44:X45,X10:X43)</f>
         <v>0</v>
       </c>
-      <c r="AC44" s="20">
+      <c r="AC44" s="38">
         <f>SUM(Y44:Y45,Y10:Y43)</f>
         <v>0</v>
       </c>
-      <c r="AD44" s="20">
+      <c r="AD44" s="38">
         <f>SUM(Z44:Z45,Z10:Z43)</f>
         <v>0</v>
       </c>
@@ -4779,19 +4779,19 @@
         <f>IF(OR(R44="",R45=""),IF(V44=FALSE,$Q$7-$Q$6-(1/24),0),IF(V44=FALSE,IF($C45&gt;$B45,$C45,$B45) - IF($B44&lt;$C44,$B44,$C44),$C44-$B44))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF44" s="20" t="b">
+      <c r="AF44" s="38" t="b">
         <f t="shared" ref="AF44" si="186">IF(AND($V44=FALSE,AE44&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG44" s="20" t="b">
+      <c r="AG44" s="38" t="b">
         <f t="shared" ref="AG44" si="187">IF(AND($V44=FALSE,AE44&gt;10/24),IF($AF44=TRUE,AE44&gt;(18/24),AE44&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH44" s="20" t="b">
+      <c r="AH44" s="38" t="b">
         <f t="shared" ref="AH44" si="188">IF(AND($V44=TRUE,AE44&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI44" s="20" t="b">
+      <c r="AI44" s="38" t="b">
         <f t="shared" ref="AI44" si="189">IF(AND($V44=TRUE,AE44&gt;10/24),IF($AH44=TRUE,AE44&gt;(18/24),AE44&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -4799,7 +4799,7 @@
     <row r="45" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A45" s="9" t="str">
         <f t="shared" ref="A45" si="190">IF(A44="","",TEXT(A44,"(aaa)"))</f>
-        <v>(火)</v>
+        <v>(木)</v>
       </c>
       <c r="B45" s="6">
         <f>IF(AND($A44&lt;&gt;"",$V44=FALSE),$Q$7,IF($V44=TRUE,"---",""))</f>
@@ -4809,25 +4809,25 @@
         <f>IF(AND(A44&lt;&gt;"",$V44=FALSE),IF(R45=0,"",IF(Q45&gt;$Q$2+U45,R45+1,R45)),IF($V44=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D45" s="33"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="36"/>
       <c r="P45" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q45" s="17">
         <f t="shared" si="4"/>
-        <v>45461</v>
+        <v>46191</v>
       </c>
       <c r="R45" s="8"/>
-      <c r="S45" s="29"/>
+      <c r="S45" s="33"/>
       <c r="U45" s="14">
         <v>17</v>
       </c>
@@ -4848,20 +4848,20 @@
         <f t="shared" ref="Z45" si="192">IF(V44=TRUE,IF(C44&lt;&gt;"",IF(C44&gt;(22/24),C44-(22/24),0),0),0) - IF(AI44,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA45" s="21"/>
-      <c r="AB45" s="21"/>
-      <c r="AC45" s="21"/>
-      <c r="AD45" s="21"/>
+      <c r="AA45" s="39"/>
+      <c r="AB45" s="39"/>
+      <c r="AC45" s="39"/>
+      <c r="AD45" s="39"/>
       <c r="AE45" s="18"/>
-      <c r="AF45" s="21"/>
-      <c r="AG45" s="21"/>
-      <c r="AH45" s="21"/>
-      <c r="AI45" s="21"/>
+      <c r="AF45" s="39"/>
+      <c r="AG45" s="39"/>
+      <c r="AH45" s="39"/>
+      <c r="AI45" s="39"/>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A46" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U46,$Q$2+$U46,"")</f>
-        <v>45462</v>
+        <v>46192</v>
       </c>
       <c r="B46" s="6" t="str">
         <f>IF(A46&lt;&gt;"",IF(R46=0,"",R46),"")</f>
@@ -4871,43 +4871,43 @@
         <f>IF(AND($A46&lt;&gt;"",$V46=FALSE),$Q$6,IF(R47=0,"",IF(Q47&gt;$Q$2+U46,R47+1,R47)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D46" s="32">
+      <c r="D46" s="26">
         <f>SUM(W46:Z47)</f>
         <v>0</v>
       </c>
-      <c r="E46" s="25" t="str">
+      <c r="E46" s="31" t="str">
         <f>IF(S46&lt;&gt;"",S46,"")</f>
         <v/>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="36">
         <f>IF(ROUNDUP(AA46*24,0)&gt;60,60,ROUNDUP(AA46*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G46" s="27" t="str">
+      <c r="G46" s="36" t="str">
         <f>IF(ROUNDUP(AA46*24,0)&gt;60,ROUNDUP(AA46*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="36">
         <f>IF(ROUNDUP(AB46*24,0)&gt;60,60,ROUNDUP(AB46*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I46" s="27" t="str">
+      <c r="I46" s="36" t="str">
         <f>IF(ROUNDUP(AB46*24,0)&gt;60,ROUNDUP(AB46*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J46" s="27">
+      <c r="J46" s="36">
         <f>IF(ROUNDUP(AC46*24,0)&gt;60,60,ROUNDUP(AC46*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K46" s="27" t="str">
+      <c r="K46" s="36" t="str">
         <f>IF(ROUNDUP(AC46*24,0)&gt;60,ROUNDUP(AC46*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L46" s="27">
+      <c r="L46" s="36">
         <f>IF(ROUNDUP(AD46*24,0)&gt;60,60,ROUNDUP(AD46*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M46" s="27" t="str">
+      <c r="M46" s="36" t="str">
         <f>IF(ROUNDUP(AD46*24,0)&gt;60,ROUNDUP(AD46*24,0)-60,"")</f>
         <v/>
       </c>
@@ -4916,10 +4916,10 @@
       </c>
       <c r="Q46" s="17">
         <f t="shared" si="4"/>
-        <v>45462</v>
+        <v>46192</v>
       </c>
       <c r="R46" s="8"/>
-      <c r="S46" s="29"/>
+      <c r="S46" s="33"/>
       <c r="U46" s="12">
         <v>18</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="X46" s="13">
-        <f t="shared" ref="X46:X71" si="195">IF(V46=FALSE,
+        <f t="shared" ref="X46" si="195">IF(V46=FALSE,
   IF(B46&lt;&gt;"",
     IF(C46-B46&gt;0,
                   IF(B46&lt;(5/24),(5/24)-B46,0),0
@@ -4951,19 +4951,19 @@
         <f t="shared" ref="Z46" si="197">IF(V46=TRUE,IF(B46&lt;(5/24),(5/24)-B46,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA46" s="20">
+      <c r="AA46" s="38">
         <f>SUM(W46:W47,W10:W45)</f>
         <v>0</v>
       </c>
-      <c r="AB46" s="20">
+      <c r="AB46" s="38">
         <f>SUM(X46:X47,X10:X45)</f>
         <v>0</v>
       </c>
-      <c r="AC46" s="20">
+      <c r="AC46" s="38">
         <f>SUM(Y46:Y47,Y10:Y45)</f>
         <v>0</v>
       </c>
-      <c r="AD46" s="20">
+      <c r="AD46" s="38">
         <f>SUM(Z46:Z47,Z10:Z45)</f>
         <v>0</v>
       </c>
@@ -4971,19 +4971,19 @@
         <f>IF(OR(R46="",R47=""),IF(V46=FALSE,$Q$7-$Q$6-(1/24),0),IF(V46=FALSE,IF($C47&gt;$B47,$C47,$B47) - IF($B46&lt;$C46,$B46,$C46),$C46-$B46))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF46" s="20" t="b">
+      <c r="AF46" s="38" t="b">
         <f t="shared" ref="AF46" si="198">IF(AND($V46=FALSE,AE46&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG46" s="20" t="b">
+      <c r="AG46" s="38" t="b">
         <f t="shared" ref="AG46" si="199">IF(AND($V46=FALSE,AE46&gt;10/24),IF($AF46=TRUE,AE46&gt;(18/24),AE46&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH46" s="20" t="b">
+      <c r="AH46" s="38" t="b">
         <f t="shared" ref="AH46" si="200">IF(AND($V46=TRUE,AE46&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI46" s="20" t="b">
+      <c r="AI46" s="38" t="b">
         <f t="shared" ref="AI46" si="201">IF(AND($V46=TRUE,AE46&gt;10/24),IF($AH46=TRUE,AE46&gt;(18/24),AE46&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -4991,7 +4991,7 @@
     <row r="47" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A47" s="9" t="str">
         <f t="shared" ref="A47" si="202">IF(A46="","",TEXT(A46,"(aaa)"))</f>
-        <v>(水)</v>
+        <v>(金)</v>
       </c>
       <c r="B47" s="6">
         <f>IF(AND($A46&lt;&gt;"",$V46=FALSE),$Q$7,IF($V46=TRUE,"---",""))</f>
@@ -5001,25 +5001,25 @@
         <f>IF(AND(A46&lt;&gt;"",$V46=FALSE),IF(R47=0,"",IF(Q47&gt;$Q$2+U47,R47+1,R47)),IF($V46=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D47" s="33"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
       <c r="P47" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q47" s="17">
         <f t="shared" si="4"/>
-        <v>45462</v>
+        <v>46192</v>
       </c>
       <c r="R47" s="8"/>
-      <c r="S47" s="29"/>
+      <c r="S47" s="33"/>
       <c r="U47" s="14">
         <v>18</v>
       </c>
@@ -5040,66 +5040,66 @@
         <f t="shared" ref="Z47" si="204">IF(V46=TRUE,IF(C46&lt;&gt;"",IF(C46&gt;(22/24),C46-(22/24),0),0),0) - IF(AI46,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA47" s="21"/>
-      <c r="AB47" s="21"/>
-      <c r="AC47" s="21"/>
-      <c r="AD47" s="21"/>
+      <c r="AA47" s="39"/>
+      <c r="AB47" s="39"/>
+      <c r="AC47" s="39"/>
+      <c r="AD47" s="39"/>
       <c r="AE47" s="18"/>
-      <c r="AF47" s="21"/>
-      <c r="AG47" s="21"/>
-      <c r="AH47" s="21"/>
-      <c r="AI47" s="21"/>
+      <c r="AF47" s="39"/>
+      <c r="AG47" s="39"/>
+      <c r="AH47" s="39"/>
+      <c r="AI47" s="39"/>
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A48" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U48,$Q$2+$U48,"")</f>
-        <v>45463</v>
+        <v>46193</v>
       </c>
       <c r="B48" s="6" t="str">
         <f>IF(A48&lt;&gt;"",IF(R48=0,"",R48),"")</f>
         <v/>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="6" t="str">
         <f>IF(AND($A48&lt;&gt;"",$V48=FALSE),$Q$6,IF(R49=0,"",IF(Q49&gt;$Q$2+U48,R49+1,R49)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D48" s="32">
+        <v/>
+      </c>
+      <c r="D48" s="26">
         <f>SUM(W48:Z49)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="25" t="str">
+      <c r="E48" s="31" t="str">
         <f>IF(S48&lt;&gt;"",S48,"")</f>
         <v/>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="36">
         <f>IF(ROUNDUP(AA48*24,0)&gt;60,60,ROUNDUP(AA48*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G48" s="27" t="str">
+      <c r="G48" s="36" t="str">
         <f>IF(ROUNDUP(AA48*24,0)&gt;60,ROUNDUP(AA48*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="36">
         <f>IF(ROUNDUP(AB48*24,0)&gt;60,60,ROUNDUP(AB48*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I48" s="27" t="str">
+      <c r="I48" s="36" t="str">
         <f>IF(ROUNDUP(AB48*24,0)&gt;60,ROUNDUP(AB48*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J48" s="27">
+      <c r="J48" s="36">
         <f>IF(ROUNDUP(AC48*24,0)&gt;60,60,ROUNDUP(AC48*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K48" s="27" t="str">
+      <c r="K48" s="36" t="str">
         <f>IF(ROUNDUP(AC48*24,0)&gt;60,ROUNDUP(AC48*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L48" s="27">
+      <c r="L48" s="36">
         <f>IF(ROUNDUP(AD48*24,0)&gt;60,60,ROUNDUP(AD48*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M48" s="27" t="str">
+      <c r="M48" s="36" t="str">
         <f>IF(ROUNDUP(AD48*24,0)&gt;60,ROUNDUP(AD48*24,0)-60,"")</f>
         <v/>
       </c>
@@ -5108,16 +5108,16 @@
       </c>
       <c r="Q48" s="17">
         <f t="shared" si="4"/>
-        <v>45463</v>
+        <v>46193</v>
       </c>
       <c r="R48" s="8"/>
-      <c r="S48" s="29"/>
+      <c r="S48" s="33"/>
       <c r="U48" s="12">
         <v>19</v>
       </c>
       <c r="V48" s="13" t="b">
         <f t="shared" ref="V48" si="205">IF(A48&lt;&gt;"",IF(OR(WEEKDAY(A48)=1,WEEKDAY(A48)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="13">
         <f t="shared" ref="W48" si="206">IF(V48=FALSE,
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="X48" s="13">
-        <f t="shared" ref="X48:X71" si="207">IF(V48=FALSE,
+        <f t="shared" ref="X48" si="207">IF(V48=FALSE,
   IF(B48&lt;&gt;"",
     IF(C48-B48&gt;0,
                   IF(B48&lt;(5/24),(5/24)-B48,0),0
@@ -5143,39 +5143,39 @@
         <f t="shared" ref="Z48" si="209">IF(V48=TRUE,IF(B48&lt;(5/24),(5/24)-B48,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA48" s="20">
+      <c r="AA48" s="38">
         <f>SUM(W48:W49,W10:W47)</f>
         <v>0</v>
       </c>
-      <c r="AB48" s="20">
+      <c r="AB48" s="38">
         <f>SUM(X48:X49,X10:X47)</f>
         <v>0</v>
       </c>
-      <c r="AC48" s="20">
+      <c r="AC48" s="38">
         <f>SUM(Y48:Y49,Y10:Y47)</f>
         <v>0</v>
       </c>
-      <c r="AD48" s="20">
+      <c r="AD48" s="38">
         <f>SUM(Z48:Z49,Z10:Z47)</f>
         <v>0</v>
       </c>
       <c r="AE48" s="19">
         <f>IF(OR(R48="",R49=""),IF(V48=FALSE,$Q$7-$Q$6-(1/24),0),IF(V48=FALSE,IF($C49&gt;$B49,$C49,$B49) - IF($B48&lt;$C48,$B48,$C48),$C48-$B48))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF48" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="38" t="b">
         <f t="shared" ref="AF48" si="210">IF(AND($V48=FALSE,AE48&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG48" s="20" t="b">
+      <c r="AG48" s="38" t="b">
         <f t="shared" ref="AG48" si="211">IF(AND($V48=FALSE,AE48&gt;10/24),IF($AF48=TRUE,AE48&gt;(18/24),AE48&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH48" s="20" t="b">
+      <c r="AH48" s="38" t="b">
         <f t="shared" ref="AH48" si="212">IF(AND($V48=TRUE,AE48&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI48" s="20" t="b">
+      <c r="AI48" s="38" t="b">
         <f t="shared" ref="AI48" si="213">IF(AND($V48=TRUE,AE48&gt;10/24),IF($AH48=TRUE,AE48&gt;(18/24),AE48&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -5183,35 +5183,35 @@
     <row r="49" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A49" s="9" t="str">
         <f t="shared" ref="A49" si="214">IF(A48="","",TEXT(A48,"(aaa)"))</f>
-        <v>(木)</v>
-      </c>
-      <c r="B49" s="6">
+        <v>(土)</v>
+      </c>
+      <c r="B49" s="6" t="str">
         <f>IF(AND($A48&lt;&gt;"",$V48=FALSE),$Q$7,IF($V48=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C49" s="6" t="str">
         <f>IF(AND(A48&lt;&gt;"",$V48=FALSE),IF(R49=0,"",IF(Q49&gt;$Q$2+U49,R49+1,R49)),IF($V48=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D49" s="33"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D49" s="27"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
       <c r="P49" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q49" s="17">
         <f t="shared" si="4"/>
-        <v>45463</v>
+        <v>46193</v>
       </c>
       <c r="R49" s="8"/>
-      <c r="S49" s="29"/>
+      <c r="S49" s="33"/>
       <c r="U49" s="14">
         <v>19</v>
       </c>
@@ -5232,66 +5232,66 @@
         <f t="shared" ref="Z49" si="216">IF(V48=TRUE,IF(C48&lt;&gt;"",IF(C48&gt;(22/24),C48-(22/24),0),0),0) - IF(AI48,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA49" s="21"/>
-      <c r="AB49" s="21"/>
-      <c r="AC49" s="21"/>
-      <c r="AD49" s="21"/>
+      <c r="AA49" s="39"/>
+      <c r="AB49" s="39"/>
+      <c r="AC49" s="39"/>
+      <c r="AD49" s="39"/>
       <c r="AE49" s="18"/>
-      <c r="AF49" s="21"/>
-      <c r="AG49" s="21"/>
-      <c r="AH49" s="21"/>
-      <c r="AI49" s="21"/>
+      <c r="AF49" s="39"/>
+      <c r="AG49" s="39"/>
+      <c r="AH49" s="39"/>
+      <c r="AI49" s="39"/>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A50" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U50,$Q$2+$U50,"")</f>
-        <v>45464</v>
+        <v>46194</v>
       </c>
       <c r="B50" s="6" t="str">
         <f>IF(A50&lt;&gt;"",IF(R50=0,"",R50),"")</f>
         <v/>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="6" t="str">
         <f>IF(AND($A50&lt;&gt;"",$V50=FALSE),$Q$6,IF(R51=0,"",IF(Q51&gt;$Q$2+U50,R51+1,R51)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D50" s="32">
+        <v/>
+      </c>
+      <c r="D50" s="26">
         <f>SUM(W50:Z51)</f>
         <v>0</v>
       </c>
-      <c r="E50" s="25" t="str">
+      <c r="E50" s="31" t="str">
         <f>IF(S50&lt;&gt;"",S50,"")</f>
         <v/>
       </c>
-      <c r="F50" s="27">
+      <c r="F50" s="36">
         <f>IF(ROUNDUP(AA50*24,0)&gt;60,60,ROUNDUP(AA50*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G50" s="27" t="str">
+      <c r="G50" s="36" t="str">
         <f>IF(ROUNDUP(AA50*24,0)&gt;60,ROUNDUP(AA50*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="36">
         <f>IF(ROUNDUP(AB50*24,0)&gt;60,60,ROUNDUP(AB50*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I50" s="27" t="str">
+      <c r="I50" s="36" t="str">
         <f>IF(ROUNDUP(AB50*24,0)&gt;60,ROUNDUP(AB50*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J50" s="27">
+      <c r="J50" s="36">
         <f>IF(ROUNDUP(AC50*24,0)&gt;60,60,ROUNDUP(AC50*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K50" s="27" t="str">
+      <c r="K50" s="36" t="str">
         <f>IF(ROUNDUP(AC50*24,0)&gt;60,ROUNDUP(AC50*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L50" s="27">
+      <c r="L50" s="36">
         <f>IF(ROUNDUP(AD50*24,0)&gt;60,60,ROUNDUP(AD50*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M50" s="27" t="str">
+      <c r="M50" s="36" t="str">
         <f>IF(ROUNDUP(AD50*24,0)&gt;60,ROUNDUP(AD50*24,0)-60,"")</f>
         <v/>
       </c>
@@ -5300,16 +5300,16 @@
       </c>
       <c r="Q50" s="17">
         <f t="shared" si="4"/>
-        <v>45464</v>
+        <v>46194</v>
       </c>
       <c r="R50" s="8"/>
-      <c r="S50" s="29"/>
+      <c r="S50" s="33"/>
       <c r="U50" s="12">
         <v>20</v>
       </c>
       <c r="V50" s="13" t="b">
         <f t="shared" ref="V50" si="217">IF(A50&lt;&gt;"",IF(OR(WEEKDAY(A50)=1,WEEKDAY(A50)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="13">
         <f t="shared" ref="W50" si="218">IF(V50=FALSE,
@@ -5319,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="13">
-        <f t="shared" ref="X50:X71" si="219">IF(V50=FALSE,
+        <f t="shared" ref="X50" si="219">IF(V50=FALSE,
   IF(B50&lt;&gt;"",
     IF(C50-B50&gt;0,
                   IF(B50&lt;(5/24),(5/24)-B50,0),0
@@ -5335,39 +5335,39 @@
         <f t="shared" ref="Z50" si="221">IF(V50=TRUE,IF(B50&lt;(5/24),(5/24)-B50,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA50" s="20">
+      <c r="AA50" s="38">
         <f>SUM(W50:W51,W10:W49)</f>
         <v>0</v>
       </c>
-      <c r="AB50" s="20">
+      <c r="AB50" s="38">
         <f>SUM(X50:X51,X10:X49)</f>
         <v>0</v>
       </c>
-      <c r="AC50" s="20">
+      <c r="AC50" s="38">
         <f>SUM(Y50:Y51,Y10:Y49)</f>
         <v>0</v>
       </c>
-      <c r="AD50" s="20">
+      <c r="AD50" s="38">
         <f>SUM(Z50:Z51,Z10:Z49)</f>
         <v>0</v>
       </c>
       <c r="AE50" s="19">
         <f>IF(OR(R50="",R51=""),IF(V50=FALSE,$Q$7-$Q$6-(1/24),0),IF(V50=FALSE,IF($C51&gt;$B51,$C51,$B51) - IF($B50&lt;$C50,$B50,$C50),$C50-$B50))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF50" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="38" t="b">
         <f t="shared" ref="AF50" si="222">IF(AND($V50=FALSE,AE50&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG50" s="20" t="b">
+      <c r="AG50" s="38" t="b">
         <f t="shared" ref="AG50" si="223">IF(AND($V50=FALSE,AE50&gt;10/24),IF($AF50=TRUE,AE50&gt;(18/24),AE50&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH50" s="20" t="b">
+      <c r="AH50" s="38" t="b">
         <f t="shared" ref="AH50" si="224">IF(AND($V50=TRUE,AE50&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI50" s="20" t="b">
+      <c r="AI50" s="38" t="b">
         <f t="shared" ref="AI50" si="225">IF(AND($V50=TRUE,AE50&gt;10/24),IF($AH50=TRUE,AE50&gt;(18/24),AE50&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -5375,35 +5375,35 @@
     <row r="51" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A51" s="9" t="str">
         <f t="shared" ref="A51" si="226">IF(A50="","",TEXT(A50,"(aaa)"))</f>
-        <v>(金)</v>
-      </c>
-      <c r="B51" s="6">
+        <v>(日)</v>
+      </c>
+      <c r="B51" s="6" t="str">
         <f>IF(AND($A50&lt;&gt;"",$V50=FALSE),$Q$7,IF($V50=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C51" s="6" t="str">
         <f>IF(AND(A50&lt;&gt;"",$V50=FALSE),IF(R51=0,"",IF(Q51&gt;$Q$2+U51,R51+1,R51)),IF($V50=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D51" s="33"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="27"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D51" s="27"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="36"/>
       <c r="P51" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q51" s="17">
         <f t="shared" si="4"/>
-        <v>45464</v>
+        <v>46194</v>
       </c>
       <c r="R51" s="8"/>
-      <c r="S51" s="29"/>
+      <c r="S51" s="33"/>
       <c r="U51" s="14">
         <v>20</v>
       </c>
@@ -5424,66 +5424,66 @@
         <f t="shared" ref="Z51" si="228">IF(V50=TRUE,IF(C50&lt;&gt;"",IF(C50&gt;(22/24),C50-(22/24),0),0),0) - IF(AI50,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA51" s="21"/>
-      <c r="AB51" s="21"/>
-      <c r="AC51" s="21"/>
-      <c r="AD51" s="21"/>
+      <c r="AA51" s="39"/>
+      <c r="AB51" s="39"/>
+      <c r="AC51" s="39"/>
+      <c r="AD51" s="39"/>
       <c r="AE51" s="18"/>
-      <c r="AF51" s="21"/>
-      <c r="AG51" s="21"/>
-      <c r="AH51" s="21"/>
-      <c r="AI51" s="21"/>
+      <c r="AF51" s="39"/>
+      <c r="AG51" s="39"/>
+      <c r="AH51" s="39"/>
+      <c r="AI51" s="39"/>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A52" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U52,$Q$2+$U52,"")</f>
-        <v>45465</v>
+        <v>46195</v>
       </c>
       <c r="B52" s="6" t="str">
         <f>IF(A52&lt;&gt;"",IF(R52=0,"",R52),"")</f>
         <v/>
       </c>
-      <c r="C52" s="6" t="str">
+      <c r="C52" s="6">
         <f>IF(AND($A52&lt;&gt;"",$V52=FALSE),$Q$6,IF(R53=0,"",IF(Q53&gt;$Q$2+U52,R53+1,R53)))</f>
-        <v/>
-      </c>
-      <c r="D52" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D52" s="26">
         <f>SUM(W52:Z53)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="25" t="str">
+      <c r="E52" s="31" t="str">
         <f>IF(S52&lt;&gt;"",S52,"")</f>
         <v/>
       </c>
-      <c r="F52" s="27">
+      <c r="F52" s="36">
         <f>IF(ROUNDUP(AA52*24,0)&gt;60,60,ROUNDUP(AA52*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G52" s="27" t="str">
+      <c r="G52" s="36" t="str">
         <f>IF(ROUNDUP(AA52*24,0)&gt;60,ROUNDUP(AA52*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="36">
         <f>IF(ROUNDUP(AB52*24,0)&gt;60,60,ROUNDUP(AB52*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I52" s="27" t="str">
+      <c r="I52" s="36" t="str">
         <f>IF(ROUNDUP(AB52*24,0)&gt;60,ROUNDUP(AB52*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J52" s="27">
+      <c r="J52" s="36">
         <f>IF(ROUNDUP(AC52*24,0)&gt;60,60,ROUNDUP(AC52*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K52" s="27" t="str">
+      <c r="K52" s="36" t="str">
         <f>IF(ROUNDUP(AC52*24,0)&gt;60,ROUNDUP(AC52*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L52" s="27">
+      <c r="L52" s="36">
         <f>IF(ROUNDUP(AD52*24,0)&gt;60,60,ROUNDUP(AD52*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M52" s="27" t="str">
+      <c r="M52" s="36" t="str">
         <f>IF(ROUNDUP(AD52*24,0)&gt;60,ROUNDUP(AD52*24,0)-60,"")</f>
         <v/>
       </c>
@@ -5492,16 +5492,16 @@
       </c>
       <c r="Q52" s="17">
         <f t="shared" si="4"/>
-        <v>45465</v>
+        <v>46195</v>
       </c>
       <c r="R52" s="8"/>
-      <c r="S52" s="29"/>
+      <c r="S52" s="33"/>
       <c r="U52" s="12">
         <v>21</v>
       </c>
       <c r="V52" s="13" t="b">
         <f t="shared" ref="V52" si="229">IF(A52&lt;&gt;"",IF(OR(WEEKDAY(A52)=1,WEEKDAY(A52)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="13">
         <f t="shared" ref="W52" si="230">IF(V52=FALSE,
@@ -5511,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="X52" s="13">
-        <f t="shared" ref="X52:X71" si="231">IF(V52=FALSE,
+        <f t="shared" ref="X52" si="231">IF(V52=FALSE,
   IF(B52&lt;&gt;"",
     IF(C52-B52&gt;0,
                   IF(B52&lt;(5/24),(5/24)-B52,0),0
@@ -5527,39 +5527,39 @@
         <f t="shared" ref="Z52" si="233">IF(V52=TRUE,IF(B52&lt;(5/24),(5/24)-B52,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA52" s="20">
+      <c r="AA52" s="38">
         <f>SUM(W52:W53,W10:W51)</f>
         <v>0</v>
       </c>
-      <c r="AB52" s="20">
+      <c r="AB52" s="38">
         <f>SUM(X52:X53,X10:X51)</f>
         <v>0</v>
       </c>
-      <c r="AC52" s="20">
+      <c r="AC52" s="38">
         <f>SUM(Y52:Y53,Y10:Y51)</f>
         <v>0</v>
       </c>
-      <c r="AD52" s="20">
+      <c r="AD52" s="38">
         <f>SUM(Z52:Z53,Z10:Z51)</f>
         <v>0</v>
       </c>
       <c r="AE52" s="19">
         <f>IF(OR(R52="",R53=""),IF(V52=FALSE,$Q$7-$Q$6-(1/24),0),IF(V52=FALSE,IF($C53&gt;$B53,$C53,$B53) - IF($B52&lt;$C52,$B52,$C52),$C52-$B52))</f>
-        <v>0</v>
-      </c>
-      <c r="AF52" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF52" s="38" t="b">
         <f t="shared" ref="AF52" si="234">IF(AND($V52=FALSE,AE52&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG52" s="20" t="b">
+      <c r="AG52" s="38" t="b">
         <f t="shared" ref="AG52" si="235">IF(AND($V52=FALSE,AE52&gt;10/24),IF($AF52=TRUE,AE52&gt;(18/24),AE52&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH52" s="20" t="b">
+      <c r="AH52" s="38" t="b">
         <f t="shared" ref="AH52" si="236">IF(AND($V52=TRUE,AE52&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI52" s="20" t="b">
+      <c r="AI52" s="38" t="b">
         <f t="shared" ref="AI52" si="237">IF(AND($V52=TRUE,AE52&gt;10/24),IF($AH52=TRUE,AE52&gt;(18/24),AE52&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -5567,35 +5567,35 @@
     <row r="53" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A53" s="9" t="str">
         <f t="shared" ref="A53" si="238">IF(A52="","",TEXT(A52,"(aaa)"))</f>
-        <v>(土)</v>
-      </c>
-      <c r="B53" s="6" t="str">
+        <v>(月)</v>
+      </c>
+      <c r="B53" s="6">
         <f>IF(AND($A52&lt;&gt;"",$V52=FALSE),$Q$7,IF($V52=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C53" s="6" t="str">
         <f>IF(AND(A52&lt;&gt;"",$V52=FALSE),IF(R53=0,"",IF(Q53&gt;$Q$2+U53,R53+1,R53)),IF($V52=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D53" s="33"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
+        <v/>
+      </c>
+      <c r="D53" s="27"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
       <c r="P53" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q53" s="17">
         <f t="shared" si="4"/>
-        <v>45465</v>
+        <v>46195</v>
       </c>
       <c r="R53" s="8"/>
-      <c r="S53" s="29"/>
+      <c r="S53" s="33"/>
       <c r="U53" s="14">
         <v>21</v>
       </c>
@@ -5616,66 +5616,66 @@
         <f t="shared" ref="Z53" si="240">IF(V52=TRUE,IF(C52&lt;&gt;"",IF(C52&gt;(22/24),C52-(22/24),0),0),0) - IF(AI52,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA53" s="21"/>
-      <c r="AB53" s="21"/>
-      <c r="AC53" s="21"/>
-      <c r="AD53" s="21"/>
+      <c r="AA53" s="39"/>
+      <c r="AB53" s="39"/>
+      <c r="AC53" s="39"/>
+      <c r="AD53" s="39"/>
       <c r="AE53" s="18"/>
-      <c r="AF53" s="21"/>
-      <c r="AG53" s="21"/>
-      <c r="AH53" s="21"/>
-      <c r="AI53" s="21"/>
+      <c r="AF53" s="39"/>
+      <c r="AG53" s="39"/>
+      <c r="AH53" s="39"/>
+      <c r="AI53" s="39"/>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A54" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U54,$Q$2+$U54,"")</f>
-        <v>45466</v>
+        <v>46196</v>
       </c>
       <c r="B54" s="6" t="str">
         <f>IF(A54&lt;&gt;"",IF(R54=0,"",R54),"")</f>
         <v/>
       </c>
-      <c r="C54" s="6" t="str">
+      <c r="C54" s="6">
         <f>IF(AND($A54&lt;&gt;"",$V54=FALSE),$Q$6,IF(R55=0,"",IF(Q55&gt;$Q$2+U54,R55+1,R55)))</f>
-        <v/>
-      </c>
-      <c r="D54" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D54" s="26">
         <f>SUM(W54:Z55)</f>
         <v>0</v>
       </c>
-      <c r="E54" s="25" t="str">
+      <c r="E54" s="31" t="str">
         <f>IF(S54&lt;&gt;"",S54,"")</f>
         <v/>
       </c>
-      <c r="F54" s="27">
+      <c r="F54" s="36">
         <f>IF(ROUNDUP(AA54*24,0)&gt;60,60,ROUNDUP(AA54*24,0))</f>
         <v>0</v>
       </c>
-      <c r="G54" s="27" t="str">
+      <c r="G54" s="36" t="str">
         <f>IF(ROUNDUP(AA54*24,0)&gt;60,ROUNDUP(AA54*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H54" s="27">
+      <c r="H54" s="36">
         <f>IF(ROUNDUP(AB54*24,0)&gt;60,60,ROUNDUP(AB54*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I54" s="27" t="str">
+      <c r="I54" s="36" t="str">
         <f>IF(ROUNDUP(AB54*24,0)&gt;60,ROUNDUP(AB54*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J54" s="27">
+      <c r="J54" s="36">
         <f>IF(ROUNDUP(AC54*24,0)&gt;60,60,ROUNDUP(AC54*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K54" s="27" t="str">
+      <c r="K54" s="36" t="str">
         <f>IF(ROUNDUP(AC54*24,0)&gt;60,ROUNDUP(AC54*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L54" s="27">
+      <c r="L54" s="36">
         <f>IF(ROUNDUP(AD54*24,0)&gt;60,60,ROUNDUP(AD54*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M54" s="27" t="str">
+      <c r="M54" s="36" t="str">
         <f>IF(ROUNDUP(AD54*24,0)&gt;60,ROUNDUP(AD54*24,0)-60,"")</f>
         <v/>
       </c>
@@ -5684,16 +5684,16 @@
       </c>
       <c r="Q54" s="17">
         <f t="shared" si="4"/>
-        <v>45466</v>
+        <v>46196</v>
       </c>
       <c r="R54" s="8"/>
-      <c r="S54" s="29"/>
+      <c r="S54" s="33"/>
       <c r="U54" s="12">
         <v>22</v>
       </c>
       <c r="V54" s="13" t="b">
         <f t="shared" ref="V54" si="241">IF(A54&lt;&gt;"",IF(OR(WEEKDAY(A54)=1,WEEKDAY(A54)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="242">IF(V54=FALSE,
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
       <c r="X54" s="13">
-        <f t="shared" ref="X54:X71" si="243">IF(V54=FALSE,
+        <f t="shared" ref="X54" si="243">IF(V54=FALSE,
   IF(B54&lt;&gt;"",
     IF(C54-B54&gt;0,
                   IF(B54&lt;(5/24),(5/24)-B54,0),0
@@ -5719,39 +5719,39 @@
         <f t="shared" ref="Z54" si="245">IF(V54=TRUE,IF(B54&lt;(5/24),(5/24)-B54,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA54" s="20">
+      <c r="AA54" s="38">
         <f>SUM(W54:W55,W10:W53)</f>
         <v>0</v>
       </c>
-      <c r="AB54" s="20">
+      <c r="AB54" s="38">
         <f>SUM(X54:X55,X10:X53)</f>
         <v>0</v>
       </c>
-      <c r="AC54" s="20">
+      <c r="AC54" s="38">
         <f>SUM(Y54:Y55,Y10:Y53)</f>
         <v>0</v>
       </c>
-      <c r="AD54" s="20">
+      <c r="AD54" s="38">
         <f>SUM(Z54:Z55,Z10:Z53)</f>
         <v>0</v>
       </c>
       <c r="AE54" s="19">
         <f>IF(OR(R54="",R55=""),IF(V54=FALSE,$Q$7-$Q$6-(1/24),0),IF(V54=FALSE,IF($C55&gt;$B55,$C55,$B55) - IF($B54&lt;$C54,$B54,$C54),$C54-$B54))</f>
-        <v>0</v>
-      </c>
-      <c r="AF54" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF54" s="38" t="b">
         <f t="shared" ref="AF54" si="246">IF(AND($V54=FALSE,AE54&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG54" s="20" t="b">
+      <c r="AG54" s="38" t="b">
         <f t="shared" ref="AG54" si="247">IF(AND($V54=FALSE,AE54&gt;10/24),IF($AF54=TRUE,AE54&gt;(18/24),AE54&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH54" s="20" t="b">
+      <c r="AH54" s="38" t="b">
         <f t="shared" ref="AH54" si="248">IF(AND($V54=TRUE,AE54&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI54" s="20" t="b">
+      <c r="AI54" s="38" t="b">
         <f t="shared" ref="AI54" si="249">IF(AND($V54=TRUE,AE54&gt;10/24),IF($AH54=TRUE,AE54&gt;(18/24),AE54&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -5759,35 +5759,35 @@
     <row r="55" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A55" s="9" t="str">
         <f t="shared" ref="A55" si="250">IF(A54="","",TEXT(A54,"(aaa)"))</f>
-        <v>(日)</v>
-      </c>
-      <c r="B55" s="6" t="str">
+        <v>(火)</v>
+      </c>
+      <c r="B55" s="6">
         <f>IF(AND($A54&lt;&gt;"",$V54=FALSE),$Q$7,IF($V54=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C55" s="6" t="str">
         <f>IF(AND(A54&lt;&gt;"",$V54=FALSE),IF(R55=0,"",IF(Q55&gt;$Q$2+U55,R55+1,R55)),IF($V54=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D55" s="33"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
+        <v/>
+      </c>
+      <c r="D55" s="27"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="36"/>
       <c r="P55" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q55" s="17">
         <f t="shared" si="4"/>
-        <v>45466</v>
+        <v>46196</v>
       </c>
       <c r="R55" s="8"/>
-      <c r="S55" s="29"/>
+      <c r="S55" s="33"/>
       <c r="U55" s="14">
         <v>22</v>
       </c>
@@ -5808,20 +5808,20 @@
         <f t="shared" ref="Z55" si="252">IF(V54=TRUE,IF(C54&lt;&gt;"",IF(C54&gt;(22/24),C54-(22/24),0),0),0) - IF(AI54,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA55" s="21"/>
-      <c r="AB55" s="21"/>
-      <c r="AC55" s="21"/>
-      <c r="AD55" s="21"/>
+      <c r="AA55" s="39"/>
+      <c r="AB55" s="39"/>
+      <c r="AC55" s="39"/>
+      <c r="AD55" s="39"/>
       <c r="AE55" s="18"/>
-      <c r="AF55" s="21"/>
-      <c r="AG55" s="21"/>
-      <c r="AH55" s="21"/>
-      <c r="AI55" s="21"/>
+      <c r="AF55" s="39"/>
+      <c r="AG55" s="39"/>
+      <c r="AH55" s="39"/>
+      <c r="AI55" s="39"/>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A56" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U56,$Q$2+$U56,"")</f>
-        <v>45467</v>
+        <v>46197</v>
       </c>
       <c r="B56" s="6">
         <f>IF(A56&lt;&gt;"",IF(R56=0,"",R56),"")</f>
@@ -5831,43 +5831,43 @@
         <f>IF(AND($A56&lt;&gt;"",$V56=FALSE),$Q$6,IF(R57=0,"",IF(Q57&gt;$Q$2+U56,R57+1,R57)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="26">
         <f>SUM(W56:Z57)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="E56" s="25" t="str">
+      <c r="E56" s="31" t="str">
         <f>IF(S56&lt;&gt;"",S56,"")</f>
         <v/>
       </c>
-      <c r="F56" s="27">
+      <c r="F56" s="36">
         <f>IF(ROUNDUP(AA56*24,0)&gt;60,60,ROUNDUP(AA56*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G56" s="27" t="str">
+      <c r="G56" s="36" t="str">
         <f>IF(ROUNDUP(AA56*24,0)&gt;60,ROUNDUP(AA56*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H56" s="27">
+      <c r="H56" s="36">
         <f>IF(ROUNDUP(AB56*24,0)&gt;60,60,ROUNDUP(AB56*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I56" s="27" t="str">
+      <c r="I56" s="36" t="str">
         <f>IF(ROUNDUP(AB56*24,0)&gt;60,ROUNDUP(AB56*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J56" s="27">
+      <c r="J56" s="36">
         <f>IF(ROUNDUP(AC56*24,0)&gt;60,60,ROUNDUP(AC56*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K56" s="27" t="str">
+      <c r="K56" s="36" t="str">
         <f>IF(ROUNDUP(AC56*24,0)&gt;60,ROUNDUP(AC56*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L56" s="27">
+      <c r="L56" s="36">
         <f>IF(ROUNDUP(AD56*24,0)&gt;60,60,ROUNDUP(AD56*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M56" s="27" t="str">
+      <c r="M56" s="36" t="str">
         <f>IF(ROUNDUP(AD56*24,0)&gt;60,ROUNDUP(AD56*24,0)-60,"")</f>
         <v/>
       </c>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="Q56" s="17">
         <f t="shared" si="4"/>
-        <v>45467</v>
+        <v>46197</v>
       </c>
       <c r="R56" s="8">
         <v>0.87430555555555556</v>
       </c>
-      <c r="S56" s="29"/>
+      <c r="S56" s="33"/>
       <c r="U56" s="12">
         <v>23</v>
       </c>
@@ -5913,19 +5913,19 @@
         <f t="shared" ref="Z56" si="255">IF(V56=TRUE,IF(B56&lt;(5/24),(5/24)-B56,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA56" s="20">
+      <c r="AA56" s="38">
         <f>SUM(W56:W57,W10:W55)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB56" s="20">
+      <c r="AB56" s="38">
         <f>SUM(X56:X57,X10:X55)</f>
         <v>0</v>
       </c>
-      <c r="AC56" s="20">
+      <c r="AC56" s="38">
         <f>SUM(Y56:Y57,Y10:Y55)</f>
         <v>0</v>
       </c>
-      <c r="AD56" s="20">
+      <c r="AD56" s="38">
         <f>SUM(Z56:Z57,Z10:Z55)</f>
         <v>0</v>
       </c>
@@ -5933,19 +5933,19 @@
         <f>IF(OR(R56="",R57=""),IF(V56=FALSE,$Q$7-$Q$6-(1/24),0),IF(V56=FALSE,IF($C57&gt;$B57,$C57,$B57) - IF($B56&lt;$C56,$B56,$C56),$C56-$B56))</f>
         <v>0.58263888888888893</v>
       </c>
-      <c r="AF56" s="20" t="b">
+      <c r="AF56" s="38" t="b">
         <f t="shared" ref="AF56" si="256">IF(AND($V56=FALSE,AE56&gt;(10/24)),TRUE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="AG56" s="20" t="b">
+      <c r="AG56" s="38" t="b">
         <f t="shared" ref="AG56" si="257">IF(AND($V56=FALSE,AE56&gt;10/24),IF($AF56=TRUE,AE56&gt;(18/24),AE56&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH56" s="20" t="b">
+      <c r="AH56" s="38" t="b">
         <f t="shared" ref="AH56" si="258">IF(AND($V56=TRUE,AE56&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI56" s="20" t="b">
+      <c r="AI56" s="38" t="b">
         <f t="shared" ref="AI56" si="259">IF(AND($V56=TRUE,AE56&gt;10/24),IF($AH56=TRUE,AE56&gt;(18/24),AE56&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -5953,7 +5953,7 @@
     <row r="57" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A57" s="9" t="str">
         <f t="shared" ref="A57" si="260">IF(A56="","",TEXT(A56,"(aaa)"))</f>
-        <v>(月)</v>
+        <v>(水)</v>
       </c>
       <c r="B57" s="6">
         <f>IF(AND($A56&lt;&gt;"",$V56=FALSE),$Q$7,IF($V56=TRUE,"---",""))</f>
@@ -5963,37 +5963,37 @@
         <f>IF(AND(A56&lt;&gt;"",$V56=FALSE),IF(R57=0,"",IF(Q57&gt;$Q$2+U57,R57+1,R57)),IF($V56=TRUE,"---",""))</f>
         <v>0.91597222222222219</v>
       </c>
-      <c r="D57" s="33"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="36"/>
+      <c r="L57" s="36"/>
+      <c r="M57" s="36"/>
       <c r="P57" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q57" s="17">
         <f t="shared" si="4"/>
-        <v>45467</v>
+        <v>46197</v>
       </c>
       <c r="R57" s="8">
         <v>0.91597222222222219</v>
       </c>
-      <c r="S57" s="29"/>
+      <c r="S57" s="33"/>
       <c r="U57" s="14">
         <v>23</v>
       </c>
       <c r="V57" s="15"/>
       <c r="W57" s="15">
-        <f t="shared" ref="W57:W71" si="261">IF(V56=FALSE,IF(C57&lt;&gt;"",IF(C57&gt;(22/24),(22/24)-B57,C57-B57),0),0) - IF(AF56,(1/24),0)</f>
+        <f t="shared" ref="W57" si="261">IF(V56=FALSE,IF(C57&lt;&gt;"",IF(C57&gt;(22/24),(22/24)-B57,C57-B57),0),0) - IF(AF56,(1/24),0)</f>
         <v>0.1763888888888889</v>
       </c>
       <c r="X57" s="15">
-        <f t="shared" ref="X57:X71" si="262">IF(V56=FALSE,IF(C57&lt;&gt;"",IF(C57&gt;(22/24),C57-(22/24),0),0),0) - IF(AG56,(1/24),0)</f>
+        <f t="shared" ref="X57" si="262">IF(V56=FALSE,IF(C57&lt;&gt;"",IF(C57&gt;(22/24),C57-(22/24),0),0),0) - IF(AG56,(1/24),0)</f>
         <v>0</v>
       </c>
       <c r="Y57" s="15">
@@ -6004,20 +6004,20 @@
         <f t="shared" ref="Z57" si="264">IF(V56=TRUE,IF(C56&lt;&gt;"",IF(C56&gt;(22/24),C56-(22/24),0),0),0) - IF(AI56,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA57" s="21"/>
-      <c r="AB57" s="21"/>
-      <c r="AC57" s="21"/>
-      <c r="AD57" s="21"/>
+      <c r="AA57" s="39"/>
+      <c r="AB57" s="39"/>
+      <c r="AC57" s="39"/>
+      <c r="AD57" s="39"/>
       <c r="AE57" s="18"/>
-      <c r="AF57" s="21"/>
-      <c r="AG57" s="21"/>
-      <c r="AH57" s="21"/>
-      <c r="AI57" s="21"/>
+      <c r="AF57" s="39"/>
+      <c r="AG57" s="39"/>
+      <c r="AH57" s="39"/>
+      <c r="AI57" s="39"/>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A58" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U58,$Q$2+$U58,"")</f>
-        <v>45468</v>
+        <v>46198</v>
       </c>
       <c r="B58" s="6" t="str">
         <f>IF(A58&lt;&gt;"",IF(R58=0,"",R58),"")</f>
@@ -6027,43 +6027,43 @@
         <f>IF(AND($A58&lt;&gt;"",$V58=FALSE),$Q$6,IF(R59=0,"",IF(Q59&gt;$Q$2+U58,R59+1,R59)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="26">
         <f>SUM(W58:Z59)</f>
         <v>0</v>
       </c>
-      <c r="E58" s="25" t="str">
+      <c r="E58" s="31" t="str">
         <f>IF(S58&lt;&gt;"",S58,"")</f>
         <v/>
       </c>
-      <c r="F58" s="27">
+      <c r="F58" s="36">
         <f>IF(ROUNDUP(AA58*24,0)&gt;60,60,ROUNDUP(AA58*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G58" s="27" t="str">
+      <c r="G58" s="36" t="str">
         <f>IF(ROUNDUP(AA58*24,0)&gt;60,ROUNDUP(AA58*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H58" s="27">
+      <c r="H58" s="36">
         <f>IF(ROUNDUP(AB58*24,0)&gt;60,60,ROUNDUP(AB58*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I58" s="27" t="str">
+      <c r="I58" s="36" t="str">
         <f>IF(ROUNDUP(AB58*24,0)&gt;60,ROUNDUP(AB58*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J58" s="27">
+      <c r="J58" s="36">
         <f>IF(ROUNDUP(AC58*24,0)&gt;60,60,ROUNDUP(AC58*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K58" s="27" t="str">
+      <c r="K58" s="36" t="str">
         <f>IF(ROUNDUP(AC58*24,0)&gt;60,ROUNDUP(AC58*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L58" s="27">
+      <c r="L58" s="36">
         <f>IF(ROUNDUP(AD58*24,0)&gt;60,60,ROUNDUP(AD58*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M58" s="27" t="str">
+      <c r="M58" s="36" t="str">
         <f>IF(ROUNDUP(AD58*24,0)&gt;60,ROUNDUP(AD58*24,0)-60,"")</f>
         <v/>
       </c>
@@ -6072,10 +6072,10 @@
       </c>
       <c r="Q58" s="17">
         <f t="shared" si="4"/>
-        <v>45468</v>
+        <v>46198</v>
       </c>
       <c r="R58" s="8"/>
-      <c r="S58" s="29"/>
+      <c r="S58" s="33"/>
       <c r="U58" s="12">
         <v>24</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="13">
-        <f t="shared" ref="X58:X71" si="267">IF(V58=FALSE,
+        <f t="shared" ref="X58" si="267">IF(V58=FALSE,
   IF(B58&lt;&gt;"",
     IF(C58-B58&gt;0,
                   IF(B58&lt;(5/24),(5/24)-B58,0),0
@@ -6107,19 +6107,19 @@
         <f t="shared" ref="Z58" si="269">IF(V58=TRUE,IF(B58&lt;(5/24),(5/24)-B58,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA58" s="20">
+      <c r="AA58" s="38">
         <f>SUM(W58:W59,W10:W57)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB58" s="20">
+      <c r="AB58" s="38">
         <f>SUM(X58:X59,X10:X57)</f>
         <v>0</v>
       </c>
-      <c r="AC58" s="20">
+      <c r="AC58" s="38">
         <f>SUM(Y58:Y59,Y10:Y57)</f>
         <v>0</v>
       </c>
-      <c r="AD58" s="20">
+      <c r="AD58" s="38">
         <f>SUM(Z58:Z59,Z10:Z57)</f>
         <v>0</v>
       </c>
@@ -6127,19 +6127,19 @@
         <f>IF(OR(R58="",R59=""),IF(V58=FALSE,$Q$7-$Q$6-(1/24),0),IF(V58=FALSE,IF($C59&gt;$B59,$C59,$B59) - IF($B58&lt;$C58,$B58,$C58),$C58-$B58))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF58" s="20" t="b">
+      <c r="AF58" s="38" t="b">
         <f t="shared" ref="AF58" si="270">IF(AND($V58=FALSE,AE58&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG58" s="20" t="b">
+      <c r="AG58" s="38" t="b">
         <f t="shared" ref="AG58" si="271">IF(AND($V58=FALSE,AE58&gt;10/24),IF($AF58=TRUE,AE58&gt;(18/24),AE58&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH58" s="20" t="b">
+      <c r="AH58" s="38" t="b">
         <f t="shared" ref="AH58" si="272">IF(AND($V58=TRUE,AE58&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI58" s="20" t="b">
+      <c r="AI58" s="38" t="b">
         <f t="shared" ref="AI58" si="273">IF(AND($V58=TRUE,AE58&gt;10/24),IF($AH58=TRUE,AE58&gt;(18/24),AE58&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -6147,7 +6147,7 @@
     <row r="59" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A59" s="9" t="str">
         <f t="shared" ref="A59" si="274">IF(A58="","",TEXT(A58,"(aaa)"))</f>
-        <v>(火)</v>
+        <v>(木)</v>
       </c>
       <c r="B59" s="6">
         <f>IF(AND($A58&lt;&gt;"",$V58=FALSE),$Q$7,IF($V58=TRUE,"---",""))</f>
@@ -6157,25 +6157,25 @@
         <f>IF(AND(A58&lt;&gt;"",$V58=FALSE),IF(R59=0,"",IF(Q59&gt;$Q$2+U59,R59+1,R59)),IF($V58=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D59" s="33"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
       <c r="P59" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q59" s="17">
         <f t="shared" si="4"/>
-        <v>45468</v>
+        <v>46198</v>
       </c>
       <c r="R59" s="8"/>
-      <c r="S59" s="29"/>
+      <c r="S59" s="33"/>
       <c r="U59" s="14">
         <v>24</v>
       </c>
@@ -6196,20 +6196,20 @@
         <f t="shared" ref="Z59" si="276">IF(V58=TRUE,IF(C58&lt;&gt;"",IF(C58&gt;(22/24),C58-(22/24),0),0),0) - IF(AI58,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA59" s="21"/>
-      <c r="AB59" s="21"/>
-      <c r="AC59" s="21"/>
-      <c r="AD59" s="21"/>
+      <c r="AA59" s="39"/>
+      <c r="AB59" s="39"/>
+      <c r="AC59" s="39"/>
+      <c r="AD59" s="39"/>
       <c r="AE59" s="18"/>
-      <c r="AF59" s="21"/>
-      <c r="AG59" s="21"/>
-      <c r="AH59" s="21"/>
-      <c r="AI59" s="21"/>
+      <c r="AF59" s="39"/>
+      <c r="AG59" s="39"/>
+      <c r="AH59" s="39"/>
+      <c r="AI59" s="39"/>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A60" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U60,$Q$2+$U60,"")</f>
-        <v>45469</v>
+        <v>46199</v>
       </c>
       <c r="B60" s="6" t="str">
         <f>IF(A60&lt;&gt;"",IF(R60=0,"",R60),"")</f>
@@ -6219,43 +6219,43 @@
         <f>IF(AND($A60&lt;&gt;"",$V60=FALSE),$Q$6,IF(R61=0,"",IF(Q61&gt;$Q$2+U60,R61+1,R61)))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="26">
         <f>SUM(W60:Z61)</f>
         <v>0</v>
       </c>
-      <c r="E60" s="25" t="str">
+      <c r="E60" s="31" t="str">
         <f>IF(S60&lt;&gt;"",S60,"")</f>
         <v/>
       </c>
-      <c r="F60" s="27">
+      <c r="F60" s="36">
         <f>IF(ROUNDUP(AA60*24,0)&gt;60,60,ROUNDUP(AA60*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G60" s="27" t="str">
+      <c r="G60" s="36" t="str">
         <f>IF(ROUNDUP(AA60*24,0)&gt;60,ROUNDUP(AA60*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H60" s="27">
+      <c r="H60" s="36">
         <f>IF(ROUNDUP(AB60*24,0)&gt;60,60,ROUNDUP(AB60*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I60" s="27" t="str">
+      <c r="I60" s="36" t="str">
         <f>IF(ROUNDUP(AB60*24,0)&gt;60,ROUNDUP(AB60*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J60" s="27">
+      <c r="J60" s="36">
         <f>IF(ROUNDUP(AC60*24,0)&gt;60,60,ROUNDUP(AC60*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K60" s="27" t="str">
+      <c r="K60" s="36" t="str">
         <f>IF(ROUNDUP(AC60*24,0)&gt;60,ROUNDUP(AC60*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L60" s="27">
+      <c r="L60" s="36">
         <f>IF(ROUNDUP(AD60*24,0)&gt;60,60,ROUNDUP(AD60*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M60" s="27" t="str">
+      <c r="M60" s="36" t="str">
         <f>IF(ROUNDUP(AD60*24,0)&gt;60,ROUNDUP(AD60*24,0)-60,"")</f>
         <v/>
       </c>
@@ -6264,10 +6264,10 @@
       </c>
       <c r="Q60" s="17">
         <f t="shared" si="4"/>
-        <v>45469</v>
+        <v>46199</v>
       </c>
       <c r="R60" s="8"/>
-      <c r="S60" s="29"/>
+      <c r="S60" s="33"/>
       <c r="U60" s="12">
         <v>25</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="13">
-        <f t="shared" ref="X60:X71" si="279">IF(V60=FALSE,
+        <f t="shared" ref="X60" si="279">IF(V60=FALSE,
   IF(B60&lt;&gt;"",
     IF(C60-B60&gt;0,
                   IF(B60&lt;(5/24),(5/24)-B60,0),0
@@ -6299,19 +6299,19 @@
         <f t="shared" ref="Z60" si="281">IF(V60=TRUE,IF(B60&lt;(5/24),(5/24)-B60,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA60" s="20">
+      <c r="AA60" s="38">
         <f>SUM(W60:W61,W10:W59)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB60" s="20">
+      <c r="AB60" s="38">
         <f>SUM(X60:X61,X10:X59)</f>
         <v>0</v>
       </c>
-      <c r="AC60" s="20">
+      <c r="AC60" s="38">
         <f>SUM(Y60:Y61,Y10:Y59)</f>
         <v>0</v>
       </c>
-      <c r="AD60" s="20">
+      <c r="AD60" s="38">
         <f>SUM(Z60:Z61,Z10:Z59)</f>
         <v>0</v>
       </c>
@@ -6319,19 +6319,19 @@
         <f>IF(OR(R60="",R61=""),IF(V60=FALSE,$Q$7-$Q$6-(1/24),0),IF(V60=FALSE,IF($C61&gt;$B61,$C61,$B61) - IF($B60&lt;$C60,$B60,$C60),$C60-$B60))</f>
         <v>0.32291666666666663</v>
       </c>
-      <c r="AF60" s="20" t="b">
+      <c r="AF60" s="38" t="b">
         <f t="shared" ref="AF60" si="282">IF(AND($V60=FALSE,AE60&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG60" s="20" t="b">
+      <c r="AG60" s="38" t="b">
         <f t="shared" ref="AG60" si="283">IF(AND($V60=FALSE,AE60&gt;10/24),IF($AF60=TRUE,AE60&gt;(18/24),AE60&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH60" s="20" t="b">
+      <c r="AH60" s="38" t="b">
         <f t="shared" ref="AH60" si="284">IF(AND($V60=TRUE,AE60&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI60" s="20" t="b">
+      <c r="AI60" s="38" t="b">
         <f t="shared" ref="AI60" si="285">IF(AND($V60=TRUE,AE60&gt;10/24),IF($AH60=TRUE,AE60&gt;(18/24),AE60&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -6339,7 +6339,7 @@
     <row r="61" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A61" s="9" t="str">
         <f t="shared" ref="A61" si="286">IF(A60="","",TEXT(A60,"(aaa)"))</f>
-        <v>(水)</v>
+        <v>(金)</v>
       </c>
       <c r="B61" s="6">
         <f>IF(AND($A60&lt;&gt;"",$V60=FALSE),$Q$7,IF($V60=TRUE,"---",""))</f>
@@ -6349,25 +6349,25 @@
         <f>IF(AND(A60&lt;&gt;"",$V60=FALSE),IF(R61=0,"",IF(Q61&gt;$Q$2+U61,R61+1,R61)),IF($V60=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D61" s="33"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="36"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="36"/>
+      <c r="K61" s="36"/>
+      <c r="L61" s="36"/>
+      <c r="M61" s="36"/>
       <c r="P61" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q61" s="17">
         <f t="shared" si="4"/>
-        <v>45469</v>
+        <v>46199</v>
       </c>
       <c r="R61" s="8"/>
-      <c r="S61" s="29"/>
+      <c r="S61" s="33"/>
       <c r="U61" s="14">
         <v>25</v>
       </c>
@@ -6388,66 +6388,66 @@
         <f t="shared" ref="Z61" si="288">IF(V60=TRUE,IF(C60&lt;&gt;"",IF(C60&gt;(22/24),C60-(22/24),0),0),0) - IF(AI60,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA61" s="21"/>
-      <c r="AB61" s="21"/>
-      <c r="AC61" s="21"/>
-      <c r="AD61" s="21"/>
+      <c r="AA61" s="39"/>
+      <c r="AB61" s="39"/>
+      <c r="AC61" s="39"/>
+      <c r="AD61" s="39"/>
       <c r="AE61" s="18"/>
-      <c r="AF61" s="21"/>
-      <c r="AG61" s="21"/>
-      <c r="AH61" s="21"/>
-      <c r="AI61" s="21"/>
+      <c r="AF61" s="39"/>
+      <c r="AG61" s="39"/>
+      <c r="AH61" s="39"/>
+      <c r="AI61" s="39"/>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A62" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U62,$Q$2+$U62,"")</f>
-        <v>45470</v>
+        <v>46200</v>
       </c>
       <c r="B62" s="6" t="str">
         <f>IF(A62&lt;&gt;"",IF(R62=0,"",R62),"")</f>
         <v/>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="6" t="str">
         <f>IF(AND($A62&lt;&gt;"",$V62=FALSE),$Q$6,IF(R63=0,"",IF(Q63&gt;$Q$2+U62,R63+1,R63)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D62" s="32">
+        <v/>
+      </c>
+      <c r="D62" s="26">
         <f>SUM(W62:Z63)</f>
         <v>0</v>
       </c>
-      <c r="E62" s="25" t="str">
+      <c r="E62" s="31" t="str">
         <f>IF(S62&lt;&gt;"",S62,"")</f>
         <v/>
       </c>
-      <c r="F62" s="27">
+      <c r="F62" s="36">
         <f>IF(ROUNDUP(AA62*24,0)&gt;60,60,ROUNDUP(AA62*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G62" s="27" t="str">
+      <c r="G62" s="36" t="str">
         <f>IF(ROUNDUP(AA62*24,0)&gt;60,ROUNDUP(AA62*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H62" s="27">
+      <c r="H62" s="36">
         <f>IF(ROUNDUP(AB62*24,0)&gt;60,60,ROUNDUP(AB62*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I62" s="27" t="str">
+      <c r="I62" s="36" t="str">
         <f>IF(ROUNDUP(AB62*24,0)&gt;60,ROUNDUP(AB62*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J62" s="27">
+      <c r="J62" s="36">
         <f>IF(ROUNDUP(AC62*24,0)&gt;60,60,ROUNDUP(AC62*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K62" s="27" t="str">
+      <c r="K62" s="36" t="str">
         <f>IF(ROUNDUP(AC62*24,0)&gt;60,ROUNDUP(AC62*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L62" s="27">
+      <c r="L62" s="36">
         <f>IF(ROUNDUP(AD62*24,0)&gt;60,60,ROUNDUP(AD62*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M62" s="27" t="str">
+      <c r="M62" s="36" t="str">
         <f>IF(ROUNDUP(AD62*24,0)&gt;60,ROUNDUP(AD62*24,0)-60,"")</f>
         <v/>
       </c>
@@ -6456,16 +6456,16 @@
       </c>
       <c r="Q62" s="17">
         <f t="shared" si="4"/>
-        <v>45470</v>
+        <v>46200</v>
       </c>
       <c r="R62" s="8"/>
-      <c r="S62" s="29"/>
+      <c r="S62" s="33"/>
       <c r="U62" s="12">
         <v>26</v>
       </c>
       <c r="V62" s="13" t="b">
         <f t="shared" ref="V62" si="289">IF(A62&lt;&gt;"",IF(OR(WEEKDAY(A62)=1,WEEKDAY(A62)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="13">
         <f t="shared" ref="W62" si="290">IF(V62=FALSE,
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="13">
-        <f t="shared" ref="X62:X71" si="291">IF(V62=FALSE,
+        <f t="shared" ref="X62" si="291">IF(V62=FALSE,
   IF(B62&lt;&gt;"",
     IF(C62-B62&gt;0,
                   IF(B62&lt;(5/24),(5/24)-B62,0),0
@@ -6491,39 +6491,39 @@
         <f t="shared" ref="Z62" si="293">IF(V62=TRUE,IF(B62&lt;(5/24),(5/24)-B62,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA62" s="20">
+      <c r="AA62" s="38">
         <f>SUM(W62:W63,W10:W61)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB62" s="20">
+      <c r="AB62" s="38">
         <f>SUM(X62:X63,X10:X61)</f>
         <v>0</v>
       </c>
-      <c r="AC62" s="20">
+      <c r="AC62" s="38">
         <f>SUM(Y62:Y63,Y10:Y61)</f>
         <v>0</v>
       </c>
-      <c r="AD62" s="20">
+      <c r="AD62" s="38">
         <f>SUM(Z62:Z63,Z10:Z61)</f>
         <v>0</v>
       </c>
       <c r="AE62" s="19">
         <f>IF(OR(R62="",R63=""),IF(V62=FALSE,$Q$7-$Q$6-(1/24),0),IF(V62=FALSE,IF($C63&gt;$B63,$C63,$B63) - IF($B62&lt;$C62,$B62,$C62),$C62-$B62))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF62" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="38" t="b">
         <f t="shared" ref="AF62" si="294">IF(AND($V62=FALSE,AE62&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG62" s="20" t="b">
+      <c r="AG62" s="38" t="b">
         <f t="shared" ref="AG62" si="295">IF(AND($V62=FALSE,AE62&gt;10/24),IF($AF62=TRUE,AE62&gt;(18/24),AE62&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH62" s="20" t="b">
+      <c r="AH62" s="38" t="b">
         <f t="shared" ref="AH62" si="296">IF(AND($V62=TRUE,AE62&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI62" s="20" t="b">
+      <c r="AI62" s="38" t="b">
         <f t="shared" ref="AI62" si="297">IF(AND($V62=TRUE,AE62&gt;10/24),IF($AH62=TRUE,AE62&gt;(18/24),AE62&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -6531,35 +6531,35 @@
     <row r="63" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A63" s="9" t="str">
         <f t="shared" ref="A63" si="298">IF(A62="","",TEXT(A62,"(aaa)"))</f>
-        <v>(木)</v>
-      </c>
-      <c r="B63" s="6">
+        <v>(土)</v>
+      </c>
+      <c r="B63" s="6" t="str">
         <f>IF(AND($A62&lt;&gt;"",$V62=FALSE),$Q$7,IF($V62=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C63" s="6" t="str">
         <f>IF(AND(A62&lt;&gt;"",$V62=FALSE),IF(R63=0,"",IF(Q63&gt;$Q$2+U63,R63+1,R63)),IF($V62=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D63" s="33"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D63" s="27"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="36"/>
+      <c r="J63" s="36"/>
+      <c r="K63" s="36"/>
+      <c r="L63" s="36"/>
+      <c r="M63" s="36"/>
       <c r="P63" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q63" s="17">
         <f t="shared" si="4"/>
-        <v>45470</v>
+        <v>46200</v>
       </c>
       <c r="R63" s="8"/>
-      <c r="S63" s="29"/>
+      <c r="S63" s="33"/>
       <c r="U63" s="14">
         <v>26</v>
       </c>
@@ -6580,66 +6580,66 @@
         <f t="shared" ref="Z63" si="300">IF(V62=TRUE,IF(C62&lt;&gt;"",IF(C62&gt;(22/24),C62-(22/24),0),0),0) - IF(AI62,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA63" s="21"/>
-      <c r="AB63" s="21"/>
-      <c r="AC63" s="21"/>
-      <c r="AD63" s="21"/>
+      <c r="AA63" s="39"/>
+      <c r="AB63" s="39"/>
+      <c r="AC63" s="39"/>
+      <c r="AD63" s="39"/>
       <c r="AE63" s="18"/>
-      <c r="AF63" s="21"/>
-      <c r="AG63" s="21"/>
-      <c r="AH63" s="21"/>
-      <c r="AI63" s="21"/>
+      <c r="AF63" s="39"/>
+      <c r="AG63" s="39"/>
+      <c r="AH63" s="39"/>
+      <c r="AI63" s="39"/>
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A64" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U64,$Q$2+$U64,"")</f>
-        <v>45471</v>
+        <v>46201</v>
       </c>
       <c r="B64" s="6" t="str">
         <f>IF(A64&lt;&gt;"",IF(R64=0,"",R64),"")</f>
         <v/>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="6" t="str">
         <f>IF(AND($A64&lt;&gt;"",$V64=FALSE),$Q$6,IF(R65=0,"",IF(Q65&gt;$Q$2+U64,R65+1,R65)))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D64" s="32">
+        <v/>
+      </c>
+      <c r="D64" s="26">
         <f>SUM(W64:Z65)</f>
         <v>0</v>
       </c>
-      <c r="E64" s="25" t="str">
+      <c r="E64" s="31" t="str">
         <f>IF(S64&lt;&gt;"",S64,"")</f>
         <v/>
       </c>
-      <c r="F64" s="27">
+      <c r="F64" s="36">
         <f>IF(ROUNDUP(AA64*24,0)&gt;60,60,ROUNDUP(AA64*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G64" s="27" t="str">
+      <c r="G64" s="36" t="str">
         <f>IF(ROUNDUP(AA64*24,0)&gt;60,ROUNDUP(AA64*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H64" s="27">
+      <c r="H64" s="36">
         <f>IF(ROUNDUP(AB64*24,0)&gt;60,60,ROUNDUP(AB64*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I64" s="27" t="str">
+      <c r="I64" s="36" t="str">
         <f>IF(ROUNDUP(AB64*24,0)&gt;60,ROUNDUP(AB64*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J64" s="27">
+      <c r="J64" s="36">
         <f>IF(ROUNDUP(AC64*24,0)&gt;60,60,ROUNDUP(AC64*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K64" s="27" t="str">
+      <c r="K64" s="36" t="str">
         <f>IF(ROUNDUP(AC64*24,0)&gt;60,ROUNDUP(AC64*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L64" s="27">
+      <c r="L64" s="36">
         <f>IF(ROUNDUP(AD64*24,0)&gt;60,60,ROUNDUP(AD64*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M64" s="27" t="str">
+      <c r="M64" s="36" t="str">
         <f>IF(ROUNDUP(AD64*24,0)&gt;60,ROUNDUP(AD64*24,0)-60,"")</f>
         <v/>
       </c>
@@ -6648,16 +6648,16 @@
       </c>
       <c r="Q64" s="17">
         <f t="shared" si="4"/>
-        <v>45471</v>
+        <v>46201</v>
       </c>
       <c r="R64" s="8"/>
-      <c r="S64" s="29"/>
+      <c r="S64" s="33"/>
       <c r="U64" s="12">
         <v>27</v>
       </c>
       <c r="V64" s="13" t="b">
         <f t="shared" ref="V64" si="301">IF(A64&lt;&gt;"",IF(OR(WEEKDAY(A64)=1,WEEKDAY(A64)=7),TRUE,FALSE),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="13">
         <f t="shared" ref="W64" si="302">IF(V64=FALSE,
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="X64" s="13">
-        <f t="shared" ref="X64:X71" si="303">IF(V64=FALSE,
+        <f t="shared" ref="X64" si="303">IF(V64=FALSE,
   IF(B64&lt;&gt;"",
     IF(C64-B64&gt;0,
                   IF(B64&lt;(5/24),(5/24)-B64,0),0
@@ -6683,39 +6683,39 @@
         <f t="shared" ref="Z64" si="305">IF(V64=TRUE,IF(B64&lt;(5/24),(5/24)-B64,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA64" s="20">
+      <c r="AA64" s="38">
         <f>SUM(W64:W65,W10:W63)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB64" s="20">
+      <c r="AB64" s="38">
         <f>SUM(X64:X65,X10:X63)</f>
         <v>0</v>
       </c>
-      <c r="AC64" s="20">
+      <c r="AC64" s="38">
         <f>SUM(Y64:Y65,Y10:Y63)</f>
         <v>0</v>
       </c>
-      <c r="AD64" s="20">
+      <c r="AD64" s="38">
         <f>SUM(Z64:Z65,Z10:Z63)</f>
         <v>0</v>
       </c>
       <c r="AE64" s="19">
         <f>IF(OR(R64="",R65=""),IF(V64=FALSE,$Q$7-$Q$6-(1/24),0),IF(V64=FALSE,IF($C65&gt;$B65,$C65,$B65) - IF($B64&lt;$C64,$B64,$C64),$C64-$B64))</f>
-        <v>0.32291666666666663</v>
-      </c>
-      <c r="AF64" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="38" t="b">
         <f t="shared" ref="AF64" si="306">IF(AND($V64=FALSE,AE64&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG64" s="20" t="b">
+      <c r="AG64" s="38" t="b">
         <f t="shared" ref="AG64" si="307">IF(AND($V64=FALSE,AE64&gt;10/24),IF($AF64=TRUE,AE64&gt;(18/24),AE64&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH64" s="20" t="b">
+      <c r="AH64" s="38" t="b">
         <f t="shared" ref="AH64" si="308">IF(AND($V64=TRUE,AE64&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI64" s="20" t="b">
+      <c r="AI64" s="38" t="b">
         <f t="shared" ref="AI64" si="309">IF(AND($V64=TRUE,AE64&gt;10/24),IF($AH64=TRUE,AE64&gt;(18/24),AE64&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -6723,35 +6723,35 @@
     <row r="65" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A65" s="9" t="str">
         <f t="shared" ref="A65" si="310">IF(A64="","",TEXT(A64,"(aaa)"))</f>
-        <v>(金)</v>
-      </c>
-      <c r="B65" s="6">
+        <v>(日)</v>
+      </c>
+      <c r="B65" s="6" t="str">
         <f>IF(AND($A64&lt;&gt;"",$V64=FALSE),$Q$7,IF($V64=TRUE,"---",""))</f>
-        <v>0.69791666666666663</v>
+        <v>---</v>
       </c>
       <c r="C65" s="6" t="str">
         <f>IF(AND(A64&lt;&gt;"",$V64=FALSE),IF(R65=0,"",IF(Q65&gt;$Q$2+U65,R65+1,R65)),IF($V64=TRUE,"---",""))</f>
-        <v/>
-      </c>
-      <c r="D65" s="33"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="27"/>
-      <c r="K65" s="27"/>
-      <c r="L65" s="27"/>
-      <c r="M65" s="27"/>
+        <v>---</v>
+      </c>
+      <c r="D65" s="27"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="36"/>
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
       <c r="P65" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q65" s="17">
         <f t="shared" si="4"/>
-        <v>45471</v>
+        <v>46201</v>
       </c>
       <c r="R65" s="8"/>
-      <c r="S65" s="29"/>
+      <c r="S65" s="33"/>
       <c r="U65" s="14">
         <v>27</v>
       </c>
@@ -6772,66 +6772,66 @@
         <f t="shared" ref="Z65" si="312">IF(V64=TRUE,IF(C64&lt;&gt;"",IF(C64&gt;(22/24),C64-(22/24),0),0),0) - IF(AI64,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA65" s="21"/>
-      <c r="AB65" s="21"/>
-      <c r="AC65" s="21"/>
-      <c r="AD65" s="21"/>
+      <c r="AA65" s="39"/>
+      <c r="AB65" s="39"/>
+      <c r="AC65" s="39"/>
+      <c r="AD65" s="39"/>
       <c r="AE65" s="18"/>
-      <c r="AF65" s="21"/>
-      <c r="AG65" s="21"/>
-      <c r="AH65" s="21"/>
-      <c r="AI65" s="21"/>
+      <c r="AF65" s="39"/>
+      <c r="AG65" s="39"/>
+      <c r="AH65" s="39"/>
+      <c r="AI65" s="39"/>
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A66" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U66,$Q$2+$U66,"")</f>
-        <v>45472</v>
+        <v>46202</v>
       </c>
       <c r="B66" s="6" t="str">
         <f>IF(A66&lt;&gt;"",IF(R66=0,"",R66),"")</f>
         <v/>
       </c>
-      <c r="C66" s="6" t="str">
+      <c r="C66" s="6">
         <f>IF(AND($A66&lt;&gt;"",$V66=FALSE),$Q$6,IF(R67=0,"",IF(Q67&gt;$Q$2+U66,R67+1,R67)))</f>
-        <v/>
-      </c>
-      <c r="D66" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D66" s="26">
         <f>SUM(W66:Z67)</f>
         <v>0</v>
       </c>
-      <c r="E66" s="25" t="str">
+      <c r="E66" s="31" t="str">
         <f>IF(S66&lt;&gt;"",S66,"")</f>
         <v/>
       </c>
-      <c r="F66" s="27">
+      <c r="F66" s="36">
         <f>IF(ROUNDUP(AA66*24,0)&gt;60,60,ROUNDUP(AA66*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G66" s="27" t="str">
+      <c r="G66" s="36" t="str">
         <f>IF(ROUNDUP(AA66*24,0)&gt;60,ROUNDUP(AA66*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H66" s="27">
+      <c r="H66" s="36">
         <f>IF(ROUNDUP(AB66*24,0)&gt;60,60,ROUNDUP(AB66*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I66" s="27" t="str">
+      <c r="I66" s="36" t="str">
         <f>IF(ROUNDUP(AB66*24,0)&gt;60,ROUNDUP(AB66*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J66" s="27">
+      <c r="J66" s="36">
         <f>IF(ROUNDUP(AC66*24,0)&gt;60,60,ROUNDUP(AC66*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K66" s="27" t="str">
+      <c r="K66" s="36" t="str">
         <f>IF(ROUNDUP(AC66*24,0)&gt;60,ROUNDUP(AC66*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L66" s="27">
+      <c r="L66" s="36">
         <f>IF(ROUNDUP(AD66*24,0)&gt;60,60,ROUNDUP(AD66*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M66" s="27" t="str">
+      <c r="M66" s="36" t="str">
         <f>IF(ROUNDUP(AD66*24,0)&gt;60,ROUNDUP(AD66*24,0)-60,"")</f>
         <v/>
       </c>
@@ -6840,16 +6840,16 @@
       </c>
       <c r="Q66" s="17">
         <f t="shared" si="4"/>
-        <v>45472</v>
+        <v>46202</v>
       </c>
       <c r="R66" s="8"/>
-      <c r="S66" s="29"/>
+      <c r="S66" s="33"/>
       <c r="U66" s="12">
         <v>28</v>
       </c>
       <c r="V66" s="13" t="b">
         <f t="shared" ref="V66" si="313">IF(A66&lt;&gt;"",IF(OR(WEEKDAY(A66)=1,WEEKDAY(A66)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W66" s="13">
         <f t="shared" ref="W66" si="314">IF(V66=FALSE,
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="13">
-        <f t="shared" ref="X66:X71" si="315">IF(V66=FALSE,
+        <f t="shared" ref="X66" si="315">IF(V66=FALSE,
   IF(B66&lt;&gt;"",
     IF(C66-B66&gt;0,
                   IF(B66&lt;(5/24),(5/24)-B66,0),0
@@ -6875,39 +6875,39 @@
         <f t="shared" ref="Z66" si="317">IF(V66=TRUE,IF(B66&lt;(5/24),(5/24)-B66,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA66" s="20">
+      <c r="AA66" s="38">
         <f>SUM(W66:W67,W10:W65)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB66" s="20">
+      <c r="AB66" s="38">
         <f>SUM(X66:X67,X10:X65)</f>
         <v>0</v>
       </c>
-      <c r="AC66" s="20">
+      <c r="AC66" s="38">
         <f>SUM(Y66:Y67,Y10:Y65)</f>
         <v>0</v>
       </c>
-      <c r="AD66" s="20">
+      <c r="AD66" s="38">
         <f>SUM(Z66:Z67,Z10:Z65)</f>
         <v>0</v>
       </c>
       <c r="AE66" s="19">
         <f>IF(OR(R66="",R67=""),IF(V66=FALSE,$Q$7-$Q$6-(1/24),0),IF(V66=FALSE,IF($C67&gt;$B67,$C67,$B67) - IF($B66&lt;$C66,$B66,$C66),$C66-$B66))</f>
-        <v>0</v>
-      </c>
-      <c r="AF66" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF66" s="38" t="b">
         <f t="shared" ref="AF66" si="318">IF(AND($V66=FALSE,AE66&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG66" s="20" t="b">
+      <c r="AG66" s="38" t="b">
         <f t="shared" ref="AG66" si="319">IF(AND($V66=FALSE,AE66&gt;10/24),IF($AF66=TRUE,AE66&gt;(18/24),AE66&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH66" s="20" t="b">
+      <c r="AH66" s="38" t="b">
         <f t="shared" ref="AH66" si="320">IF(AND($V66=TRUE,AE66&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI66" s="20" t="b">
+      <c r="AI66" s="38" t="b">
         <f t="shared" ref="AI66" si="321">IF(AND($V66=TRUE,AE66&gt;10/24),IF($AH66=TRUE,AE66&gt;(18/24),AE66&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -6915,35 +6915,35 @@
     <row r="67" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A67" s="9" t="str">
         <f t="shared" ref="A67" si="322">IF(A66="","",TEXT(A66,"(aaa)"))</f>
-        <v>(土)</v>
-      </c>
-      <c r="B67" s="6" t="str">
+        <v>(月)</v>
+      </c>
+      <c r="B67" s="6">
         <f>IF(AND($A66&lt;&gt;"",$V66=FALSE),$Q$7,IF($V66=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C67" s="6" t="str">
         <f>IF(AND(A66&lt;&gt;"",$V66=FALSE),IF(R67=0,"",IF(Q67&gt;$Q$2+U67,R67+1,R67)),IF($V66=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D67" s="33"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
+        <v/>
+      </c>
+      <c r="D67" s="27"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="36"/>
+      <c r="K67" s="36"/>
+      <c r="L67" s="36"/>
+      <c r="M67" s="36"/>
       <c r="P67" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q67" s="17">
         <f t="shared" si="4"/>
-        <v>45472</v>
+        <v>46202</v>
       </c>
       <c r="R67" s="8"/>
-      <c r="S67" s="29"/>
+      <c r="S67" s="33"/>
       <c r="U67" s="14">
         <v>28</v>
       </c>
@@ -6964,66 +6964,66 @@
         <f t="shared" ref="Z67" si="324">IF(V66=TRUE,IF(C66&lt;&gt;"",IF(C66&gt;(22/24),C66-(22/24),0),0),0) - IF(AI66,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA67" s="21"/>
-      <c r="AB67" s="21"/>
-      <c r="AC67" s="21"/>
-      <c r="AD67" s="21"/>
+      <c r="AA67" s="39"/>
+      <c r="AB67" s="39"/>
+      <c r="AC67" s="39"/>
+      <c r="AD67" s="39"/>
       <c r="AE67" s="18"/>
-      <c r="AF67" s="21"/>
-      <c r="AG67" s="21"/>
-      <c r="AH67" s="21"/>
-      <c r="AI67" s="21"/>
+      <c r="AF67" s="39"/>
+      <c r="AG67" s="39"/>
+      <c r="AH67" s="39"/>
+      <c r="AI67" s="39"/>
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A68" s="5">
         <f>IF((EOMONTH($Q$2,0)-$Q$2)&gt;=$U68,$Q$2+$U68,"")</f>
-        <v>45473</v>
+        <v>46203</v>
       </c>
       <c r="B68" s="6" t="str">
         <f>IF(A68&lt;&gt;"",IF(R68=0,"",R68),"")</f>
         <v/>
       </c>
-      <c r="C68" s="6" t="str">
+      <c r="C68" s="6">
         <f>IF(AND($A68&lt;&gt;"",$V68=FALSE),$Q$6,IF(R69=0,"",IF(Q69&gt;$Q$2+U68,R69+1,R69)))</f>
-        <v/>
-      </c>
-      <c r="D68" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D68" s="26">
         <f>SUM(W68:Z69)</f>
         <v>0</v>
       </c>
-      <c r="E68" s="25" t="str">
+      <c r="E68" s="31" t="str">
         <f>IF(S68&lt;&gt;"",S68,"")</f>
         <v/>
       </c>
-      <c r="F68" s="27">
+      <c r="F68" s="36">
         <f>IF(ROUNDUP(AA68*24,0)&gt;60,60,ROUNDUP(AA68*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G68" s="27" t="str">
+      <c r="G68" s="36" t="str">
         <f>IF(ROUNDUP(AA68*24,0)&gt;60,ROUNDUP(AA68*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H68" s="27">
+      <c r="H68" s="36">
         <f>IF(ROUNDUP(AB68*24,0)&gt;60,60,ROUNDUP(AB68*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I68" s="27" t="str">
+      <c r="I68" s="36" t="str">
         <f>IF(ROUNDUP(AB68*24,0)&gt;60,ROUNDUP(AB68*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J68" s="27">
+      <c r="J68" s="36">
         <f>IF(ROUNDUP(AC68*24,0)&gt;60,60,ROUNDUP(AC68*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K68" s="27" t="str">
+      <c r="K68" s="36" t="str">
         <f>IF(ROUNDUP(AC68*24,0)&gt;60,ROUNDUP(AC68*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L68" s="27">
+      <c r="L68" s="36">
         <f>IF(ROUNDUP(AD68*24,0)&gt;60,60,ROUNDUP(AD68*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M68" s="27" t="str">
+      <c r="M68" s="36" t="str">
         <f>IF(ROUNDUP(AD68*24,0)&gt;60,ROUNDUP(AD68*24,0)-60,"")</f>
         <v/>
       </c>
@@ -7032,16 +7032,16 @@
       </c>
       <c r="Q68" s="17">
         <f t="shared" si="4"/>
-        <v>45473</v>
+        <v>46203</v>
       </c>
       <c r="R68" s="8"/>
-      <c r="S68" s="29"/>
+      <c r="S68" s="33"/>
       <c r="U68" s="12">
         <v>29</v>
       </c>
       <c r="V68" s="13" t="b">
         <f t="shared" ref="V68" si="325">IF(A68&lt;&gt;"",IF(OR(WEEKDAY(A68)=1,WEEKDAY(A68)=7),TRUE,FALSE),"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W68" s="13">
         <f t="shared" ref="W68" si="326">IF(V68=FALSE,
@@ -7051,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="X68" s="13">
-        <f t="shared" ref="X68:X71" si="327">IF(V68=FALSE,
+        <f t="shared" ref="X68" si="327">IF(V68=FALSE,
   IF(B68&lt;&gt;"",
     IF(C68-B68&gt;0,
                   IF(B68&lt;(5/24),(5/24)-B68,0),0
@@ -7067,39 +7067,39 @@
         <f t="shared" ref="Z68" si="329">IF(V68=TRUE,IF(B68&lt;(5/24),(5/24)-B68,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA68" s="20">
+      <c r="AA68" s="38">
         <f>SUM(W68:W69,W10:W67)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB68" s="20">
+      <c r="AB68" s="38">
         <f>SUM(X68:X69,X10:X67)</f>
         <v>0</v>
       </c>
-      <c r="AC68" s="20">
+      <c r="AC68" s="38">
         <f>SUM(Y68:Y69,Y10:Y67)</f>
         <v>0</v>
       </c>
-      <c r="AD68" s="20">
+      <c r="AD68" s="38">
         <f>SUM(Z68:Z69,Z10:Z67)</f>
         <v>0</v>
       </c>
       <c r="AE68" s="19">
         <f>IF(OR(R68="",R69=""),IF(V68=FALSE,$Q$7-$Q$6-(1/24),0),IF(V68=FALSE,IF($C69&gt;$B69,$C69,$B69) - IF($B68&lt;$C68,$B68,$C68),$C68-$B68))</f>
-        <v>0</v>
-      </c>
-      <c r="AF68" s="20" t="b">
+        <v>0.32291666666666663</v>
+      </c>
+      <c r="AF68" s="38" t="b">
         <f t="shared" ref="AF68" si="330">IF(AND($V68=FALSE,AE68&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG68" s="20" t="b">
+      <c r="AG68" s="38" t="b">
         <f t="shared" ref="AG68" si="331">IF(AND($V68=FALSE,AE68&gt;10/24),IF($AF68=TRUE,AE68&gt;(18/24),AE68&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH68" s="20" t="b">
+      <c r="AH68" s="38" t="b">
         <f t="shared" ref="AH68" si="332">IF(AND($V68=TRUE,AE68&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI68" s="20" t="b">
+      <c r="AI68" s="38" t="b">
         <f t="shared" ref="AI68" si="333">IF(AND($V68=TRUE,AE68&gt;10/24),IF($AH68=TRUE,AE68&gt;(18/24),AE68&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -7107,35 +7107,35 @@
     <row r="69" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A69" s="9" t="str">
         <f t="shared" ref="A69" si="334">IF(A68="","",TEXT(A68,"(aaa)"))</f>
-        <v>(日)</v>
-      </c>
-      <c r="B69" s="6" t="str">
+        <v>(火)</v>
+      </c>
+      <c r="B69" s="6">
         <f>IF(AND($A68&lt;&gt;"",$V68=FALSE),$Q$7,IF($V68=TRUE,"---",""))</f>
-        <v>---</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="C69" s="6" t="str">
         <f>IF(AND(A68&lt;&gt;"",$V68=FALSE),IF(R69=0,"",IF(Q69&gt;$Q$2+U69,R69+1,R69)),IF($V68=TRUE,"---",""))</f>
-        <v>---</v>
-      </c>
-      <c r="D69" s="33"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="27"/>
-      <c r="L69" s="27"/>
-      <c r="M69" s="27"/>
+        <v/>
+      </c>
+      <c r="D69" s="27"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36"/>
+      <c r="J69" s="36"/>
+      <c r="K69" s="36"/>
+      <c r="L69" s="36"/>
+      <c r="M69" s="36"/>
       <c r="P69" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q69" s="17">
         <f t="shared" si="4"/>
-        <v>45473</v>
+        <v>46203</v>
       </c>
       <c r="R69" s="8"/>
-      <c r="S69" s="29"/>
+      <c r="S69" s="33"/>
       <c r="U69" s="14">
         <v>29</v>
       </c>
@@ -7156,15 +7156,15 @@
         <f t="shared" ref="Z69" si="336">IF(V68=TRUE,IF(C68&lt;&gt;"",IF(C68&gt;(22/24),C68-(22/24),0),0),0) - IF(AI68,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA69" s="21"/>
-      <c r="AB69" s="21"/>
-      <c r="AC69" s="21"/>
-      <c r="AD69" s="21"/>
+      <c r="AA69" s="39"/>
+      <c r="AB69" s="39"/>
+      <c r="AC69" s="39"/>
+      <c r="AD69" s="39"/>
       <c r="AE69" s="18"/>
-      <c r="AF69" s="21"/>
-      <c r="AG69" s="21"/>
-      <c r="AH69" s="21"/>
-      <c r="AI69" s="21"/>
+      <c r="AF69" s="39"/>
+      <c r="AG69" s="39"/>
+      <c r="AH69" s="39"/>
+      <c r="AI69" s="39"/>
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A70" s="5" t="str">
@@ -7179,43 +7179,43 @@
         <f>IF(AND($A70&lt;&gt;"",$V70=FALSE),$Q$6,IF(R71=0,"",IF(Q71&gt;$Q$2+U70,R71+1,R71)))</f>
         <v/>
       </c>
-      <c r="D70" s="32">
+      <c r="D70" s="26">
         <f>SUM(W70:Z71)</f>
         <v>0</v>
       </c>
-      <c r="E70" s="25" t="str">
+      <c r="E70" s="31" t="str">
         <f>IF(S70&lt;&gt;"",S70,"")</f>
         <v/>
       </c>
-      <c r="F70" s="27">
+      <c r="F70" s="36">
         <f>IF(ROUNDUP(AA70*24,0)&gt;60,60,ROUNDUP(AA70*24,0))</f>
         <v>5</v>
       </c>
-      <c r="G70" s="27" t="str">
+      <c r="G70" s="36" t="str">
         <f>IF(ROUNDUP(AA70*24,0)&gt;60,ROUNDUP(AA70*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="H70" s="27">
+      <c r="H70" s="36">
         <f>IF(ROUNDUP(AB70*24,0)&gt;60,60,ROUNDUP(AB70*24,0))</f>
         <v>0</v>
       </c>
-      <c r="I70" s="27" t="str">
+      <c r="I70" s="36" t="str">
         <f>IF(ROUNDUP(AB70*24,0)&gt;60,ROUNDUP(AB70*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="J70" s="27">
+      <c r="J70" s="36">
         <f>IF(ROUNDUP(AC70*24,0)&gt;60,60,ROUNDUP(AC70*24,0))</f>
         <v>0</v>
       </c>
-      <c r="K70" s="27" t="str">
+      <c r="K70" s="36" t="str">
         <f>IF(ROUNDUP(AC70*24,0)&gt;60,ROUNDUP(AC70*24,0)-60,"")</f>
         <v/>
       </c>
-      <c r="L70" s="27">
+      <c r="L70" s="36">
         <f>IF(ROUNDUP(AD70*24,0)&gt;60,60,ROUNDUP(AD70*24,0))</f>
         <v>0</v>
       </c>
-      <c r="M70" s="27" t="str">
+      <c r="M70" s="36" t="str">
         <f>IF(ROUNDUP(AD70*24,0)&gt;60,ROUNDUP(AD70*24,0)-60,"")</f>
         <v/>
       </c>
@@ -7224,10 +7224,10 @@
       </c>
       <c r="Q70" s="17">
         <f t="shared" si="4"/>
-        <v>45474</v>
+        <v>46204</v>
       </c>
       <c r="R70" s="8"/>
-      <c r="S70" s="29"/>
+      <c r="S70" s="33"/>
       <c r="U70" s="12">
         <v>30</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="13">
-        <f t="shared" ref="X70:X71" si="339">IF(V70=FALSE,
+        <f t="shared" ref="X70" si="339">IF(V70=FALSE,
   IF(B70&lt;&gt;"",
     IF(C70-B70&gt;0,
                   IF(B70&lt;(5/24),(5/24)-B70,0),0
@@ -7259,19 +7259,19 @@
         <f t="shared" ref="Z70" si="341">IF(V70=TRUE,IF(B70&lt;(5/24),(5/24)-B70,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA70" s="20">
+      <c r="AA70" s="38">
         <f>SUM(W70:W71,W10:W69)</f>
         <v>0.1763888888888889</v>
       </c>
-      <c r="AB70" s="20">
+      <c r="AB70" s="38">
         <f>SUM(X70:X71,X10:X69)</f>
         <v>0</v>
       </c>
-      <c r="AC70" s="20">
+      <c r="AC70" s="38">
         <f>SUM(Y70:Y71,Y10:Y69)</f>
         <v>0</v>
       </c>
-      <c r="AD70" s="20">
+      <c r="AD70" s="38">
         <f>SUM(Z70:Z71,Z10:Z69)</f>
         <v>0</v>
       </c>
@@ -7279,19 +7279,19 @@
         <f>IF(OR(R70="",R71=""),IF(V70=FALSE,$Q$7-$Q$6-(1/24),0),IF(V70=FALSE,IF($C71&gt;$B71,$C71,$B71) - IF($B70&lt;$C70,$B70,$C70),$C70-$B70))</f>
         <v>0</v>
       </c>
-      <c r="AF70" s="20" t="b">
+      <c r="AF70" s="38" t="b">
         <f t="shared" ref="AF70" si="342">IF(AND($V70=FALSE,AE70&gt;(10/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AG70" s="20" t="b">
+      <c r="AG70" s="38" t="b">
         <f t="shared" ref="AG70" si="343">IF(AND($V70=FALSE,AE70&gt;10/24),IF($AF70=TRUE,AE70&gt;(18/24),AE70&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AH70" s="20" t="b">
+      <c r="AH70" s="38" t="b">
         <f t="shared" ref="AH70" si="344">IF(AND($V70=TRUE,AE70&gt;(7/24)),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AI70" s="20" t="b">
+      <c r="AI70" s="38" t="b">
         <f t="shared" ref="AI70" si="345">IF(AND($V70=TRUE,AE70&gt;10/24),IF($AH70=TRUE,AE70&gt;(18/24),AE70&gt;(10/24)),FALSE)</f>
         <v>0</v>
       </c>
@@ -7309,25 +7309,25 @@
         <f>IF(AND(A70&lt;&gt;"",$V70=FALSE),IF(R71=0,"",IF(Q71&gt;$Q$2+U71,R71+1,R71)),IF($V70=TRUE,"---",""))</f>
         <v/>
       </c>
-      <c r="D71" s="33"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="27"/>
-      <c r="K71" s="27"/>
-      <c r="L71" s="27"/>
-      <c r="M71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="36"/>
+      <c r="M71" s="36"/>
       <c r="P71" s="7" t="s">
         <v>46</v>
       </c>
       <c r="Q71" s="17">
         <f t="shared" si="4"/>
-        <v>45474</v>
+        <v>46204</v>
       </c>
       <c r="R71" s="8"/>
-      <c r="S71" s="29"/>
+      <c r="S71" s="33"/>
       <c r="U71" s="14">
         <v>30</v>
       </c>
@@ -7348,15 +7348,15 @@
         <f t="shared" ref="Z71" si="348">IF(V70=TRUE,IF(C70&lt;&gt;"",IF(C70&gt;(22/24),C70-(22/24),0),0),0) - IF(AI70,(1/24),0)</f>
         <v>0</v>
       </c>
-      <c r="AA71" s="21"/>
-      <c r="AB71" s="21"/>
-      <c r="AC71" s="21"/>
-      <c r="AD71" s="21"/>
+      <c r="AA71" s="39"/>
+      <c r="AB71" s="39"/>
+      <c r="AC71" s="39"/>
+      <c r="AD71" s="39"/>
       <c r="AE71" s="18"/>
-      <c r="AF71" s="21"/>
-      <c r="AG71" s="21"/>
-      <c r="AH71" s="21"/>
-      <c r="AI71" s="21"/>
+      <c r="AF71" s="39"/>
+      <c r="AG71" s="39"/>
+      <c r="AH71" s="39"/>
+      <c r="AI71" s="39"/>
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.45">
       <c r="AG72" s="16"/>
@@ -8015,6 +8015,591 @@
     </row>
   </sheetData>
   <mergeCells count="609">
+    <mergeCell ref="AF70:AF71"/>
+    <mergeCell ref="AG70:AG71"/>
+    <mergeCell ref="AH70:AH71"/>
+    <mergeCell ref="AI70:AI71"/>
+    <mergeCell ref="AF64:AF65"/>
+    <mergeCell ref="AG64:AG65"/>
+    <mergeCell ref="AH64:AH65"/>
+    <mergeCell ref="AI64:AI65"/>
+    <mergeCell ref="AF66:AF67"/>
+    <mergeCell ref="AG66:AG67"/>
+    <mergeCell ref="AH66:AH67"/>
+    <mergeCell ref="AI66:AI67"/>
+    <mergeCell ref="AF68:AF69"/>
+    <mergeCell ref="AG68:AG69"/>
+    <mergeCell ref="AH68:AH69"/>
+    <mergeCell ref="AI68:AI69"/>
+    <mergeCell ref="AF58:AF59"/>
+    <mergeCell ref="AG58:AG59"/>
+    <mergeCell ref="AH58:AH59"/>
+    <mergeCell ref="AI58:AI59"/>
+    <mergeCell ref="AF60:AF61"/>
+    <mergeCell ref="AG60:AG61"/>
+    <mergeCell ref="AH60:AH61"/>
+    <mergeCell ref="AI60:AI61"/>
+    <mergeCell ref="AF62:AF63"/>
+    <mergeCell ref="AG62:AG63"/>
+    <mergeCell ref="AH62:AH63"/>
+    <mergeCell ref="AI62:AI63"/>
+    <mergeCell ref="AF52:AF53"/>
+    <mergeCell ref="AG52:AG53"/>
+    <mergeCell ref="AH52:AH53"/>
+    <mergeCell ref="AI52:AI53"/>
+    <mergeCell ref="AF54:AF55"/>
+    <mergeCell ref="AG54:AG55"/>
+    <mergeCell ref="AH54:AH55"/>
+    <mergeCell ref="AI54:AI55"/>
+    <mergeCell ref="AF56:AF57"/>
+    <mergeCell ref="AG56:AG57"/>
+    <mergeCell ref="AH56:AH57"/>
+    <mergeCell ref="AI56:AI57"/>
+    <mergeCell ref="AF46:AF47"/>
+    <mergeCell ref="AG46:AG47"/>
+    <mergeCell ref="AH46:AH47"/>
+    <mergeCell ref="AI46:AI47"/>
+    <mergeCell ref="AF48:AF49"/>
+    <mergeCell ref="AG48:AG49"/>
+    <mergeCell ref="AH48:AH49"/>
+    <mergeCell ref="AI48:AI49"/>
+    <mergeCell ref="AF50:AF51"/>
+    <mergeCell ref="AG50:AG51"/>
+    <mergeCell ref="AH50:AH51"/>
+    <mergeCell ref="AI50:AI51"/>
+    <mergeCell ref="AF40:AF41"/>
+    <mergeCell ref="AG40:AG41"/>
+    <mergeCell ref="AH40:AH41"/>
+    <mergeCell ref="AI40:AI41"/>
+    <mergeCell ref="AF42:AF43"/>
+    <mergeCell ref="AG42:AG43"/>
+    <mergeCell ref="AH42:AH43"/>
+    <mergeCell ref="AI42:AI43"/>
+    <mergeCell ref="AF44:AF45"/>
+    <mergeCell ref="AG44:AG45"/>
+    <mergeCell ref="AH44:AH45"/>
+    <mergeCell ref="AI44:AI45"/>
+    <mergeCell ref="AF34:AF35"/>
+    <mergeCell ref="AG34:AG35"/>
+    <mergeCell ref="AH34:AH35"/>
+    <mergeCell ref="AI34:AI35"/>
+    <mergeCell ref="AF36:AF37"/>
+    <mergeCell ref="AG36:AG37"/>
+    <mergeCell ref="AH36:AH37"/>
+    <mergeCell ref="AI36:AI37"/>
+    <mergeCell ref="AF38:AF39"/>
+    <mergeCell ref="AG38:AG39"/>
+    <mergeCell ref="AH38:AH39"/>
+    <mergeCell ref="AI38:AI39"/>
+    <mergeCell ref="AF28:AF29"/>
+    <mergeCell ref="AG28:AG29"/>
+    <mergeCell ref="AH28:AH29"/>
+    <mergeCell ref="AI28:AI29"/>
+    <mergeCell ref="AF30:AF31"/>
+    <mergeCell ref="AG30:AG31"/>
+    <mergeCell ref="AH30:AH31"/>
+    <mergeCell ref="AI30:AI31"/>
+    <mergeCell ref="AF32:AF33"/>
+    <mergeCell ref="AG32:AG33"/>
+    <mergeCell ref="AH32:AH33"/>
+    <mergeCell ref="AI32:AI33"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="AH22:AH23"/>
+    <mergeCell ref="AI22:AI23"/>
+    <mergeCell ref="AF24:AF25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="AH24:AH25"/>
+    <mergeCell ref="AI24:AI25"/>
+    <mergeCell ref="AF26:AF27"/>
+    <mergeCell ref="AG26:AG27"/>
+    <mergeCell ref="AH26:AH27"/>
+    <mergeCell ref="AI26:AI27"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="AH16:AH17"/>
+    <mergeCell ref="AI16:AI17"/>
+    <mergeCell ref="AF18:AF19"/>
+    <mergeCell ref="AG18:AG19"/>
+    <mergeCell ref="AH18:AH19"/>
+    <mergeCell ref="AI18:AI19"/>
+    <mergeCell ref="AF20:AF21"/>
+    <mergeCell ref="AG20:AG21"/>
+    <mergeCell ref="AH20:AH21"/>
+    <mergeCell ref="AI20:AI21"/>
+    <mergeCell ref="AF10:AF11"/>
+    <mergeCell ref="AG10:AG11"/>
+    <mergeCell ref="AH10:AH11"/>
+    <mergeCell ref="AI10:AI11"/>
+    <mergeCell ref="AF12:AF13"/>
+    <mergeCell ref="AG12:AG13"/>
+    <mergeCell ref="AH12:AH13"/>
+    <mergeCell ref="AI12:AI13"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="AH14:AH15"/>
+    <mergeCell ref="AI14:AI15"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="F4:M4"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="AB10:AB11"/>
+    <mergeCell ref="AC10:AC11"/>
+    <mergeCell ref="AD10:AD11"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AB12:AB13"/>
+    <mergeCell ref="AC12:AC13"/>
+    <mergeCell ref="AD12:AD13"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="AB20:AB21"/>
+    <mergeCell ref="AC20:AC21"/>
+    <mergeCell ref="AD20:AD21"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="AB18:AB19"/>
+    <mergeCell ref="AC18:AC19"/>
+    <mergeCell ref="AD18:AD19"/>
+    <mergeCell ref="AA28:AA29"/>
+    <mergeCell ref="AB28:AB29"/>
+    <mergeCell ref="AC28:AC29"/>
+    <mergeCell ref="AD28:AD29"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="AB30:AB31"/>
+    <mergeCell ref="AC30:AC31"/>
+    <mergeCell ref="AD30:AD31"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AB26:AB27"/>
+    <mergeCell ref="AC26:AC27"/>
+    <mergeCell ref="AD26:AD27"/>
+    <mergeCell ref="AA36:AA37"/>
+    <mergeCell ref="AB36:AB37"/>
+    <mergeCell ref="AC36:AC37"/>
+    <mergeCell ref="AD36:AD37"/>
+    <mergeCell ref="AA38:AA39"/>
+    <mergeCell ref="AB38:AB39"/>
+    <mergeCell ref="AC38:AC39"/>
+    <mergeCell ref="AD38:AD39"/>
+    <mergeCell ref="AA32:AA33"/>
+    <mergeCell ref="AB32:AB33"/>
+    <mergeCell ref="AC32:AC33"/>
+    <mergeCell ref="AD32:AD33"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AB34:AB35"/>
+    <mergeCell ref="AC34:AC35"/>
+    <mergeCell ref="AD34:AD35"/>
+    <mergeCell ref="AA44:AA45"/>
+    <mergeCell ref="AB44:AB45"/>
+    <mergeCell ref="AC44:AC45"/>
+    <mergeCell ref="AD44:AD45"/>
+    <mergeCell ref="AA46:AA47"/>
+    <mergeCell ref="AB46:AB47"/>
+    <mergeCell ref="AC46:AC47"/>
+    <mergeCell ref="AD46:AD47"/>
+    <mergeCell ref="AA40:AA41"/>
+    <mergeCell ref="AB40:AB41"/>
+    <mergeCell ref="AC40:AC41"/>
+    <mergeCell ref="AD40:AD41"/>
+    <mergeCell ref="AA42:AA43"/>
+    <mergeCell ref="AB42:AB43"/>
+    <mergeCell ref="AC42:AC43"/>
+    <mergeCell ref="AD42:AD43"/>
+    <mergeCell ref="AA52:AA53"/>
+    <mergeCell ref="AB52:AB53"/>
+    <mergeCell ref="AC52:AC53"/>
+    <mergeCell ref="AD52:AD53"/>
+    <mergeCell ref="AA54:AA55"/>
+    <mergeCell ref="AB54:AB55"/>
+    <mergeCell ref="AC54:AC55"/>
+    <mergeCell ref="AD54:AD55"/>
+    <mergeCell ref="AA48:AA49"/>
+    <mergeCell ref="AB48:AB49"/>
+    <mergeCell ref="AC48:AC49"/>
+    <mergeCell ref="AD48:AD49"/>
+    <mergeCell ref="AA50:AA51"/>
+    <mergeCell ref="AB50:AB51"/>
+    <mergeCell ref="AC50:AC51"/>
+    <mergeCell ref="AD50:AD51"/>
+    <mergeCell ref="AB60:AB61"/>
+    <mergeCell ref="AC60:AC61"/>
+    <mergeCell ref="AD60:AD61"/>
+    <mergeCell ref="AA62:AA63"/>
+    <mergeCell ref="AB62:AB63"/>
+    <mergeCell ref="AC62:AC63"/>
+    <mergeCell ref="AD62:AD63"/>
+    <mergeCell ref="AA56:AA57"/>
+    <mergeCell ref="AB56:AB57"/>
+    <mergeCell ref="AC56:AC57"/>
+    <mergeCell ref="AD56:AD57"/>
+    <mergeCell ref="AA58:AA59"/>
+    <mergeCell ref="AB58:AB59"/>
+    <mergeCell ref="AC58:AC59"/>
+    <mergeCell ref="AD58:AD59"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="AB70:AB71"/>
+    <mergeCell ref="AC70:AC71"/>
+    <mergeCell ref="AD70:AD71"/>
+    <mergeCell ref="W8:Z8"/>
+    <mergeCell ref="AA8:AD8"/>
+    <mergeCell ref="AA68:AA69"/>
+    <mergeCell ref="AB68:AB69"/>
+    <mergeCell ref="AC68:AC69"/>
+    <mergeCell ref="AD68:AD69"/>
+    <mergeCell ref="AA70:AA71"/>
+    <mergeCell ref="AA64:AA65"/>
+    <mergeCell ref="AB64:AB65"/>
+    <mergeCell ref="AC64:AC65"/>
+    <mergeCell ref="AD64:AD65"/>
+    <mergeCell ref="AA66:AA67"/>
+    <mergeCell ref="AB66:AB67"/>
+    <mergeCell ref="AC66:AC67"/>
+    <mergeCell ref="AD66:AD67"/>
+    <mergeCell ref="AA60:AA61"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="M32:M33"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="M50:M51"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="K48:K49"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="M54:M55"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="L60:L61"/>
+    <mergeCell ref="M60:M61"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="K60:K61"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="M64:M65"/>
+    <mergeCell ref="M66:M67"/>
+    <mergeCell ref="M68:M69"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="S68:S69"/>
+    <mergeCell ref="S70:S71"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="S26:S27"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="S34:S35"/>
+    <mergeCell ref="S36:S37"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="S40:S41"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="S28:S29"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="S56:S57"/>
+    <mergeCell ref="S58:S59"/>
+    <mergeCell ref="S60:S61"/>
+    <mergeCell ref="S62:S63"/>
+    <mergeCell ref="S64:S65"/>
+    <mergeCell ref="S66:S67"/>
+    <mergeCell ref="S44:S45"/>
+    <mergeCell ref="S46:S47"/>
+    <mergeCell ref="S48:S49"/>
+    <mergeCell ref="S50:S51"/>
+    <mergeCell ref="S52:S53"/>
+    <mergeCell ref="S54:S55"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D60:D61"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="Q3:S3"/>
     <mergeCell ref="Q4:S4"/>
@@ -8039,591 +8624,6 @@
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="S56:S57"/>
-    <mergeCell ref="S58:S59"/>
-    <mergeCell ref="S60:S61"/>
-    <mergeCell ref="S62:S63"/>
-    <mergeCell ref="S64:S65"/>
-    <mergeCell ref="S66:S67"/>
-    <mergeCell ref="S44:S45"/>
-    <mergeCell ref="S46:S47"/>
-    <mergeCell ref="S48:S49"/>
-    <mergeCell ref="S50:S51"/>
-    <mergeCell ref="S52:S53"/>
-    <mergeCell ref="S54:S55"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="S34:S35"/>
-    <mergeCell ref="S36:S37"/>
-    <mergeCell ref="S38:S39"/>
-    <mergeCell ref="S40:S41"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="S28:S29"/>
-    <mergeCell ref="S30:S31"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="S12:S13"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="M64:M65"/>
-    <mergeCell ref="M66:M67"/>
-    <mergeCell ref="M68:M69"/>
-    <mergeCell ref="M70:M71"/>
-    <mergeCell ref="S68:S69"/>
-    <mergeCell ref="S70:S71"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L68:L69"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="K70:K71"/>
-    <mergeCell ref="L70:L71"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="S26:S27"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="K68:K69"/>
-    <mergeCell ref="L64:L65"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="K66:K67"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="I64:I65"/>
-    <mergeCell ref="J64:J65"/>
-    <mergeCell ref="K64:K65"/>
-    <mergeCell ref="L60:L61"/>
-    <mergeCell ref="M60:M61"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="K62:K63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="K60:K61"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="K56:K57"/>
-    <mergeCell ref="L52:L53"/>
-    <mergeCell ref="M52:M53"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="M54:M55"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="K52:K53"/>
-    <mergeCell ref="L48:L49"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="J50:J51"/>
-    <mergeCell ref="K50:K51"/>
-    <mergeCell ref="L50:L51"/>
-    <mergeCell ref="M50:M51"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="J48:J49"/>
-    <mergeCell ref="K48:K49"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="K46:K47"/>
-    <mergeCell ref="L46:L47"/>
-    <mergeCell ref="M46:M47"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="K42:K43"/>
-    <mergeCell ref="L42:L43"/>
-    <mergeCell ref="M42:M43"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L32:L33"/>
-    <mergeCell ref="M32:M33"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="K32:K33"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="AB70:AB71"/>
-    <mergeCell ref="AC70:AC71"/>
-    <mergeCell ref="AD70:AD71"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="AA8:AD8"/>
-    <mergeCell ref="AA68:AA69"/>
-    <mergeCell ref="AB68:AB69"/>
-    <mergeCell ref="AC68:AC69"/>
-    <mergeCell ref="AD68:AD69"/>
-    <mergeCell ref="AA70:AA71"/>
-    <mergeCell ref="AA64:AA65"/>
-    <mergeCell ref="AB64:AB65"/>
-    <mergeCell ref="AC64:AC65"/>
-    <mergeCell ref="AD64:AD65"/>
-    <mergeCell ref="AA66:AA67"/>
-    <mergeCell ref="AB66:AB67"/>
-    <mergeCell ref="AC66:AC67"/>
-    <mergeCell ref="AD66:AD67"/>
-    <mergeCell ref="AA60:AA61"/>
-    <mergeCell ref="AB60:AB61"/>
-    <mergeCell ref="AC60:AC61"/>
-    <mergeCell ref="AD60:AD61"/>
-    <mergeCell ref="AA62:AA63"/>
-    <mergeCell ref="AB62:AB63"/>
-    <mergeCell ref="AC62:AC63"/>
-    <mergeCell ref="AD62:AD63"/>
-    <mergeCell ref="AA56:AA57"/>
-    <mergeCell ref="AB56:AB57"/>
-    <mergeCell ref="AC56:AC57"/>
-    <mergeCell ref="AD56:AD57"/>
-    <mergeCell ref="AA58:AA59"/>
-    <mergeCell ref="AB58:AB59"/>
-    <mergeCell ref="AC58:AC59"/>
-    <mergeCell ref="AD58:AD59"/>
-    <mergeCell ref="AA52:AA53"/>
-    <mergeCell ref="AB52:AB53"/>
-    <mergeCell ref="AC52:AC53"/>
-    <mergeCell ref="AD52:AD53"/>
-    <mergeCell ref="AA54:AA55"/>
-    <mergeCell ref="AB54:AB55"/>
-    <mergeCell ref="AC54:AC55"/>
-    <mergeCell ref="AD54:AD55"/>
-    <mergeCell ref="AA48:AA49"/>
-    <mergeCell ref="AB48:AB49"/>
-    <mergeCell ref="AC48:AC49"/>
-    <mergeCell ref="AD48:AD49"/>
-    <mergeCell ref="AA50:AA51"/>
-    <mergeCell ref="AB50:AB51"/>
-    <mergeCell ref="AC50:AC51"/>
-    <mergeCell ref="AD50:AD51"/>
-    <mergeCell ref="AA44:AA45"/>
-    <mergeCell ref="AB44:AB45"/>
-    <mergeCell ref="AC44:AC45"/>
-    <mergeCell ref="AD44:AD45"/>
-    <mergeCell ref="AA46:AA47"/>
-    <mergeCell ref="AB46:AB47"/>
-    <mergeCell ref="AC46:AC47"/>
-    <mergeCell ref="AD46:AD47"/>
-    <mergeCell ref="AA40:AA41"/>
-    <mergeCell ref="AB40:AB41"/>
-    <mergeCell ref="AC40:AC41"/>
-    <mergeCell ref="AD40:AD41"/>
-    <mergeCell ref="AA42:AA43"/>
-    <mergeCell ref="AB42:AB43"/>
-    <mergeCell ref="AC42:AC43"/>
-    <mergeCell ref="AD42:AD43"/>
-    <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="AB36:AB37"/>
-    <mergeCell ref="AC36:AC37"/>
-    <mergeCell ref="AD36:AD37"/>
-    <mergeCell ref="AA38:AA39"/>
-    <mergeCell ref="AB38:AB39"/>
-    <mergeCell ref="AC38:AC39"/>
-    <mergeCell ref="AD38:AD39"/>
-    <mergeCell ref="AA32:AA33"/>
-    <mergeCell ref="AB32:AB33"/>
-    <mergeCell ref="AC32:AC33"/>
-    <mergeCell ref="AD32:AD33"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AB34:AB35"/>
-    <mergeCell ref="AC34:AC35"/>
-    <mergeCell ref="AD34:AD35"/>
-    <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="AB28:AB29"/>
-    <mergeCell ref="AC28:AC29"/>
-    <mergeCell ref="AD28:AD29"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="AB30:AB31"/>
-    <mergeCell ref="AC30:AC31"/>
-    <mergeCell ref="AD30:AD31"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="AB24:AB25"/>
-    <mergeCell ref="AC24:AC25"/>
-    <mergeCell ref="AD24:AD25"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="AC26:AC27"/>
-    <mergeCell ref="AD26:AD27"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="AB20:AB21"/>
-    <mergeCell ref="AC20:AC21"/>
-    <mergeCell ref="AD20:AD21"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="AB22:AB23"/>
-    <mergeCell ref="AC22:AC23"/>
-    <mergeCell ref="AD22:AD23"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="AB18:AB19"/>
-    <mergeCell ref="AC18:AC19"/>
-    <mergeCell ref="AD18:AD19"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="AB10:AB11"/>
-    <mergeCell ref="AC10:AC11"/>
-    <mergeCell ref="AD10:AD11"/>
-    <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="AB12:AB13"/>
-    <mergeCell ref="AC12:AC13"/>
-    <mergeCell ref="AD12:AD13"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="AF10:AF11"/>
-    <mergeCell ref="AG10:AG11"/>
-    <mergeCell ref="AH10:AH11"/>
-    <mergeCell ref="AI10:AI11"/>
-    <mergeCell ref="AF12:AF13"/>
-    <mergeCell ref="AG12:AG13"/>
-    <mergeCell ref="AH12:AH13"/>
-    <mergeCell ref="AI12:AI13"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="AG14:AG15"/>
-    <mergeCell ref="AH14:AH15"/>
-    <mergeCell ref="AI14:AI15"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="AH16:AH17"/>
-    <mergeCell ref="AI16:AI17"/>
-    <mergeCell ref="AF18:AF19"/>
-    <mergeCell ref="AG18:AG19"/>
-    <mergeCell ref="AH18:AH19"/>
-    <mergeCell ref="AI18:AI19"/>
-    <mergeCell ref="AF20:AF21"/>
-    <mergeCell ref="AG20:AG21"/>
-    <mergeCell ref="AH20:AH21"/>
-    <mergeCell ref="AI20:AI21"/>
-    <mergeCell ref="AF22:AF23"/>
-    <mergeCell ref="AG22:AG23"/>
-    <mergeCell ref="AH22:AH23"/>
-    <mergeCell ref="AI22:AI23"/>
-    <mergeCell ref="AF24:AF25"/>
-    <mergeCell ref="AG24:AG25"/>
-    <mergeCell ref="AH24:AH25"/>
-    <mergeCell ref="AI24:AI25"/>
-    <mergeCell ref="AF26:AF27"/>
-    <mergeCell ref="AG26:AG27"/>
-    <mergeCell ref="AH26:AH27"/>
-    <mergeCell ref="AI26:AI27"/>
-    <mergeCell ref="AF28:AF29"/>
-    <mergeCell ref="AG28:AG29"/>
-    <mergeCell ref="AH28:AH29"/>
-    <mergeCell ref="AI28:AI29"/>
-    <mergeCell ref="AF30:AF31"/>
-    <mergeCell ref="AG30:AG31"/>
-    <mergeCell ref="AH30:AH31"/>
-    <mergeCell ref="AI30:AI31"/>
-    <mergeCell ref="AF32:AF33"/>
-    <mergeCell ref="AG32:AG33"/>
-    <mergeCell ref="AH32:AH33"/>
-    <mergeCell ref="AI32:AI33"/>
-    <mergeCell ref="AF34:AF35"/>
-    <mergeCell ref="AG34:AG35"/>
-    <mergeCell ref="AH34:AH35"/>
-    <mergeCell ref="AI34:AI35"/>
-    <mergeCell ref="AF36:AF37"/>
-    <mergeCell ref="AG36:AG37"/>
-    <mergeCell ref="AH36:AH37"/>
-    <mergeCell ref="AI36:AI37"/>
-    <mergeCell ref="AF38:AF39"/>
-    <mergeCell ref="AG38:AG39"/>
-    <mergeCell ref="AH38:AH39"/>
-    <mergeCell ref="AI38:AI39"/>
-    <mergeCell ref="AF40:AF41"/>
-    <mergeCell ref="AG40:AG41"/>
-    <mergeCell ref="AH40:AH41"/>
-    <mergeCell ref="AI40:AI41"/>
-    <mergeCell ref="AF42:AF43"/>
-    <mergeCell ref="AG42:AG43"/>
-    <mergeCell ref="AH42:AH43"/>
-    <mergeCell ref="AI42:AI43"/>
-    <mergeCell ref="AF44:AF45"/>
-    <mergeCell ref="AG44:AG45"/>
-    <mergeCell ref="AH44:AH45"/>
-    <mergeCell ref="AI44:AI45"/>
-    <mergeCell ref="AF46:AF47"/>
-    <mergeCell ref="AG46:AG47"/>
-    <mergeCell ref="AH46:AH47"/>
-    <mergeCell ref="AI46:AI47"/>
-    <mergeCell ref="AF48:AF49"/>
-    <mergeCell ref="AG48:AG49"/>
-    <mergeCell ref="AH48:AH49"/>
-    <mergeCell ref="AI48:AI49"/>
-    <mergeCell ref="AF50:AF51"/>
-    <mergeCell ref="AG50:AG51"/>
-    <mergeCell ref="AH50:AH51"/>
-    <mergeCell ref="AI50:AI51"/>
-    <mergeCell ref="AF52:AF53"/>
-    <mergeCell ref="AG52:AG53"/>
-    <mergeCell ref="AH52:AH53"/>
-    <mergeCell ref="AI52:AI53"/>
-    <mergeCell ref="AF54:AF55"/>
-    <mergeCell ref="AG54:AG55"/>
-    <mergeCell ref="AH54:AH55"/>
-    <mergeCell ref="AI54:AI55"/>
-    <mergeCell ref="AF56:AF57"/>
-    <mergeCell ref="AG56:AG57"/>
-    <mergeCell ref="AH56:AH57"/>
-    <mergeCell ref="AI56:AI57"/>
-    <mergeCell ref="AF58:AF59"/>
-    <mergeCell ref="AG58:AG59"/>
-    <mergeCell ref="AH58:AH59"/>
-    <mergeCell ref="AI58:AI59"/>
-    <mergeCell ref="AF60:AF61"/>
-    <mergeCell ref="AG60:AG61"/>
-    <mergeCell ref="AH60:AH61"/>
-    <mergeCell ref="AI60:AI61"/>
-    <mergeCell ref="AF62:AF63"/>
-    <mergeCell ref="AG62:AG63"/>
-    <mergeCell ref="AH62:AH63"/>
-    <mergeCell ref="AI62:AI63"/>
-    <mergeCell ref="AF70:AF71"/>
-    <mergeCell ref="AG70:AG71"/>
-    <mergeCell ref="AH70:AH71"/>
-    <mergeCell ref="AI70:AI71"/>
-    <mergeCell ref="AF64:AF65"/>
-    <mergeCell ref="AG64:AG65"/>
-    <mergeCell ref="AH64:AH65"/>
-    <mergeCell ref="AI64:AI65"/>
-    <mergeCell ref="AF66:AF67"/>
-    <mergeCell ref="AG66:AG67"/>
-    <mergeCell ref="AH66:AH67"/>
-    <mergeCell ref="AI66:AI67"/>
-    <mergeCell ref="AF68:AF69"/>
-    <mergeCell ref="AG68:AG69"/>
-    <mergeCell ref="AH68:AH69"/>
-    <mergeCell ref="AI68:AI69"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
